--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenhe\Desktop\Test\知财PoC\IPC_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEFC73A-2310-4359-89C4-D6798319CA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E165F0ED-1C81-457F-8820-9DC52E603B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{685DA10D-DEC5-4705-BAF0-A25F74872425}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="5" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sample!$A$1:$L$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="141">
   <si>
     <t>publication-doc-number</t>
   </si>
@@ -455,7 +458,23 @@
     <t>A61M60/00,A61M1/00,B01D61/00,A61B5/00,B01D35/00,A61M60/00,A61M1/00,G11B27/00,G11B15/00,G06F7/00,G06F16/00,G06F18/00,G06V10/00,G11B27/00,H04L41/00,G07C1/00,G06F7/00,G06F18/00,G06M3/00,G04C23/00,A61M60/00,A61B5/00,H04W68/00,G06F11/00,G04C21/00</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>middle_nums</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>final_nums</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in_middle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A63F5/04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in_final</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -509,7 +528,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -519,38 +538,29 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -560,14 +570,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -576,26 +583,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -606,6 +650,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}" name="表2" displayName="表2" ref="I1:L26" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="I1:L26" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{668323CC-C691-4B3E-9439-CA42E7EA43F7}" name="middle_nums">
+      <calculatedColumnFormula>LEN(G2)-LEN(SUBSTITUTE(G2,"/",""))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{2AEC24EC-0005-48E6-A62B-724BD7DEF298}" name="final_nums">
+      <calculatedColumnFormula>LEN(H2)-LEN(SUBSTITUTE(H2,"/",""))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{296F10EE-168B-4A76-91E8-AD2AA5FD245B}" name="in_middle">
+      <calculatedColumnFormula>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),G2))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{BCBCAEFC-B480-4DD8-AB56-2C6F0711A6EB}" name="in_final">
+      <calculatedColumnFormula>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),H2))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -905,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742BDA38-63BE-424F-A9B2-256A772D5CD7}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -914,764 +979,1107 @@
     <col min="4" max="4" width="24.140625" customWidth="1"/>
     <col min="5" max="5" width="22.2109375" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.2109375" customWidth="1"/>
+    <col min="7" max="7" width="19.92578125" customWidth="1"/>
     <col min="8" max="8" width="19.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.78515625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
+      <c r="I1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>2019000004</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
+      <c r="I2">
+        <f>LEN(G2)-LEN(SUBSTITUTE(G2,"/",""))</f>
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <f>LEN(H2)-LEN(SUBSTITUTE(H2,"/",""))</f>
+        <v>25</v>
+      </c>
+      <c r="K2" t="b">
+        <f>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),G2))</f>
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <f>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),H2))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
         <v>2019000021</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+      <c r="I3">
+        <f t="shared" ref="I3:I26" si="0">LEN(G3)-LEN(SUBSTITUTE(G3,"/",""))</f>
+        <v>80</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J26" si="1">LEN(H3)-LEN(SUBSTITUTE(H3,"/",""))</f>
+        <v>20</v>
+      </c>
+      <c r="K3" t="b">
+        <f t="shared" ref="K3:K26" si="2">ISNUMBER(SEARCH(LEFT($C3,FIND("/",$C3)-1),G3))</f>
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <f t="shared" ref="L3:L26" si="3">ISNUMBER(SEARCH(LEFT($C3,FIND("/",$C3)-1),H3))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>2019000028</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K4" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
         <v>2019000046</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K5" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>2019000051</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="5">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="K6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
         <v>2019000055</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K7" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>2019000059</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K8" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
         <v>2019000061</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K9" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>2019000064</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="5">
-        <v>1</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K10" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
         <v>2019000102</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K11" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>2019000125</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K12" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
         <v>2019000169</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K13" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>2019000190</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="5">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K14" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
         <v>2019000203</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K15" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>2019000223</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="5">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="K16" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
         <v>2019000227</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K17" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>2019000246</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F18" s="5">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="I18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K18" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
         <v>2019000249</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K19" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>2019000250</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K20" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>2019000266</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="6">
-        <v>1</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="I19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
-        <v>2019000250</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="E21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K21" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>2019000277</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K22" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>2019000293</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K23" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>2019000297</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="5">
-        <v>1</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>2019000266</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
-        <v>2019000277</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>2019000293</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F23" s="6">
-        <v>1</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
-        <v>2019000297</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="5">
-        <v>1</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K24" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
         <v>2019000302</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F25" s="6">
-        <v>1</v>
-      </c>
-      <c r="G25" s="6" t="s">
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="I25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K25" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>2019000311</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F26" s="5">
-        <v>1</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I26" t="s">
-        <v>136</v>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K26" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenhe\Desktop\Test\知财PoC\IPC_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E165F0ED-1C81-457F-8820-9DC52E603B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F844C743-2B19-4E0B-8F1A-8B80A7907AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{685DA10D-DEC5-4705-BAF0-A25F74872425}"/>
   </bookViews>
   <sheets>
-    <sheet name="sample" sheetId="5" r:id="rId1"/>
+    <sheet name="説明" sheetId="6" r:id="rId1"/>
+    <sheet name="sample" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sample!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sample!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="151">
   <si>
     <t>publication-doc-number</t>
   </si>
@@ -456,25 +457,54 @@
   </si>
   <si>
     <t>A61M60/00,A61M1/00,B01D61/00,A61B5/00,B01D35/00,A61M60/00,A61M1/00,G11B27/00,G11B15/00,G06F7/00,G06F16/00,G06F18/00,G06V10/00,G11B27/00,H04L41/00,G07C1/00,G06F7/00,G06F18/00,G06M3/00,G04C23/00,A61M60/00,A61B5/00,H04W68/00,G06F11/00,G04C21/00</t>
-  </si>
-  <si>
-    <t>middle_nums</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>final_nums</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_middle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>A63F5/04</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in_final</t>
+    <t>middle_main_hit_count</t>
+  </si>
+  <si>
+    <t>middle_main_miss_count</t>
+  </si>
+  <si>
+    <t>middle_all_hit_count</t>
+  </si>
+  <si>
+    <t>middle_all_miss_count</t>
+  </si>
+  <si>
+    <t>final_main_hit_count</t>
+  </si>
+  <si>
+    <t>final_main_miss_count</t>
+  </si>
+  <si>
+    <t>final_all_hit_count</t>
+  </si>
+  <si>
+    <t>final_all_miss_count</t>
+  </si>
+  <si>
+    <t>actual_all_ipc_count</t>
+  </si>
+  <si>
+    <t>middle_predicted_ipc_count</t>
+  </si>
+  <si>
+    <t>final_predicted_ipc_count</t>
+  </si>
+  <si>
+    <t>テストデータ各指標の説明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Field</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>説明</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +512,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,6 +537,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -528,7 +573,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -564,13 +609,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -592,11 +661,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -632,13 +736,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -653,21 +750,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}" name="表2" displayName="表2" ref="I1:L26" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="1">
-  <autoFilter ref="I1:L26" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{668323CC-C691-4B3E-9439-CA42E7EA43F7}" name="middle_nums">
-      <calculatedColumnFormula>LEN(G2)-LEN(SUBSTITUTE(G2,"/",""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{2AEC24EC-0005-48E6-A62B-724BD7DEF298}" name="final_nums">
-      <calculatedColumnFormula>LEN(H2)-LEN(SUBSTITUTE(H2,"/",""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{296F10EE-168B-4A76-91E8-AD2AA5FD245B}" name="in_middle">
-      <calculatedColumnFormula>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),G2))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{BCBCAEFC-B480-4DD8-AB56-2C6F0711A6EB}" name="in_final">
-      <calculatedColumnFormula>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),H2))</calculatedColumnFormula>
-    </tableColumn>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50C048EB-92AB-4244-B4D0-048FBE6AF9A0}" name="表1" displayName="表1" ref="A2:B10" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B10" xr:uid="{50C048EB-92AB-4244-B4D0-048FBE6AF9A0}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{ADC04FDD-BFC8-4C2D-A7BC-99817619D621}" name="Field"/>
+    <tableColumn id="2" xr3:uid="{9169A870-5B79-4A57-B7F7-BC09DEE38743}" name="説明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}" name="表2" displayName="表2" ref="I1:S26" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="1">
+  <autoFilter ref="I1:S26" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{668323CC-C691-4B3E-9439-CA42E7EA43F7}" name="middle_main_hit_count"/>
+    <tableColumn id="2" xr3:uid="{2AEC24EC-0005-48E6-A62B-724BD7DEF298}" name="middle_main_miss_count"/>
+    <tableColumn id="3" xr3:uid="{296F10EE-168B-4A76-91E8-AD2AA5FD245B}" name="middle_all_hit_count"/>
+    <tableColumn id="4" xr3:uid="{BCBCAEFC-B480-4DD8-AB56-2C6F0711A6EB}" name="middle_all_miss_count"/>
+    <tableColumn id="5" xr3:uid="{39AA68BB-B3B6-4BE5-A595-97711FFF28FE}" name="final_main_hit_count"/>
+    <tableColumn id="6" xr3:uid="{500C2E05-0458-4856-BBF7-E6CF48F9C67C}" name="final_main_miss_count"/>
+    <tableColumn id="7" xr3:uid="{039B68DD-843B-40BE-AE5A-D6757A744BB1}" name="final_all_hit_count"/>
+    <tableColumn id="8" xr3:uid="{06BC69B4-9933-4DBD-9834-D689A8B513BC}" name="final_all_miss_count"/>
+    <tableColumn id="9" xr3:uid="{E3C38C6F-432E-4566-8376-483C704A6042}" name="actual_all_ipc_count"/>
+    <tableColumn id="10" xr3:uid="{74934023-1831-42EC-996B-51104C7C684B}" name="middle_predicted_ipc_count"/>
+    <tableColumn id="15" xr3:uid="{242EE457-F26C-4D60-ABB9-6E6888A4AA7C}" name="final_predicted_ipc_count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -969,8 +1076,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B08F830B-D02E-4816-93C9-531D788971DC}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="30.78515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.45" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" spans="1:2" ht="18.45" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742BDA38-63BE-424F-A9B2-256A772D5CD7}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -986,7 +1167,7 @@
     <col min="11" max="11" width="10.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1012,19 +1193,40 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M1" t="s">
+        <v>141</v>
+      </c>
+      <c r="N1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>145</v>
+      </c>
+      <c r="R1" t="s">
+        <v>146</v>
+      </c>
+      <c r="S1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>2019000004</v>
       </c>
@@ -1050,23 +1252,40 @@
         <v>13</v>
       </c>
       <c r="I2">
-        <f>LEN(G2)-LEN(SUBSTITUTE(G2,"/",""))</f>
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <f>LEN(H2)-LEN(SUBSTITUTE(H2,"/",""))</f>
-        <v>25</v>
-      </c>
-      <c r="K2" t="b">
-        <f>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),G2))</f>
-        <v>1</v>
-      </c>
-      <c r="L2" t="b">
-        <f>ISNUMBER(SEARCH(LEFT($C2,FIND("/",$C2)-1),H2))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <v>76</v>
+      </c>
+      <c r="S2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2019000021</v>
       </c>
@@ -1092,23 +1311,40 @@
         <v>19</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I26" si="0">LEN(G3)-LEN(SUBSTITUTE(G3,"/",""))</f>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J26" si="1">LEN(H3)-LEN(SUBSTITUTE(H3,"/",""))</f>
-        <v>20</v>
-      </c>
-      <c r="K3" t="b">
-        <f t="shared" ref="K3:K26" si="2">ISNUMBER(SEARCH(LEFT($C3,FIND("/",$C3)-1),G3))</f>
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <f t="shared" ref="L3:L26" si="3">ISNUMBER(SEARCH(LEFT($C3,FIND("/",$C3)-1),H3))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
+        <v>81</v>
+      </c>
+      <c r="S3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2019000028</v>
       </c>
@@ -1134,23 +1370,40 @@
         <v>25</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K4" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L4" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>73</v>
+      </c>
+      <c r="S4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2019000046</v>
       </c>
@@ -1176,23 +1429,40 @@
         <v>30</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K5" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L5" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>58</v>
+      </c>
+      <c r="S5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2019000051</v>
       </c>
@@ -1218,23 +1488,40 @@
         <v>35</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="K6" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L6" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>74</v>
+      </c>
+      <c r="S6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2019000055</v>
       </c>
@@ -1260,23 +1547,40 @@
         <v>41</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K7" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L7" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>89</v>
+      </c>
+      <c r="S7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2019000059</v>
       </c>
@@ -1302,23 +1606,40 @@
         <v>47</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K8" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L8" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>66</v>
+      </c>
+      <c r="S8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>2019000061</v>
       </c>
@@ -1344,23 +1665,40 @@
         <v>51</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K9" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L9" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>86</v>
+      </c>
+      <c r="S9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2019000064</v>
       </c>
@@ -1386,23 +1724,40 @@
         <v>57</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K10" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L10" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>2</v>
+      </c>
+      <c r="R10">
+        <v>78</v>
+      </c>
+      <c r="S10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>2019000102</v>
       </c>
@@ -1428,23 +1783,40 @@
         <v>63</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K11" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L11" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="R11">
+        <v>66</v>
+      </c>
+      <c r="S11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2019000125</v>
       </c>
@@ -1470,23 +1842,40 @@
         <v>68</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K12" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L12" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>65</v>
+      </c>
+      <c r="S12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>2019000169</v>
       </c>
@@ -1512,23 +1901,40 @@
         <v>73</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K13" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L13" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>66</v>
+      </c>
+      <c r="S13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>2019000190</v>
       </c>
@@ -1554,23 +1960,40 @@
         <v>79</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>77</v>
+      </c>
+      <c r="S14">
         <v>20</v>
       </c>
-      <c r="K14" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L14" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>2019000203</v>
       </c>
@@ -1596,23 +2019,40 @@
         <v>82</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K15" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L15" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>41</v>
+      </c>
+      <c r="S15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>2019000223</v>
       </c>
@@ -1638,23 +2078,40 @@
         <v>85</v>
       </c>
       <c r="I16">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="K16" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>61</v>
+      </c>
+      <c r="S16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>2019000227</v>
       </c>
@@ -1680,23 +2137,40 @@
         <v>91</v>
       </c>
       <c r="I17">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K17" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L17" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>85</v>
+      </c>
+      <c r="S17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>2019000246</v>
       </c>
@@ -1722,23 +2196,40 @@
         <v>96</v>
       </c>
       <c r="I18">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K18" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L18" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>75</v>
+      </c>
+      <c r="S18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>2019000249</v>
       </c>
@@ -1746,7 +2237,7 @@
         <v>74</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>22</v>
@@ -1764,23 +2255,40 @@
         <v>99</v>
       </c>
       <c r="I19">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K19" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>61</v>
+      </c>
+      <c r="S19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2019000250</v>
       </c>
@@ -1806,23 +2314,40 @@
         <v>105</v>
       </c>
       <c r="I20">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K20" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L20" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>55</v>
+      </c>
+      <c r="S20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>2019000266</v>
       </c>
@@ -1848,23 +2373,40 @@
         <v>108</v>
       </c>
       <c r="I21">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K21" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L21" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>79</v>
+      </c>
+      <c r="S21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2019000277</v>
       </c>
@@ -1890,23 +2432,40 @@
         <v>113</v>
       </c>
       <c r="I22">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K22" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L22" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>71</v>
+      </c>
+      <c r="S22">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>2019000293</v>
       </c>
@@ -1932,23 +2491,40 @@
         <v>118</v>
       </c>
       <c r="I23">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="K23" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L23" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>2</v>
+      </c>
+      <c r="R23">
+        <v>62</v>
+      </c>
+      <c r="S23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2019000297</v>
       </c>
@@ -1974,23 +2550,40 @@
         <v>124</v>
       </c>
       <c r="I24">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K24" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L24" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>64</v>
+      </c>
+      <c r="S24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>2019000302</v>
       </c>
@@ -2016,23 +2609,40 @@
         <v>130</v>
       </c>
       <c r="I25">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K25" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L25" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>61</v>
+      </c>
+      <c r="S25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2019000311</v>
       </c>
@@ -2058,23 +2668,41 @@
         <v>135</v>
       </c>
       <c r="I26">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="K26" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L26" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>2</v>
+      </c>
+      <c r="R26">
+        <v>47</v>
+      </c>
+      <c r="S26">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H26" xr:uid="{742BDA38-63BE-424F-A9B2-256A772D5CD7}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenhe\Desktop\Test\知财PoC\IPC_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F844C743-2B19-4E0B-8F1A-8B80A7907AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CA53C9-CF57-4527-9E50-79E339E6C2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{685DA10D-DEC5-4705-BAF0-A25F74872425}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{685DA10D-DEC5-4705-BAF0-A25F74872425}"/>
   </bookViews>
   <sheets>
     <sheet name="説明" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="149">
   <si>
     <t>publication-doc-number</t>
   </si>
@@ -87,12 +87,6 @@
     <t>【課題】合成乳化剤が無添加であるにも関わらず、内相がきめ細かく、ボリューム、食感、及び老化抑制に優れたパンを作業性よく製造可能なパン生地を提供すること 【解決手段】油脂組成物が練り込まれたパン生地であって、前記パン生地は、合成乳化剤を含まず、アミラーゼを穀粉１００ｇに対し１．５〜１５０単位含有し、前記油脂組成物は、融点が２５〜４５℃の油脂と、Ｌ−アスコルビン酸とを含有し、含気され、比重が０．２〜０．８ｇ／ｍＬであり、油脂組成物の含有量は穀粉１００重量部に対し１〜３０重量部、油脂組成物に含まれるＬ−アスコルビン酸の含有量は穀粉１００重量部に対し４．０×１０〜４．０×１０重量部、油脂組成物に含まれていないがパン生地中に含まれているＬ−アスコルビン酸の含有量は穀粉１００重量部に対し１×１０重量部未満である、パン生地。</t>
   </si>
   <si>
-    <t>A23C9/00,A21D13/00,A23C15/00,A23C11/00,A23L7/00,A23C19/00,A21D2/00,D06P1/00,A01J15/00,A21D8/00,C08F2/00,C08B30/00,A23G3/00,C11D10/00,D06L4/00,C09D11/00,C07C17/00,B05D7/00,D06N3/00,C07C57/00,A23C15/00,C07C69/00,A21D13/00,C12P7/00,C09K8/00,B01F101/00,C08G63/00,C08K13/00,G01N33/00,A23G9/00,C10M173/00,A23L29/00,C11D3/00,C10M107/00,C10M143/00,A23C11/00,C10M119/00,A61K47/00,C10M159/00,C10L1/00,C12N9/00,A21D8/00,D21H23/00,C12N15/00,C12P19/00,A23C9/00,A23K10/00,C09K8/00,A23L2/00,A21D13/00,C09D1/00,C01F7/00,A23L13/00,C04B38/00,A21D2/00,D06L4/00,A23L7/00,C12Q1/00,C08F2/00,C07C209/00,C08J9/00,A23L7/00,B65B1/00,A21D13/00,B65B3/00,C09K8/00,A23P20/00,B29C70/00,G05D5/00,B65B25/00,A21D8/00,A23P10/00,B28C1/00,H01M8/00,B21B37/00,A62D1/00,A23P30/00,F16L55/00,C12G1/00,C12C11/00,A21D13/00,H01M4/00,A23L7/00,B65B25/00,A21B5/00,A21D8/00,C08J9/00,C12G1/00,C12C11/00,B28C1/00,C08G69/00,A21C3/00,B28B21/00,A01J25/00,F16C33/00,B01F101/00,D02J1/00,C03B23/00,C04B35/00,C08J3/00</t>
-  </si>
-  <si>
-    <t>A21D2/00,A21D8/00,A21D13/00,A23L7/00,A23C15/00,A23C15/00,A21D13/00,C07C69/00,C12P7/00,B01F101/00,C12N9/00,A21D8/00,A21D13/00,C12P19/00,C12N15/00,A21D13/00,A23L7/00,C08J9/00,A23P20/00,G05D5/00,A21D13/00,A23L7/00,A21B5/00,A21D8/00,C08J9/00</t>
-  </si>
-  <si>
     <t>複合油脂性菓子</t>
   </si>
   <si>
@@ -105,30 +99,15 @@
     <t>【課題】油脂性菓子の内層と外層とで食感の変化を楽しむことができると共に、保存期間中における品質の劣化を抑制できるようにした複合油脂性菓子を提供する。 【解決手段】内層１２をなす第１油脂性菓子と、前記第１油脂性菓子の全部又は少なくとも大部分を覆って外層１１をなす第２油脂性菓子とを接合してなる複合油脂性菓子１０ａであって、前記第１油脂性菓子は、水分含量が５質量％以上２０質量％以下であり、前記第２油脂性菓子は、還元イソマルツロース及び／又はイソマルツロースを２６質量％以上５０質量％以下含有しており、前記第２油脂性菓子の表層が、焼成によって手で持ったときにべとつかない程度に熱変性している。</t>
   </si>
   <si>
-    <t>A23G3/00,C09K8/00,B32B37/00,A23P20/00,C03C25/00,A23G9/00,H01M50/00,A23G1/00,A21D13/00,B29C48/00,C08K13/00,H01M8/00,D04H1/00,B29C43/00,B29C39/00,B29C41/00,B29C64/00,G11B7/00,C06B45/00,C08G63/00,C09K8/00,C08F2/00,A23G1/00,D21H23/00,A23C19/00,A21D13/00,A23G3/00,A23P10/00,A23P20/00,F24F1/00,B29C70/00,D21H21/00,D21H19/00,C09F5/00,A23L2/00,A23L7/00,H01M4/00,A23L3/00,A61P17/00,C14C9/00,A61K31/00,C07H3/00,C07H19/00,C06B45/00,C08F2/00,C08G18/00,C12P19/00,C09K23/00,C12C7/00,A23C19/00,A61K9/00,A23G3/00,C12Q1/00,B01F101/00,A23L29/00,A23C15/00,A23L33/00,C13K1/00,C08G63/00,A23P20/00,C23C8/00,C21D1/00,C25D5/00,H01L21/00,C23C10/00,B29C48/00,C23C22/00,B05D5/00,C08J7/00,C23C18/00,B29C53/00,B28B1/00,A23B7/00,C03B37/00,B05D3/00,C23D13/00,H05K3/00,B24C1/00,B22F1/00,A23B4/00</t>
-  </si>
-  <si>
-    <t>A23G3/00,A23P20/00,B32B37/00,A23G1/00,A21D13/00,A23G1/00,A23G3/00,A21D13/00,A23P20/00,A23P10/00,C07H3/00,C12P19/00,C06B45/00,A61K31/00,C07H19/00,B05D5/00,C08J7/00,C21D1/00,B29C48/00,C23C18/00</t>
-  </si>
-  <si>
     <t>アイソレータ</t>
   </si>
   <si>
     <t>C12M1/00</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>【課題】   滅菌時に、短時間で滅菌ガスを作業室全体に行き渡らせる。 【解決手段】   作業室と、前記作業室の前面に設けた前面扉を有し、循環用ファンにより、エアフィルタおよびパンチング板を介して前記作業室に清浄な空気が供給されるアイソレータであって、前記エアフィルタと前記パンチング板との間の領域に、少なくとも２つの滅菌ガス投入口を設けたものである。</t>
   </si>
   <si>
-    <t>F24F3/00,A23L3/00,B65G53/00,H01J7/00,B07B11/00,A47L15/00,B65B55/00,A61M16/00,H01J61/00,H01H33/00,F26B3/00,C10B21/00,G21C19/00,A61G10/00,C01B3/00,A61B90/00,C02F1/00,D21C7/00,C12M1/00,F24F8/00,F24F1/00,H02B11/00,G21C19/00,E06B3/00,H01P1/00,H01R13/00,H01M50/00,B04C5/00,B01D33/00,F01C20/00,H01H13/00,E06B7/00,H01F27/00,H01H33/00,F23C10/00,E04B2/00,B65D1/00,F25D23/00,B65H3/00,H01J11/00,B01D46/00,F24F3/00,F01N3/00,B01D35/00,F02M35/00,F24F7/00,F02M26/00,F24F1/00,B01D33/00,B05B14/00,F01P5/00,F23N1/00,B01F25/00,B01D41/00,A47L5/00,B05B16/00,F24F11/00,B04B15/00,F23C10/00,E03D9/00,F27B7/00,F27B1/00,F27B5/00,F27B15/00,F23B50/00,E03C1/00,F24H9/00,B65B55/00,F27B14/00,F27B9/00,F27B3/00,F23C7/00,F02M69/00,A61M39/00,C10J3/00,B01D35/00,C21D9/00,G02F1/00,B29C45/00,H01H33/00</t>
-  </si>
-  <si>
-    <t>F24F3/00,A23L3/00,B65G53/00,B65B55/00,A61M16/00,F24F1/00,E06B3/00,B01D33/00,H02B11/00,G21C19/00,B01D46/00,F24F3/00,F24F7/00,B01D35/00,F24F1/00,B65B55/00,F27B5/00,F27B7/00,F27B1/00,F27B15/00</t>
-  </si>
-  <si>
     <t>ペット用吸収性シート</t>
   </si>
   <si>
@@ -138,12 +117,6 @@
     <t>【課題】機能性材料の流出を抑制することができるペット用吸収性シートを提供する。 【解決手段】ペット用吸収性シート１０は、表面シート１２と、裏面シート１４と、表面シート１２と裏面シート１４との間に設けられた吸収体２０と、機能性材料４０と、表面シート１２側から裏面シート１４の方へ向かって凹む凹部５０と、を有する。機能性材料４０は、凹部５０の位置に設けられている。</t>
   </si>
   <si>
-    <t>A61F13/00,B32B5/00,B41M5/00,H01M50/00,B29C63/00,D21H27/00,B65D81/00,A61L15/00,B32B37/00,F24S70/00,G09F11/00,G03F1/00,B29C70/00,B31B50/00,B01D24/00,A47C7/00,D04H1/00,D06N3/00,B62D1/00,A61F5/00,E04B2/00,B29C63/00,A61F13/00,E04F13/00,H01M50/00,B29C70/00,B29C73/00,A61L15/00,A47C27/00,B65D81/00,F16K1/00,B65H75/00,F42D1/00,F16L55/00,B31B50/00,B23K37/00,G09F11/00,G21C7/00,A23L3/00,B65H59/00,A61F13/00,E04B2/00,B65B11/00,B32B3/00,B29C48/00,B65D5/00,F24S70/00,B65D75/00,A43B7/00,B62J1/00,B60V1/00,B65D81/00,B65B43/00,G09F11/00,B60R21/00,H01S3/00,G01B3/00,B41F13/00,B29C70/00,A47C7/00,A61F13/00,F24S70/00,B29C70/00,G02F1/00,B65D81/00,A61L15/00,H01S3/00,G01N21/00,F24S10/00,C09K8/00,D04H1/00,F01N1/00,F04B37/00,G03F1/00,D06B15/00,B23K26/00,B41M5/00,B32B5/00,B29C73/00,B68G11/00</t>
-  </si>
-  <si>
-    <t>A61F13/00,A61L15/00,B32B5/00,D21H27/00,B29C63/00,A61F13/00,A61L15/00,B29C63/00,B29C70/00,B65D81/00,A61F13/00,B32B3/00,F24S70/00,B65B11/00,B65D75/00,A61F13/00,A61L15/00,B29C70/00,F24S70/00,B65D81/00</t>
-  </si>
-  <si>
     <t>熱湯を注いで粘性を付与するための顆粒状組成物</t>
   </si>
   <si>
@@ -153,12 +126,6 @@
     <t>【課題】沸騰水ほどの高温の熱湯を使用せずとも、粘性を安定に発現することのできる、スープ、シチュー、又はソースなどを作るための組成物の提供。 【解決手段】未α化澱粉と、α化澱粉と、油脂と、澱粉分解物とを含む、熱湯を注いで粘性を付与するための顆粒状組成物。未α化澱粉含有量(A)及びα化澱粉含有量(B)の合計が５．０〜７０．０質量％であり、(A)：(B)の質量比が１：０．１〜６．０である、前記顆粒状組成物。未α化澱粉が、馬鈴薯澱粉及び／又はタピオカ澱粉を含み、α化澱粉が、α化ヒドロキシプロピル化リン酸架橋澱粉及び／又はα化リン酸架橋澱粉を含み、油脂の含有量が２５質量％以下であり、乳化剤を０．１質量％以上を含む、前記顆粒状組成物。</t>
   </si>
   <si>
-    <t>A23L7/00,A23P10/00,H01F1/00,C09K8/00,C08J9/00,H01M8/00,A61K9/00,G03C1/00,A61K47/00,C05G5/00,C23C10/00,B05D1/00,C06B45/00,A47J47/00,C04B103/00,B24D3/00,A23L11/00,D04H3/00,C08J5/00,C08J3/00,C01F7/00,B01F101/00,A23L7/00,C12C7/00,C08J3/00,A21D13/00,A23L29/00,D21H23/00,B29B7/00,A23C9/00,C08B30/00,A23P10/00,C10M169/00,B01F35/00,A21D8/00,C07C17/00,C08F2/00,A23K10/00,B01F23/00,G01N30/00,C08F2/00,A23P10/00,A61K9/00,C09K8/00,A23C9/00,A23G1/00,B02C4/00,B01F101/00,C08J3/00,B01J2/00,A23P20/00,C10M169/00,A23L7/00,C10N50/00,G05D11/00,C08K13/00,D06P1/00,D01F2/00,C03C25/00,G02F1/00,A23P10/00,A23L7/00,C08J9/00,B02C4/00,C08B30/00,B05D1/00,C07C51/00,C08K9/00,A23L29/00,D21H23/00,C09C3/00,D01F2/00,C01F7/00,B41M5/00,E01C19/00,C23C10/00,A23G9/00,C01F11/00,C08F2/00,D06P1/00</t>
-  </si>
-  <si>
-    <t>A23L7/00,A23P10/00,A23L7/00,A23L29/00,B01F101/00,C08J3/00,A21D13/00,A23P10/00,A23C9/00,B01F101/00,B01J2/00,C08J3/00,A23P10/00,A23L7/00,C08B30/00,A23L29/00,C08K9/00</t>
-  </si>
-  <si>
     <t>草刈機</t>
   </si>
   <si>
@@ -171,12 +138,6 @@
     <t>【課題】  草刈刃の回転の停止を迅速に行うことができる草刈機を提案する。   【解決手段】  草刈機１は、回転力を発生する原動機１１と、該原動機１１の回転力を受けて回転する駆動軸２３を保持するヘッド部１７と、を備える。駆動軸２３は、その回転により、草刈刃３が回転するように構成されている。草刈機１のヘッド部１７は、駆動軸２３の回転を停止可能に構成された回転抑制装置５を備える。</t>
   </si>
   <si>
-    <t>H02P3/00,D03D51/00,E05B67/00,B65B57/00,F41A17/00,B41J7/00,A24C5/00,E05D11/00,B60T8/00,A01D34/00,B27B17/00,B65G51/00,B41J33/00,G01D11/00,F16H48/00,H02P6/00,B23Q11/00,B26D7/00,G04B11/00,D02H13/00,A01D34/00,B61C9/00,B62M6/00,B64C27/00,F16H39/00,E05F15/00,E02F3/00,F02N15/00,F16D55/00,B64D35/00,B60K17/00,B23Q5/00,B01F35/00,A01K89/00,B62M1/00,F16D13/00,F16H3/00,F01C1/00,A63H31/00,F04C2/00,A01D34/00,A01B63/00,F16H61/00,H02K7/00,B66D1/00,B65H23/00,B64C25/00,D03D43/00,B01D21/00,B62M6/00,B62M9/00,H02P1/00,B23D17/00,B41J23/00,E05B81/00,H01H71/00,H01H33/00,D05B69/00,A01D63/00,B21B37/00,F41A17/00,B26B21/00,A01D75/00,A01D43/00,A01D34/00,B27B17/00,A01D7/00,D03D51/00,A01D57/00,A01D63/00,A01F29/00,A01B39/00,B66B29/00,F01B25/00,F01C20/00,B41F1/00,E02F3/00,F02K9/00,B23Q11/00,A01D31/00</t>
-  </si>
-  <si>
-    <t>A01D34/00,H02P3/00,D03D51/00,B60T8/00,F41A17/00,A01D34/00,F16D55/00,F16H39/00,B61C9/00,B64D35/00,A01D34/00,F16H61/00,H02K7/00,B62M6/00,A01B63/00,F41A17/00,A01D75/00,D03D51/00,A01D34/00,B26B21/00</t>
-  </si>
-  <si>
     <t>送液装置およびそれを用いた細胞培養装置</t>
   </si>
   <si>
@@ -189,24 +150,12 @@
     <t>【課題】新規な送液装置及びそれを用いた細胞培養装置の提供。 【解決手段】第１の液体を含む第１の容器１０２、第２の液体を含む第２の容器１１１、第１の液体及び第２の液体を入れる第３の容器１０８、第１の液体及び第２の液体を排出する第４の容器１２１、第３の液体を含む第５の容器１１７、第１の液体を送る第１の送液管１０５、第２の液体を送る第２の送液管１１２、第１の送液管中の第１の液体及び第２の送液管中の第２の液体を第３の容器に送る第３の送液管１０７、第３の送液管での送液を制御する為の第１の送液ポンプ１０６、第３の液体を第３の容器に送る為の第４の送液管１１６、第５の容器中の第３の液体を第４の送液管を通じて第３の容器に送る第５の送液管、第３の容器中の第１の液体を第４の送液管を通じて第４の容器に排出する第６の送液管１２２、第４の送液管での送液を制御する第２の送液ポンプ１１５、を備える、送液装置。</t>
   </si>
   <si>
-    <t>B01F25/00,F17D1/00,B67D7/00,A61M39/00,B05B9/00,B65G53/00,F24S10/00,H01M50/00,A61M5/00,F16L39/00,B60R21/00,B60T11/00,B65D21/00,F25B41/00,G21C13/00,F16L47/00,G21C19/00,F16H47/00,H01H29/00,F04B1/00,F16H61/00,A61M60/00,F15B9/00,F04D29/00,F17D1/00,F04B43/00,F04F5/00,B67D7/00,F01P5/00,A61M5/00,F04F1/00,F04D25/00,F04D13/00,B65G53/00,G01G13/00,F01M1/00,F16D48/00,B05B9/00,H01M50/00,G01N30/00,B01F33/00,B01F25/00,B01F23/00,B01J8/00,B29B7/00,B05C3/00,B28C5/00,B05B7/00,B01F35/00,G05D11/00,B01F29/00,G01N30/00,B05B9/00,F17D1/00,B67D7/00,B28C7/00,A47L1/00,B65B29/00,B01J38/00,B07B9/00,A61M60/00,A61M5/00,B01F25/00,A61M1/00,H01M50/00,C12M1/00,B01D24/00,F04F5/00,B60S1/00,B05B7/00,B01D33/00,B01F27/00,G01N27/00,B65G53/00,A61B5/00,F27D3/00,G01P3/00,G01R33/00,B05C7/00,C12N15/00,G21F5/00,B65D21/00,G11B15/00,B67D7/00,B01F31/00,B01F29/00,B60K15/00,G21C13/00,A61M5/00,B01F35/00,H01L23/00,B01F27/00,A23B4/00,B65D77/00,B01D24/00,B08B9/00,B01J8/00,B65D41/00,B65D5/00,G21C3/00</t>
-  </si>
-  <si>
-    <t>F17D1/00,A61M39/00,B01F25/00,F16L39/00,B67D7/00,A61M60/00,F04B43/00,F15B9/00,F04D29/00,F17D1/00,B01F33/00,B01F25/00,B01F23/00,G05D11/00,B01F35/00,C12M1/00,A61M5/00,A61M1/00,B01F25/00,A61M60/00,B65D21/00,B67D7/00,B01F29/00,B01F31/00,A61M5/00</t>
-  </si>
-  <si>
     <t>容器入り液状又はペースト状食品組成物、及びその製造方法</t>
   </si>
   <si>
     <t>【課題】水への分散性が特に優れた、容器入り液状又はペースト状食品組成物を提供する。 【解決手段】本発明は、α化していない澱粉、油脂及び水を含有する容器入り液状又はペースト状食品組成物であって、粒子径が５０μｍ以下の油滴を形成する油脂を２質量％以上含有することを特徴とする、容器入り液状又はペースト状食品組成物に関する。</t>
   </si>
   <si>
-    <t>C09K8/00,G03C1/00,A23L29/00,A23L33/00,A23P10/00,C04B103/00,B41M5/00,B01F23/00,D06P1/00,B02C4/00,A23G9/00,C09D11/00,E01C19/00,H01G11/00,A23L7/00,C12G3/00,A61L9/00,C08J3/00,C10M169/00,A61K8/00,A23L7/00,A23L29/00,D21H23/00,C12C7/00,A23C9/00,A23L33/00,C09K8/00,C11D3/00,G03C1/00,A23F5/00,C01F7/00,A23G9/00,A23P10/00,A23K10/00,C08K9/00,A21D8/00,C08B30/00,A21D13/00,C08G59/00,C08K13/00,B01F23/00,C09K8/00,B22F1/00,A23P10/00,G01N33/00,C08J3/00,B01J2/00,B01F25/00,E01C19/00,H01F1/00,B05B1/00,C08J9/00,B01F101/00,C08G63/00,C03C25/00,A23G1/00,A23L33/00,C02F1/00,B01J19/00,C08F2/00,B65B25/00,A23L3/00,B65B55/00,B65B1/00,B65B3/00,A23C3/00,B65D85/00,B65B29/00,B65D81/00,A23B7/00,B01F29/00,B65B39/00,B65D51/00,A23P20/00,B65D77/00,B65B5/00,A23G9/00,B65B43/00,B65B31/00,A23B4/00</t>
-  </si>
-  <si>
-    <t>A23L29/00,A23L33/00,A23P10/00,B01F23/00,B02C4/00,A23L7/00,A23L29/00,A23L33/00,A23C9/00,A23F5/00,B01F23/00,A23P10/00,C08J3/00,B01J2/00,B01F25/00,B65B25/00,A23L3/00,B65B55/00,B65B3/00,B65D85/00</t>
-  </si>
-  <si>
     <t>アルコール飲料添加用の花の製造方法、アルコール飲料の製造方法、及び容器入りアルコール飲料</t>
   </si>
   <si>
@@ -219,12 +168,6 @@
     <t>【課題】短時間でアルコール飲料添加用の花を製造する。 【解決手段】本発明のアルコール飲料添加用の花の製造方法は、アルコール水溶液、及び糖類を含有する処理液体に、生花を浸漬した状態で、減圧下にて加熱して、処理液体を生花に含浸させる。生花は、カロチノイド色素を含有する花、及び／又は白色の花であることが好ましい。減圧下にて加熱する処理液体の温度は、４０〜８３℃が好ましい。加熱時間は、２〜３０分間が好ましい。例えば、この製造方法によれば、数日でアルコール飲料添加用の花を製造することができ、従来の６ヶ月以上を要していた製造方法よりも非常に短時間で、有益である。</t>
   </si>
   <si>
-    <t>A23L2/00,C12G3/00,C09K8/00,H01J1/00,B01F101/00,A23K10/00,A23G1/00,C09D1/00,A47J31/00,A23F5/00,A23L29/00,A23F3/00,C12G1/00,H01J19/00,B22D41/00,C08K9/00,C07B63/00,A23L7/00,D21H17/00,D06M14/00,H01L21/00,B01J38/00,B09B3/00,C10G67/00,C23C22/00,A23L3/00,A47J31/00,B05C3/00,F26B3/00,B28B21/00,B29C70/00,C21D1/00,D06M23/00,A23B9/00,C03C25/00,H01C17/00,F28B3/00,C12C1/00,G21C19/00,C01F7/00,G03C7/00,C09K8/00,A23F3/00,C08K9/00,C12G3/00,C08J11/00,C23C22/00,B05C3/00,C12G1/00,C12C7/00,C10G53/00,B05C1/00,A23F5/00,B29C70/00,C12N1/00,D06M23/00,B01J38/00,C01F7/00,C03B18/00,D06B23/00,A23F3/00,C12G1/00,H01M4/00,C12G3/00,A23L2/00,C08J9/00,A23F5/00,C12F3/00,C10G53/00,C10G65/00,C12C7/00,C08G69/00,D21H23/00,B23F9/00,C01B17/00,C04B35/00,D06M23/00,C01F7/00,B09B3/00,C01B25/00</t>
-  </si>
-  <si>
-    <t>C12G3/00,A23L2/00,A47J31/00,B01F101/00,A23K10/00,A23L3/00,F26B3/00,B05C3/00,A47J31/00,C23C22/00,C12G3/00,A23F3/00,C12C7/00,C09K8/00,C08K9/00,C12G3/00,A23F3/00,C12G1/00,A23L2/00,C12F3/00</t>
-  </si>
-  <si>
     <t>ペット用食事管理システム</t>
   </si>
   <si>
@@ -237,12 +180,6 @@
     <t>【課題】   餌の重量の変化によってペットの個体別に食事量を記録し、前記個体に最適な食事量を算出するペット用食事管理システムを提供すること。 【解決手段】   ペットによって使用される食器に入っている食事の重量と、食器の動きと、を取得し、前記食器の動きのパターンに基づいて、前記食器を使用したペットの個体の特定を行い、食器内の餌の重量の変化に基づいて、前記個体判別手段によって特定された個体による食事量の記録を行う、ペット用食事管理システムを提供する。</t>
   </si>
   <si>
-    <t>G01G19/00,G01G23/00,G01G13/00,B07C5/00,B65B1/00,G01G1/00,G01G3/00,G01N9/00,G01G21/00,A01K39/00,G01G17/00,G01G11/00,G01G15/00,G07F15/00,G01N29/00,F02M69/00,G07D11/00,A01K97/00,G01N5/00,G01V7/00,G11B27/00,G11B15/00,B60T8/00,G06V10/00,B23Q35/00,G01V8/00,H04N19/00,H01H19/00,G01G19/00,E05B81/00,G06V20/00,A63F13/00,A47G19/00,G11B19/00,G01N29/00,G06F18/00,B26D5/00,G06F3/00,G01C19/00,B41J33/00,H04H60/00,G11B27/00,C40B20/00,G01P3/00,G01S13/00,G11B15/00,G06K21/00,A47G19/00,H04W12/00,A47G23/00,A61B5/00,G06T7/00,G01N27/00,G01L3/00,G08G1/00,G06V30/00,G06K7/00,G01V8/00,G01N29/00,G11B23/00,G06F119/00,G01G19/00,B07C5/00,G01G23/00,F01K7/00,A01K61/00,B65B3/00,A61B5/00,G01D9/00,G06Q10/00,G01G13/00,F01L31/00,A01M29/00,H04L67/00,H04N21/00,A63F13/00,A61M60/00,G01G1/00,D06F58/00,A23L33/00</t>
-  </si>
-  <si>
-    <t>G01G19/00,G01G13/00,G01G3/00,G01G23/00,A01K39/00,G06V10/00,G01G19/00,G01V8/00,G11B27/00,H01H19/00,C40B20/00,G01P3/00,A47G19/00,G06K21/00,A47G23/00,G06F119/00,G01G19/00,G01D9/00,A61B5/00,G06Q10/00</t>
-  </si>
-  <si>
     <t>コンバイン</t>
   </si>
   <si>
@@ -252,12 +189,6 @@
     <t>【課題】ロードセルを用いてグレンタンク重量を検出する際に、グレンタンクの重量が安定的に作用するようにして穀物重量の検出精度が低減することを回避できるようにする。 【解決手段】機体フレーム上に搭載される穀物貯留用のグレンタンク５と、グレンタンク５が載置されて、グレンタンク５に貯留された穀粒の重量を計測するロードセル６０と、ロードセル６０を載置支持する載置支持部と、が備えられたコンバイン。</t>
   </si>
   <si>
-    <t>B60K15/00,B64D37/00,F02K1/00,G21C3/00,C12C1/00,A01F12/00,G07F11/00,C10J3/00,D21D5/00,G11B23/00,B63J2/00,B62D33/00,B65D25/00,G21F5/00,B63B25/00,F24B1/00,B63B43/00,F22B9/00,G03D13/00,G21C19/00,G01G19/00,G01G13/00,G01G23/00,B07C5/00,G01G3/00,B65B1/00,B65G67/00,G01G1/00,G01G11/00,B62B1/00,G01G17/00,C12C1/00,A01F12/00,G01G15/00,F41A9/00,G21C19/00,B65G69/00,B65G65/00,G07D11/00,G01V7/00,B60P1/00,B65H39/00,B62B1/00,F16M11/00,B65G17/00,B41F13/00,E21D15/00,G11B3/00,G09B1/00,G21C3/00,G11B5/00,B63B27/00,B61F5/00,B65D19/00,G11B15/00,E02F9/00,H05K7/00,F16D65/00,A47C1/00,E04B1/00,G01G19/00,G01G13/00,G01G23/00,B07C5/00,G01G1/00,G01G3/00,A01F12/00,G01G11/00,B65B1/00,G01G21/00,C12C1/00,G01G15/00,G01F1/00,B63B25/00,G01P3/00,B63B43/00,F16D43/00,G01M1/00,A01D41/00,B66F9/00</t>
-  </si>
-  <si>
-    <t>B60K15/00,A01F12/00,B64D37/00,C12C1/00,G21C3/00,G01G19/00,G01G13/00,G01G23/00,G01G3/00,B07C5/00,F16M11/00,B60P1/00,E21D15/00,B62B1/00,B65G17/00,G01G19/00,G01G13/00,G01G23/00,G01G3/00,A01F12/00</t>
-  </si>
-  <si>
     <t>クランプユニット及びこれを備える透析装置</t>
   </si>
   <si>
@@ -267,12 +198,6 @@
     <t>【課題】チューブの閉塞を判定するために、チューブを安定して保持できるクランプユニット及びこれを備える透析装置を提供すること。 【解決手段】クランプユニット６０は、ユニット本体６１と、ユニット本体６１を開閉する蓋部６２と、を備え、蓋部６２の閉鎖時に、ユニット本体６１と蓋部６２との間に配置される液体が流通するチューブをクランプするクランプ部６５と、チューブが配置されるチューブ配置部６１１，６２１においてクランプ部６５に並んで配置され、チューブからの圧力による荷重を検出する荷重検出部６６と、を備える。</t>
   </si>
   <si>
-    <t>E04G7/00,B65D5/00,G01C19/00,F16L37/00,F16D1/00,F16L3/00,A45D2/00,A61B17/00,B65D43/00,B65D35/00,B27G13/00,A45D6/00,A44B11/00,A61F2/00,B21D26/00,B65H29/00,F16D13/00,B23Q1/00,H01R33/00,B42F13/00,G01F1/00,F16L55/00,E21B47/00,F16D55/00,B67D7/00,G01P5/00,G01D5/00,B65G51/00,B65D75/00,B65G53/00,F16L37/00,B60R21/00,F15B21/00,H01M8/00,E03C1/00,G05D11/00,F25B41/00,F01D11/00,F16T1/00,G01N21/00,G01L5/00,G01G19/00,G01F1/00,G01G3/00,F16F1/00,A61M60/00,G01L13/00,E21D15/00,E21B47/00,B21B38/00,G01L23/00,G01G11/00,G01N11/00,F16C19/00,F16B31/00,G01L21/00,G01G23/00,B21B19/00,H01J41/00,G11B15/00,A61M60/00,B01D35/00,G01C19/00,A61F2/00,F16L55/00,G01F1/00,A61B50/00,F41A9/00,B01D33/00,B01D25/00,F02B13/00,D01H7/00,B65D55/00,D05C15/00,A23G3/00,B41J13/00,B01D29/00,F23K3/00,F02M37/00,D06F29/00</t>
-  </si>
-  <si>
-    <t>F16L3/00,A61B17/00,F16L37/00,B65D35/00,B65D43/00,G01F1/00,F16L55/00,G01P5/00,G01D5/00,B65G51/00,G01L5/00,G01G19/00,G01F1/00,G01G3/00,G01L13/00,A61M60/00,A61F2/00,A61B50/00,F16L55/00,G01F1/00</t>
-  </si>
-  <si>
     <t>遊技機</t>
   </si>
   <si>
@@ -285,30 +210,12 @@
     <t>【課題】演出に関する設定について改良した遊技機を提供することを目的とする。 【解決手段】この遊技機は、メニュー状態を経由して制御された音量設定状態は、時間の経過で終了するため、いつまでも音量設定画像が液晶表示器５１に表示され続けることを防止することができ、さらに、遊技状態から直接的に制御された音量設定状態も、時間の経過で終了するため、いつまでも音量設定画像が液晶表示器５１に表示され続けることを防止することができる。</t>
   </si>
   <si>
-    <t>A63F13/00,B61G1/00,G05B19/00,B01D61/00,B60K35/00,B60W50/00,G06F3/00,H03G9/00,D06F33/00,B61L3/00,H05G1/00,H02M7/00,H04M1/00,B64D25/00,B64G1/00,G11B19/00,B23Q15/00,B23B39/00,H04N23/00,D06F34/00,F16H61/00,B01D61/00,A63F13/00,H03G3/00,H03G9/00,F04D29/00,F41A25/00,F41A23/00,H02M7/00,H04M1/00,G10H1/00,F01N3/00,G05F1/00,H03J7/00,B60T8/00,G11B3/00,F41A21/00,G03B7/00,H03G1/00,G10L21/00,G04C23/00,H03J7/00,H01H43/00,A63F13/00,D06F33/00,G09F11/00,G06F1/00,G01S3/00,B67D7/00,H03G3/00,B61G1/00,F23N5/00,G03B7/00,H04M15/00,H02P8/00,G11B19/00,F02M7/00,H04W24/00,B66D1/00,H02H3/00,A63F13/00,H01J31/00,G09G5/00,H04N1/00,B60K35/00,H04N25/00,H04N13/00,G01S7/00,H04N23/00,G03G15/00,G09G3/00,H10K59/00,G06F3/00,G04G9/00,G08G1/00,F41J5/00,G09G1/00,H04N9/00,G06V30/00,G11B7/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G05B19/00,G06F3/00,H03G9/00,B60K35/00,A63F13/00,H03G3/00,H03G9/00,H04M1/00,H02M7/00,G04C23/00,H01H43/00,A63F13/00,G06F1/00,G09F11/00,A63F13/00,G09G5/00,H01J31/00,H04N13/00,H04N1/00</t>
-  </si>
-  <si>
     <t>【課題】電気部品が意図せずに動作してしまうことを防止できる遊技機を提供すること。 【解決手段】シリアル／パラレル変換回路１には、該変換回路を動作させるための電源Ｖ ＣＣが接続されるとともに、該電源ＶＣＣは、シリアル制御信号１及びクロック信号１の 信号線のノイズを除去するためのノイズ除去回路１及びパラレル制御信号１、２の信号線 の電圧をプルアップさせるプルアップ抵抗１に接続されており、電源ＶＣＣは、２本の電 源線（ＶＣＣ１及びＶＣＣ２）を介して供給される。</t>
   </si>
   <si>
-    <t>H03M1/00,H04N5/00,A63F13/00,G06F7/00,H04N25/00,H04N9/00,H04L25/00,H03F3/00,G01R31/00,H04L27/00,H04Q1/00,H04B1/00,H03K17/00,H04N1/00,G06F3/00,G11C16/00,H02M1/00,G11C11/00,H04N11/00,A01B3/00,H04N9/00,H03K17/00,H04N5/00,H04N25/00,H04B1/00,G11C16/00,H04M1/00,H04B3/00,H04N1/00,H04N23/00,G08B29/00,G11C11/00,H04L27/00,H02M1/00,H05B41/00,A63F13/00,H02J3/00,G10L21/00,H01F27/00,H03K21/00,G05F1/00,H03K17/00,G11C11/00,G05B19/00,G01R31/00,G09F11/00,F16H61/00,H01R12/00,H03K3/00,H04N5/00,H05B45/00,H02M7/00,H05B41/00,H04N25/00,G08B29/00,G01F1/00,F02D41/00,H02M1/00,H03K21/00,G11C16/00,H02J3/00,H03K17/00,B60L9/00,G05F1/00,H02P27/00,H02M1/00,B60L1/00,H04Q3/00,G01R31/00,H02J1/00,H02J9/00,H01Q5/00,G06F1/00,H04N25/00,A63F13/00,H05C1/00,H02M3/00,G06G7/00,G06F9/00,G04G19/00,H03K17/00,F16H61/00,G06F21/00,G05G5/00,B60W50/00,H05B41/00,H02H5/00,H05B47/00,H01R13/00,H04M3/00,D01H13/00,H02M1/00,B60D1/00,F41A17/00,F16F15/00,G01R11/00,B60L15/00,F16P7/00,G05D1/00,H01H71/00</t>
-  </si>
-  <si>
-    <t>G06F7/00,H03M1/00,H04L25/00,A63F13/00,G01R31/00,H03K17/00,H04B1/00,H04B3/00,H04N9/00,H04N5/00,H03K17/00,H03K3/00,G05F1/00,H01R12/00,G05B19/00,H02J3/00,H02J1/00,H03K17/00,G05F1/00,H02M1/00,H03K17/00,H02H5/00,G05G5/00,H01R13/00,G06F21/00</t>
-  </si>
-  <si>
     <t>【課題】従来とは異なる態様で遊技状態を移行させることで、遊技の幅を広げることができる遊技機を提供する。 【解決手段】遊技区間は、ＡＲＴを実行可能な有利区間と、ＡＲＴを実行できない通常区間と、を含み、ＡＲＴ制御手段は、ＡＲＴの実行権利を得たときに、非ＡＲＴ中であればＡＲＴを開始し、ＡＲＴ中であれば当該実行権利をストックするように構成されている。また、有利区間の終了後に移行する遊技状態には、実行権利のストック数が関連付けられている。</t>
   </si>
   <si>
-    <t>A63F13/00,G05B19/00,G05D1/00,B60T8/00,H02P1/00,H02M7/00,G21C7/00,B60W10/00,B61L27/00,B60W20/00,H04Q3/00,F21V29/00,B60L1/00,E05B81/00,G05D13/00,H03J7/00,H02M5/00,F01D11/00,C01B3/00,H02P7/00,G05D1/00,H04N21/00,G09F11/00,G05B19/00,A63F13/00,B60L15/00,F15B9/00,E05B81/00,G11B15/00,B60W30/00,G11B19/00,B60W50/00,B61G1/00,G04C23/00,G11B3/00,H03K17/00,G01G19/00,H04N5/00,B27F7/00,F42B19/00,H04N21/00,G06F21/00,H04H60/00,F15B9/00,H04L47/00,H04W16/00,G06F13/00,G06Q10/00,G07D11/00,G11B11/00,E04B2/00,F24F120/00,G06V10/00,H04N1/00,H04N19/00,H04L41/00,G01G19/00,G06F9/00,G01R22/00,B23B31/00,A63F13/00,H04N19/00,A63F7/00,C03B9/00,H04N25/00,G06V10/00,G06V30/00,H04N21/00,A63F9/00,H04W72/00,G10L21/00,H04H20/00,G06T7/00,B05B12/00,H01L21/00,G06F21/00,H03M13/00,A61F13/00,H04L67/00,B60Q3/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G05B19/00,A63F13/00,G05B19/00,G09F11/00,H04N21/00,G05D1/00,G06Q10/00,G06F13/00,G06F21/00,G07D11/00,H04N21/00,A63F13/00,A63F7/00,A63F9/00,H04N19/00,H04N21/00</t>
-  </si>
-  <si>
     <t>ゲームシステム</t>
   </si>
   <si>
@@ -321,12 +228,6 @@
     <t>【課題】予約しているプレイヤを、待ち時間に、他のゲーム機でプレイするように促すゲームシステムを提供する。 【解決手段】ゲームシステム１、店舗内に配置されたゲーム機１０，ゲーム機２０と、ゲーム機１０のプレイ中において、次回以降のゲーム機１０のプレイの予約を予約ＩＤによって識別可能に受け付ける予約管理部４６ａとを備え、予約管理部４６ａは、ゲーム機１０でプレイが終了したことに応じてゲーム機２０でのプレイを中断し、予約ＩＤの入力に応じて、予約されたプレイをゲーム機１０で実行可能にし、予約ＩＤの入力に応じて、中断されたプレイをゲーム機２０で再開可能にする。</t>
   </si>
   <si>
-    <t>A63F13/00,H04M1/00,H04N21/00,C03B9/00,H04L41/00,G05B19/00,H04L47/00,G06Q10/00,H04L67/00,H04W92/00,G06Q20/00,B60T11/00,G11B17/00,B23B31/00,H04W12/00,A63F7/00,B61G1/00,H01S3/00,H04H20/00,H04H60/00,A63F13/00,H04H20/00,H04L67/00,H02P5/00,H01R13/00,H04Q3/00,H04M1/00,H04W88/00,G06F15/00,H04H60/00,G01F1/00,H01H31/00,H03H7/00,H03H9/00,H01H33/00,H04B1/00,G05B11/00,H10K59/00,F15B11/00,H02M7/00,A63F13/00,G08B5/00,G05D1/00,D03D51/00,H04L67/00,H02P8/00,G11B11/00,G06F13/00,H01H43/00,H04W36/00,E06B9/00,H01H71/00,H01H73/00,H04N21/00,G06F1/00,H04L41/00,H03K17/00,B66B1/00,H04N1/00,H01M8/00,A63F13/00,H04L67/00,H04M3/00,H04L65/00,H04N21/00,H04W68/00,G06F13/00,H04M1/00,H04L51/00,H04L41/00,G08G1/00,H04L47/00,H04W4/00,A63F7/00,H04H60/00,H04L45/00,G07F17/00,B64U70/00,G01S19/00,G09G5/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G06Q10/00,H04N21/00,G05B19/00,H04L41/00,A63F13/00,H04L67/00,G06F15/00,H04W88/00,H04Q3/00,A63F13/00,G11B11/00,G06F13/00,H04L67/00,H04W36/00,A63F13/00,H04W68/00,H04L67/00,H04L65/00,H04N21/00</t>
-  </si>
-  <si>
     <t>洗濯物干し具</t>
   </si>
   <si>
@@ -336,21 +237,9 @@
     <t>【課題】  多くの衣服ハンガーを識別性良く吊り下げることができ、且つ、吊り下げられた衣服ハンガーの下端部が地面に接触し難い洗濯物干し具を提供する。 【解決手段】  本発明の洗濯物干し具１０は、物干し竿３に吊り下げ可能な吊り部１３をそれぞれ有する一対の本体部材１と、前記一対の本体部材１に架設された第１架橋桿２１と、前記一対の本体部材１に架設され且つ前記第１架橋桿２１から間隔を空けて配置された第２架橋桿２２と、を有し、前記吊り部１３が、前記第１架橋桿２１と前記第２架橋桿２２の間に配設されており、前記吊り部１３を前記物干し竿３に吊り下げた際、前記第１架橋桿２１が前記第２架橋桿２２よりも上方に位置するように構成されている。</t>
   </si>
   <si>
-    <t>A47G25/00,D06F58/00,A47H1/00,D06F33/00,A47K10/00,E04G1/00,D06F5/00,D06F53/00,A41D27/00,B42F15/00,E04H17/00,E02D7/00,A41F11/00,B66C1/00,E21D15/00,B65H75/00,A47F7/00,B65D63/00,F16L3/00,D06F1/00,A47G25/00,F16L37/00,A45C13/00,A47F7/00,B66C1/00,B65H3/00,E01F9/00,A41F11/00,D06F71/00,B41L3/00,B65B67/00,B65B13/00,D06F33/00,H01R4/00,B65D77/00,D01H13/00,A63C10/00,A47B88/00,H01R33/00,D01G15/00,A47G25/00,H01R13/00,A41F11/00,D06F33/00,A61F13/00,A41F3/00,H02B1/00,B65D25/00,A45F5/00,D05B27/00,A41F17/00,E05C17/00,G07F11/00,H01R33/00,E04G3/00,A41H9/00,F24S25/00,H01R4/00,A43B21/00,A47F7/00,E06C1/00,E04G1/00,E01D15/00,H02M7/00,E04B2/00,C07C13/00,F16H15/00,B64C9/00,E01D19/00,F24S25/00,F04B1/00,F04F5/00,H04L5/00,B65G21/00,E04G17/00,F16S3/00,E05C17/00,A61K31/00,E01B11/00,F16D3/00</t>
-  </si>
-  <si>
-    <t>A47G25/00,D06F53/00,D06F58/00,D06F5/00,A47H1/00,A47G25/00,A47F7/00,A41F11/00,D06F71/00,B65H3/00,A47G25/00,A41F11/00,A41F3/00,D06F33/00,A45F5/00,E06C1/00,E04G1/00,E01D15/00,E01D19/00,E04B2/00</t>
-  </si>
-  <si>
     <t>【課題】演出を好適に行うことが可能な遊技機を提供すること。 【解決手段】スロットマシン１０は、スピーカ装置６４による音演出が、各音源ＩＣによる音生成処理によって生成される音により行われる。各音源ＩＣにおいて、音生成処理は１０ｍｓｅｃ周期で更新され、所定の音情報に基づいて音の生成を行う。サブ制御装置は、音生成処理の更新周期と音演出を開始させるべき開始タイミングとのズレが生じている場合、当該ズレに相当する期間に亘って遊技者が把握困難又は把握不可となる音の生成が行われるように、音生成処理に用いられる音情報を設定する。</t>
   </si>
   <si>
-    <t>A63F13/00,G10H1/00,B60K35/00,H03G9/00,G10L13/00,H03K17/00,G05B19/00,H02M7/00,H03G3/00,H04H60/00,H01S3/00,B64G1/00,B23H7/00,G10K11/00,B61G1/00,G11B19/00,G10L25/00,H02M5/00,G04C21/00,G05F1/00,H03J7/00,H03L7/00,G10H1/00,A63F13/00,H04N9/00,H04N5/00,H04N21/00,H03G9/00,G10L13/00,G01S7/00,H04M1/00,H02M7/00,G10L19/00,H01S3/00,G01S13/00,G04C23/00,H03G3/00,H03K5/00,H01H43/00,H04N13/00,H04N5/00,G10H1/00,H04N23/00,H04N21/00,G04C21/00,A63F13/00,G10L21/00,H03L7/00,G01R11/00,G04C23/00,H04N9/00,H03B5/00,G01K7/00,H04L47/00,H03M1/00,H03K5/00,H03D3/00,F16H1/00,G01C19/00,G01V1/00,A63F13/00,G10H1/00,H03G9/00,B60K35/00,H04N1/00,H01S3/00,H04N23/00,H03G3/00,G10L21/00,H04N5/00,G05B11/00,H03K3/00,B60W50/00,G10K11/00,G10K15/00,G21C7/00,H04N25/00,H03M1/00,G01F1/00,H03G1/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G10H1/00,H03G9/00,G10L13/00,H03G3/00,H03L7/00,H03J7/00,G10H1/00,H03G9/00,A63F13/00,G10H1/00,G10L21/00,A63F13/00,H03L7/00,G04C21/00,A63F13/00,G10H1/00,H03G9/00,G10L21/00,H03G3/00</t>
-  </si>
-  <si>
     <t>医療用撮像装置</t>
   </si>
   <si>
@@ -363,21 +252,9 @@
     <t>【課題】小型化及び軽量化を図りつつ、利便性の向上を図ることが可能な撮像装置を提供する。 【解決手段】医療用撮像装置５は、外装を構成するケーシング１１と、ケーシング１１内に収納され、被写体像を撮像する撮像部２１と、ケーシング１１の外面に回転可能に設けられた操作リング１４と、操作リング１４の回転を検知する検知部１７と、検知部１７の検知結果に基づいて、操作リング１４の回転方向及び回転量を算出する操作算出部２３２と、操作算出部２３２にて算出された操作リング１４の回転方向及び回転量に応じた第１の機能または第２の機能を実行する機能実行部２３３と、機能実行部２３３にて実行させる機能を第１の機能または第２の機能に切り替える機能切替部２３１とを備える。</t>
   </si>
   <si>
-    <t>A61B6/00,H04N23/00,H05G1/00,A61M60/00,F01D25/00,H01H85/00,G03B17/00,H05K7/00,H01R13/00,A61B50/00,H04N5/00,H02K5/00,G16H30/00,D05B73/00,F16J15/00,G12B9/00,G03C5/00,B64C1/00,B64U20/00,H05K5/00,H04N23/00,G03B17/00,H04N1/00,H04N13/00,G02B9/00,G03G15/00,H04N5/00,G03C8/00,G03B27/00,G11B7/00,G03B15/00,B41B15/00,H04N25/00,G02B27/00,G01C11/00,G02F1/00,G03B19/00,H05G1/00,G03B7/00,G03B35/00,E05F15/00,H01H19/00,B43K24/00,H01H73/00,F16D1/00,H01H3/00,E05F11/00,F16L37/00,D01H7/00,E05D15/00,B65H51/00,G08B5/00,B65D41/00,H01H31/00,F41A3/00,H01H13/00,G05G1/00,E04H6/00,B24B39/00,A63H1/00,G01C19/00,H02P21/00,H01H19/00,F16H21/00,G01S3/00,B41J33/00,B28B1/00,B01F27/00,G05G1/00,G01S1/00,B65H49/00,H02K11/00,H02P8/00,G01L3/00,B65H51/00,D06F49/00,H02P23/00,H03J5/00,D05B27/00,A46B7/00,E05F15/00,H01H41/00,G04C23/00,H02M7/00,H01H19/00,B43K24/00,F16L37/00,H01H73/00,H01H3/00,H01H13/00,D01H7/00,G06F3/00,B41J33/00,B28B1/00,H01H81/00,E04H6/00,F01L9/00,H02P21/00,H02M1/00,A63H1/00</t>
-  </si>
-  <si>
-    <t>A61B6/00,H04N23/00,G03B17/00,H05K7/00,A61B50/00,H04N23/00,G03B17/00,H04N5/00,G02B9/00,H04N13/00,H01H19/00,H01H3/00,F16D1/00,E05F15/00,B43K24/00,G01C19/00,H01H19/00,G05G1/00,G01S3/00,H02P21/00,H01H41/00,H01H19/00,H01H3/00,H01H13/00,E05F15/00</t>
-  </si>
-  <si>
     <t>【課題】技量に自信を持っている遊技者にとっても興趣に富んだ遊技機を提供すること。 【解決手段】第１の役が内部当籤役として決定された場合において特定の図柄表示手段に対する停止操作が第１のタイミングで行われた場合、特定の図柄表示手段において複数の図柄が第１の態様で停止表示され、その後第１の図柄組合せを停止表示させることができる。第２の役が内部当籤役として決定された場合において当該停止操作が第１のタイミングで行われた場合、特定の図柄表示手段において複数の図柄が第２の態様で停止表示され、その後第２の図柄組合せを停止表示させることができる。第３の役が内部当籤役として決定された場合において当該停止操作が第２のタイミングで行われた場合、特定の図柄表示手段において複数の図柄が第１の態様で停止表示され、その後第１の図柄組合せを停止表示させることができる。</t>
   </si>
   <si>
-    <t>G05B19/00,G09G5/00,A63F13/00,B60K35/00,A63F7/00,G06F3/00,H03K17/00,G05G5/00,D06F34/00,G11B15/00,G05B11/00,F24F11/00,G09G1/00,G06M1/00,B23B31/00,G01S7/00,D05B19/00,H02P8/00,H04N25/00,G07D7/00,A63F13/00,H01H43/00,D03D51/00,G04C23/00,H02P8/00,H04M1/00,A63F7/00,D06F105/00,B65B57/00,H01H7/00,H03K17/00,B41J21/00,B62M6/00,G01S7/00,G04F8/00,F41A3/00,G06F1/00,D05B69/00,G04F7/00,F02D11/00,A63F7/00,A63F13/00,G01S3/00,A63F9/00,C03B9/00,H03K17/00,F41J5/00,G11B19/00,D06F13/00,A63F3/00,B62M6/00,B30B11/00,G06C9/00,G05B19/00,F16H61/00,B65H19/00,B65H23/00,G07G1/00,B21D19/00,G06F9/00,A63F13/00,A63F7/00,H02M3/00,G05B19/00,F15B9/00,E05B81/00,H01S3/00,F24H15/00,B60T8/00,H03G3/00,B23Q15/00,F24F11/00,B60W30/00,B60W10/00,H02M7/00,B61G1/00,B23B39/00,B60G17/00,H04H60/00,H02M5/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G09G5/00,G05B19/00,A63F7/00,G06F3/00,A63F13/00,A63F7/00,H01H43/00,G04C23/00,H01H7/00,A63F7/00,A63F13/00,A63F9/00,A63F3/00,F41J5/00,A63F13/00,A63F7/00,G05B19/00,F15B9/00,H03G3/00</t>
-  </si>
-  <si>
     <t>パンツタイプ使い捨ておむつ</t>
   </si>
   <si>
@@ -387,12 +264,6 @@
     <t>【課題】臀部カバー部の角が目立つ等により外観が悪化するのを防止する。 【解決手段】上記課題は、後側外装体１２Ｂにおける臀部カバー部Ｃには、幅方向ＷＤに沿う細長状のカバー部弾性部材１６ａ〜１６ｃが前後方向ＬＤに間隔を空けて３本以上設けられており、臀部カバー部Ｃはカバー部弾性部材１６ａ〜１６ｃにより幅方向中央側に収縮しており、最もウエスト開口ＷＯ側に位置するカバー部弾性部材１６ａは、臀部カバー部Ｃにおけるウエスト開口ＷＯ側の端部に配置されるとともに、最も脚開口ＬＯ側に位置するカバー部弾性部材１６ｃは、臀部カバー部Ｃにおける脚開口ＬＯ側の端部に配置されており、最もウエスト開口ＷＯ側に位置するカバー部弾性部材１６ａとウエスト開口ＷＯ側から数えて２本目のカバー部弾性部材１６ｂとの中心間隔をｄとし、臀部カバー部Ｃの前後方向長さをｄとしたとき、ｄ＞０．５ｄであることにより解決される。</t>
   </si>
   <si>
-    <t>A61F13/00,B65D5/00,A47C17/00,B60R21/00,A47C7/00,B65H75/00,B65D88/00,A47K13/00,B64C1/00,B62J6/00,G04C23/00,F16K3/00,B29C63/00,B64C9/00,A01B63/00,E04F13/00,B61F1/00,G01B3/00,B62J13/00,B64C3/00,A47C7/00,F16D3/00,B60R21/00,A47C23/00,F16F15/00,H01R13/00,B62J1/00,B60G15/00,F16F1/00,F16C1/00,B64C25/00,B60N2/00,F41A3/00,B60G3/00,B62D1/00,E04F13/00,B65D81/00,B66F3/00,B65D88/00,H01H1/00,B60R21/00,B65D41/00,A47K13/00,F16L33/00,F16D65/00,B60R22/00,E04G7/00,F16L55/00,A61F13/00,F16K3/00,F41A3/00,E05F15/00,A47C1/00,F16L37/00,B65D5/00,B41J19/00,B62M9/00,B28B21/00,B65D90/00,E21B1/00,B65D5/00,B65D17/00,B65B43/00,G03B9/00,A47B57/00,E06B3/00,H01R13/00,A61F13/00,B65D88/00,H02B1/00,D03D47/00,B65D50/00,B65D41/00,H01M50/00,B65D51/00,B65D39/00,B60R21/00,E06B1/00,B65D71/00,B21D26/00</t>
-  </si>
-  <si>
-    <t>A61F13/00,A47C17/00,A47C7/00,A47K13/00,B65D5/00,A47C7/00,A47C23/00,B62J1/00,F16F1/00,B60G15/00,A61F13/00,B65D41/00,A47K13/00,F16L33/00,B60R21/00,A61F13/00,B65D17/00,B65B43/00,E06B3/00,B65D5/00</t>
-  </si>
-  <si>
     <t>靴</t>
   </si>
   <si>
@@ -402,12 +273,6 @@
     <t>【課題】オーバーシューズの持参の忘れを抑制しつつ、よりスムーズにオーバーシューズを着脱できるようにした靴を提供する。 【解決手段】靴本体と、オーバーシューズユニットと、を備えた靴が提供される。前記靴本体は、人体の足に装着可能である。前記オーバーシューズユニットは、前記靴本体の外面に取り付けられる。前記オーバーシューズユニットは、収納空間を有する収納部と、前記収納空間内において前記収納部に取り付けられたオーバーシューズと、を有する。前記収納部は、前記オーバーシューズを前記収納空間内に収納可能であるとともに、前記オーバーシューズを前記収納空間に出し入れするための開口部を有する。前記オーバーシューズは、前記収納空間から取り出した状態において、前記靴本体の底部を覆うように前記靴本体に取り付け可能である。</t>
   </si>
   <si>
-    <t>A43B7/00,A43D3/00,A63C10/00,A63C11/00,A43D100/00,A43D11/00,A43B13/00,A43D25/00,F41A3/00,H02K5/00,A43B9/00,B64C25/00,A43D1/00,B62D43/00,F24F1/00,A47G25/00,A47L23/00,B64D27/00,D01H7/00,F41A15/00,A63C9/00,A43D25/00,A43B7/00,A43D11/00,A43D3/00,A43D100/00,A63C1/00,A43D1/00,A47L23/00,A63C11/00,A47G25/00,A63C10/00,A43D21/00,A43B13/00,A43D95/00,B63B19/00,B60R22/00,G05G1/00,H01M50/00,A43B9/00,A43B7/00,A43D3/00,A63C10/00,A63C1/00,A43D1/00,A43B9/00,B65D21/00,A47L23/00,A43B3/00,B65D75/00,B62B3/00,A43D11/00,A43D100/00,A43B13/00,B65B19/00,A41B11/00,B65D77/00,A63C11/00,A43D25/00,A47G25/00,A43B7/00,A43D3/00,A43B9/00,A47L23/00,A43B3/00,A41B11/00,A63C10/00,A43D21/00,A63C9/00,A43D1/00,A63C11/00,A43D100/00,B60R22/00,A43D11/00,A63C1/00,A61F5/00,A43D25/00,A43B17/00,A61F13/00,D03D45/00</t>
-  </si>
-  <si>
-    <t>A43B7/00,A43D11/00,A43D100/00,A43B13/00,A43D3/00,A43D11/00,A43B7/00,A43D100/00,A43D25/00,A47L23/00,A43B7/00,A43B9/00,A43B3/00,B65D21/00,B65D75/00,A43B7/00,A43B3/00,A43B9/00,A43D3/00,A47L23/00</t>
-  </si>
-  <si>
     <t>吸込口体および電気掃除機</t>
   </si>
   <si>
@@ -420,12 +285,6 @@
     <t>【課題】ケース体の側部から塵埃を吸込口へと効果的に吸い込むことができる床ブラシおよびこれを備えた電気掃除機を提供する。 【解決手段】床ブラシ30は、ケース体35と、３つ以上の接地部40と、真空度保持体41と、回転ブラシ37とを有する。ケース体35は、床面に対向する下部に吸込口51を備える。接地部40は、ケース体35を床面に対して支持する。真空度保持体41は、ケース体35の吸込口51の後部に沿って配置され床面側に突出する。回転ブラシ37は、床面と接触可能な清掃部材65を備え、吸込口51に回転可能に配置される。ケース体35の下部は、吸込口51の側部の位置が接地部40の少なくともいずれかの周囲と略面一に形成されている。</t>
   </si>
   <si>
-    <t>A47L5/00,A47L11/00,H01R39/00,A61C17/00,B01D33/00,A47L13/00,B08B9/00,A47L9/00,H02M7/00,H01M50/00,B08B1/00,B65B35/00,B04C5/00,H05K7/00,H02B1/00,G11B5/00,B64C25/00,F02M69/00,A24F40/00,A45D24/00,E04B5/00,A47C4/00,H01R13/00,A47L11/00,H01R39/00,A61C13/00,F24S25/00,F21Y107/00,A43B7/00,A47C17/00,E04F13/00,B65H3/00,H02B1/00,E04F15/00,H01H9/00,A47L23/00,A47C1/00,A46B17/00,B60B15/00,B01J8/00,A47L5/00,B65D35/00,H01M50/00,H01J5/00,B65B43/00,B65D43/00,B65H3/00,E04H17/00,B65H29/00,A61C17/00,H01R33/00,B65D75/00,F16L59/00,B65H5/00,F02M69/00,H01J19/00,E05C17/00,F16J15/00,B67B7/00,F04B37/00,A47L5/00,A47L11/00,B08B9/00,H01R39/00,B01D33/00,B08B1/00,B01D46/00,A47L9/00,H02M7/00,B65H39/00,B01F27/00,B26F1/00,A01G20/00,A47L15/00,A63B21/00,B05B15/00,B43K24/00,A47L13/00,C14B1/00,B01D29/00,A47L5/00,B01D46/00,F02M35/00,B04C5/00,F02B25/00,A61C17/00,A47L9/00,F02M26/00,D01G15/00,A47L11/00,E21B21/00,B65B1/00,B01D33/00,F26B13/00,A45D24/00,F01N3/00,F23J3/00,B65H3/00,F02M69/00,F24F1/00</t>
-  </si>
-  <si>
-    <t>A47L5/00,A47L9/00,A47L13/00,A47L11/00,B01D33/00,A47L11/00,F24S25/00,E04B5/00,A43B7/00,A47C17/00,A47L5/00,B65D35/00,B65D43/00,A61C17/00,B65B43/00,A47L5/00,A47L9/00,A47L11/00,B08B1/00,B08B9/00,A47L5/00,A47L9/00,A47L11/00,B01D46/00,B04C5/00</t>
-  </si>
-  <si>
     <t>アンギオＣＴ装置</t>
   </si>
   <si>
@@ -438,12 +297,6 @@
     <t>【課題】  アンギオ装置とＣＴ装置とを交替させるためのセット時間及び退避時間を減少させる。 【解決手段】  実施形態に係るアンギオＣＴ装置は、寝台装置、ＣＴガントリ、アンギオガントリ、第１セット手段及び撮像制御手段を具備する。前記寝台装置は、被検体が載置される天板を有する。前記ＣＴガントリは、前記天板が挿入される開口部を有する。前記アンギオガントリは、一端にＸ線管を有し、且つ他端にＸ線検出器を有する。前記第１セット手段は、両ガントリの交差モードが選択されると、前記Ｘ線管と前記Ｘ線検出器とを結ぶ直線が、前記被検体及び前記開口部を通過するように、前記ＣＴガントリと前記アンギオガントリとを交差させた状態にセットする。前記撮像制御手段は、前記交差させた前記ＣＴガントリ及び前記アンギオガントリによる撮像を制御する。</t>
   </si>
   <si>
-    <t>H05G1/00,H01J37/00,H01J3/00,H01J29/00,H01J31/00,G01S7/00,G01T1/00,H01Q3/00,A61B6/00,G01J5/00,G01S3/00,H01Q9/00,H01Q21/00,H01Q1/00,G09G1/00,H03K3/00,G11B7/00,H01Q19/00,H01J35/00,H04N1/00,G01C19/00,E06B9/00,B66C23/00,E01F9/00,B62J6/00,B66B17/00,F01C20/00,B29C48/00,E04G9/00,B60K35/00,G11B17/00,G11B7/00,B62D1/00,E01B7/00,A61F2/00,G01J5/00,E01B3/00,B23Q1/00,A24F15/00,A47B88/00,A47C17/00,A61G7/00,C10B49/00,F16M11/00,B60P3/00,A47B23/00,B63B29/00,A61G1/00,B66F7/00,A61B50/00,A47B91/00,B22C11/00,B65H5/00,A61B90/00,E04B5/00,E04H6/00,A61G15/00,E01B3/00,B61D1/00,B23Q5/00,G01S3/00,G01S13/00,G05B19/00,G01C11/00,G01C3/00,G01S5/00,H01Q3/00,G06F3/00,G01N23/00,G11B5/00,G01S1/00,G03F7/00,H01Q1/00,H02M1/00,G01S17/00,H04N13/00,G06T7/00,G05D1/00,G21C7/00,A63B51/00,H04N23/00,H04N13/00,H04N25/00,G05B19/00,H04N1/00,H05G1/00,G03B7/00,G01C11/00,H04N5/00,H01S3/00,G02F1/00,G01J5/00,G03H1/00,H02M1/00,B60R1/00,G03B17/00,G03B39/00,H10K39/00,B62M6/00,H01J29/00</t>
-  </si>
-  <si>
-    <t>H05G1/00,A61B6/00,G01T1/00,H01J37/00,H01J3/00,E06B9/00,B66B17/00,B66C23/00,F01C20/00,B29C48/00,A61G7/00,A47C17/00,F16M11/00,A61G1/00,A47B23/00,G05B19/00,G01N23/00,G01S5/00,G01C11/00,G01C3/00,H04N23/00,H04N25/00,H05G1/00,G05B19/00,G03B7/00</t>
-  </si>
-  <si>
     <t>血液浄化システム</t>
   </si>
   <si>
@@ -451,16 +304,6 @@
   </si>
   <si>
     <t>【課題】血液浄化治療中に記憶されて蓄積された過去情報を有効活用することができるとともに、非定常的に発生する特定事項に対する対応を素早く且つ適切に行わせることができる血液浄化システムを提供する。 【解決手段】記憶手段３ａに記憶された過去情報には、血液浄化治療中において非定常的に発生した特定事項が含まれるとともに、記憶手段３ａに蓄積された過去情報を検索し、所望の特定事項を抽出可能な抽出手段５と、抽出手段５で抽出された特定事項が所定回数以上発生した時間を多発時間として算出し得る算出手段５と、算出手段５で算出された多発時間を現在の血液浄化治療中に表示手段４ａにて表示させ得る表示制御手段７とを具備した血液浄化システムである。</t>
-  </si>
-  <si>
-    <t>A61M60/00,B01D35/00,A61M1/00,B01D61/00,B01D29/00,B01D33/00,B01D25/00,A61B5/00,B01D46/00,B61G1/00,F02M35/00,B07B11/00,B08B9/00,B60L1/00,B05B15/00,B01D53/00,A47K7/00,D06F43/00,B01D36/00,A47L9/00,A61M60/00,B41J5/00,B41B27/00,G11B27/00,A61M1/00,B01D29/00,G11B15/00,G06F7/00,G11B7/00,A23C9/00,G06F12/00,B66B1/00,G06K1/00,B01D33/00,G01N33/00,G11B25/00,A61B5/00,G01P1/00,B30B9/00,B01J49/00,G06F16/00,G06V10/00,G06F18/00,G06T7/00,G10L17/00,H04H60/00,H04L41/00,H04N21/00,G11B27/00,G10L19/00,H04M1/00,G10L25/00,G06V30/00,G06N5/00,H04L67/00,G10L21/00,G02F1/00,H04N19/00,H01M8/00,F24F11/00,G04C23/00,G06F7/00,H03L7/00,G07C1/00,G06F18/00,H04M15/00,G06M3/00,H01H43/00,G04B23/00,H04N19/00,H04N25/00,G08C19/00,G04C21/00,G07C3/00,G01P3/00,G01R19/00,H01M8/00,H04L41/00,H03K3/00,G01D5/00,B60K35/00,H04W68/00,B60W50/00,A61M60/00,F24H15/00,G04C21/00,G06F11/00,A61B5/00,G06M3/00,H04L41/00,D06F33/00,G16H50/00,H04H60/00,H04M1/00,H04N5/00,G09G5/00,G11B7/00,H04L67/00,F16H61/00,G07D11/00</t>
-  </si>
-  <si>
-    <t>A61M60/00,A61M1/00,B01D61/00,A61B5/00,B01D35/00,A61M60/00,A61M1/00,G11B27/00,G11B15/00,G06F7/00,G06F16/00,G06F18/00,G06V10/00,G11B27/00,H04L41/00,G07C1/00,G06F7/00,G06F18/00,G06M3/00,G04C23/00,A61M60/00,A61B5/00,H04W68/00,G06F11/00,G04C21/00</t>
-  </si>
-  <si>
-    <t>A63F5/04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>middle_main_hit_count</t>
@@ -506,6 +349,156 @@
   <si>
     <t>説明</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A23C9/00,A21D13/00,C09K8/00,A23L7/00,A23C11/00,A23L29/00,A23C15/00,G03C1/00,A21D2/00,A21D8/00,C08F2/00,C04B103/00,C09D1/00,B32B27/00,A23F5/00,C08B30/00,A23C19/00,A61K47/00,D06L4/00,B05D7/00,C09K8/00,G01N33/00,B01F101/00,A23C15/00,A23L33/00,C11C3/00,C08G63/00,A21D8/00,A21D10/00,C10M127/00,C10G71/00,C08K13/00,C10N30/00,B65D85/00,A23D9/00,A23C19/00,A23P10/00,C10M101/00,A23G1/00,A23D7/00,C12N9/00,C12P19/00,C12Q1/00,C23G1/00,D21H23/00,A23C9/00,A21D8/00,C09D1/00,C09K8/00,C12G1/00,A23L13/00,A23C19/00,A21D2/00,A23L2/00,C12N15/00,A23K10/00,C09D7/00,A23L3/00,A23K30/00,A23C13/00,C23C22/00,C09K8/00,A23L33/00,A21D2/00,A21D13/00,C09D1/00,C12Q1/00,C08G63/00,C04B35/00,C07F9/00,C07C47/00,A21D8/00,C09K23/00,C08K13/00,C07C51/00,C09B43/00,D01F6/00,C11D3/00,A23C9/00,A61K31/00,A23L7/00,B29C48/00,B28B21/00,A21D13/00,B65B25/00,A21D8/00,C08J9/00,B29C70/00,B28B11/00,A23G3/00,A21C3/00,A23P10/00,B21D22/00,C03B23/00,B23P9/00,B21D26/00,B01D25/00,D21H23/00,B29C44/00,B31D5/00</t>
+  </si>
+  <si>
+    <t>A21D13/00,A21D2/00,A21D8/00,A23L7/00,A23L29/00,A21D8/00,A21D10/00,A23L33/00,C11C3/00,B01F101/00,C12N9/00,C12P19/00,C12Q1/00,A21D8/00,A23C9/00,A23L33/00,A21D2/00,A21D13/00,C12Q1/00,C09K8/00,A23L7/00,A21D13/00,A21D8/00,C08J9/00,B29C48/00</t>
+  </si>
+  <si>
+    <t>A23G3/00,H01M50/00,C09K8/00,B32B37/00,B29C48/00,A23P20/00,C03C25/00,A23G1/00,A21D13/00,B65D75/00,D04H1/00,H01M8/00,B29C64/00,C08G63/00,G11B7/00,B29C43/00,B29C39/00,B29C41/00,B32B25/00,B29C63/00,C09K8/00,A23G1/00,A23F5/00,D21H23/00,A21D13/00,A23C19/00,C08F2/00,A23P20/00,A23G3/00,C12C7/00,B29C70/00,B01J19/00,B01D53/00,C08F20/00,C08F120/00,C08F220/00,B41M5/00,A61P17/00,A01N25/00,D21H19/00,A61K31/00,C07H3/00,C12P19/00,C07H19/00,C12C7/00,C08F2/00,C08G18/00,C09K23/00,A23C19/00,C06B45/00,A61K9/00,A23G3/00,B01F101/00,C13B50/00,C12Q1/00,A23L33/00,C08G63/00,A23P20/00,C13K1/00,A23G9/00,C23C8/00,C21D1/00,B29C53/00,C25D5/00,C08J7/00,C23C22/00,H01L21/00,B05D5/00,C03B27/00,B24C1/00,C23C18/00,C23C10/00,C23C2/00,B28B1/00,C03C15/00,C10L9/00,C21D5/00,B05D3/00,C23D13/00,C23C16/00,A21D13/00,C09K8/00,A23L33/00,A23G3/00,A23B4/00,A23C15/00,C10N30/00,A23B7/00,A23P10/00,B01F101/00,A23C19/00,A23B9/00,A23B5/00,A23G1/00,A23L7/00,A23D9/00,G01N33/00,A23D7/00,A23P20/00,A01J27/00</t>
+  </si>
+  <si>
+    <t>A23G3/00,A23P20/00,A23G1/00,A21D13/00,B32B37/00,A23G1/00,A21D13/00,A23P20/00,A23G3/00,A23C19/00,C07H3/00,C12P19/00,C07H19/00,C09K23/00,C06B45/00,C21D1/00,B05D5/00,C08J7/00,C03B27/00,B24C1/00,A21D13/00,A23L33/00,A23G3/00,A23P10/00,A23B4/00</t>
+  </si>
+  <si>
+    <t>B65G53/00,C10J3/00,F24F3/00,A23L3/00,B65B55/00,C10B21/00,C23C16/00,F23D14/00,F27D7/00,C02F1/00,C12M1/00,H01J61/00,B07B11/00,B01J38/00,A61M16/00,F16F9/00,H01J7/00,F27B7/00,F27B5/00,B01D53/00,F24F1/00,H01M50/00,H01R13/00,H02B11/00,E06B3/00,H01P1/00,G21C19/00,B04C5/00,E04B2/00,E06B9/00,F01N1/00,H01F41/00,B65H3/00,E06B7/00,B03C3/00,F02C7/00,H01L21/00,F16L59/00,H01B7/00,E04B1/00,F24F3/00,F24F1/00,B01D46/00,A47L5/00,F01N3/00,F01P5/00,F02M35/00,F02M26/00,F24F11/00,F23N1/00,F24F7/00,F02F1/00,B60H1/00,F01P7/00,F23D14/00,B01D35/00,F23C10/00,F04D25/00,E03D9/00,A47L15/00,F24F1/00,B01D29/00,B01D33/00,B29C45/00,F27B7/00,F27B5/00,B01D25/00,F27B15/00,F27B1/00,B29C48/00,F02B25/00,G05B11/00,F23C10/00,B05B14/00,F23K5/00,F27B14/00,F27B9/00,F02M35/00,F02C6/00,F23C7/00</t>
+  </si>
+  <si>
+    <t>F24F3/00,F27D7/00,A23L3/00,B65B55/00,B65G53/00,F24F1/00,E06B3/00,E06B9/00,E04B2/00,B04C5/00,F24F3/00,F24F1/00,B01D46/00,F24F11/00,F01N3/00,F24F1/00,B01D29/00,B01D33/00,B01D25/00,B29C45/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,B41M5/00,B32B5/00,H01M50/00,D21H27/00,F24S70/00,B65D81/00,B62J1/00,A61F5/00,A61L15/00,B32B3/00,G09F11/00,G03F1/00,C04B41/00,B01D24/00,D01G15/00,B32B25/00,B65B11/00,B41J17/00,B29C63/00,H01M50/00,B29C63/00,B65D90/00,B29C73/00,B65H63/00,B29C48/00,B67D7/00,B01J19/00,B05B15/00,B23K35/00,A23L3/00,G09F11/00,G01N23/00,B65B1/00,F42B3/00,E04F13/00,F01D5/00,F16L55/00,G02B1/00,F16L11/00,E04B2/00,B60R21/00,A61F13/00,B64D25/00,B60V1/00,F02K1/00,A47C1/00,B29C48/00,B60J10/00,B62J1/00,B65D81/00,B60N2/00,B65D75/00,B65D90/00,F16K1/00,C01B3/00,A47C7/00,A47C4/00,G01L5/00,B29C64/00,A61F13/00,A61L15/00,B65B35/00,H01M4/00,B65B41/00,B65B43/00,F24S70/00,B65D81/00,A61L17/00,C07C7/00,B65B1/00,B01D39/00,H01J29/00,A01N25/00,G21F9/00,B01J47/00,F16L59/00,C09K8/00,B01D24/00,D06B23/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,B32B5/00,A61L15/00,D21H27/00,F24S70/00,B29C63/00,B29C73/00,B01J19/00,B65D90/00,B29C48/00,A61F13/00,B29C48/00,B60J10/00,E04B2/00,B60R21/00,A61F13/00,A61L15/00,F24S70/00,A61L17/00,B65D81/00</t>
+  </si>
+  <si>
+    <t>A23L7/00,H01F1/00,A23P10/00,A23P20/00,A61K9/00,A61L15/00,A23L29/00,H01M8/00,B24D3/00,C23C10/00,C09K8/00,A23G9/00,C06B45/00,B05D1/00,A61L9/00,A61K47/00,C08C1/00,D06P1/00,B29B9/00,F28C3/00,H01M50/00,A23L7/00,C08J3/00,D04H1/00,G03F7/00,G03C1/00,C08B30/00,A21D13/00,C08F2/00,H01F1/00,B05D1/00,D06P1/00,B01F35/00,A23P10/00,C10M169/00,A23L29/00,B29B7/00,C09C1/00,B01J20/00,B29C70/00,C08F2/00,C09K8/00,B01F101/00,G01N33/00,C08J3/00,C11D10/00,A61K8/00,B01F23/00,A23P10/00,G03C1/00,C10N50/00,A23L33/00,C07C17/00,C10G71/00,A61L15/00,D06L4/00,C10M169/00,G05D11/00,A23G1/00,C08K9/00,C08J9/00,G03C1/00,A23L7/00,A23P10/00,B02C4/00,B01J2/00,C08B30/00,C07C51/00,D06P1/00,C08J5/00,C08K9/00,C08J3/00,B05D1/00,A23L29/00,B29C44/00,C23C10/00,A21D13/00,G03C7/00,E01C19/00,G03F7/00,F04B15/00,A47J31/00,H01M10/00,C10J1/00,F01P7/00,C07C4/00,F02F1/00,F24H15/00,C01F7/00,B65G53/00,G01M3/00,B01F35/00,F24F6/00,F02C1/00,G01L5/00,F24S60/00,H01L23/00,F01K25/00,F23D11/00,G01N25/00</t>
+  </si>
+  <si>
+    <t>A23L7/00,A23P10/00,A23P20/00,A23L29/00,A61K9/00,A23L7/00,C08B30/00,C08J3/00,A21D13/00,C08F2/00,B01F23/00,A23P10/00,B01F101/00,C08J3/00,C08F2/00,A23L7/00,C08B30/00,A23P10/00,B01J2/00,B02C4/00,A47J31/00,F24H15/00,B65G53/00,C10J1/00,F04B15/00</t>
+  </si>
+  <si>
+    <t>H02P3/00,D03D51/00,H01H73/00,H02P6/00,D05B69/00,B61L5/00,B65B57/00,A01B35/00,G01D11/00,F16H48/00,B43K24/00,B65G51/00,B25B23/00,B65H59/00,G05G5/00,D01H7/00,H01H3/00,B41J29/00,B61F17/00,F16H33/00,F41A19/00,B62M6/00,B66D1/00,H01H33/00,A61M60/00,H02K7/00,A01D34/00,E05F15/00,B60S9/00,F42B19/00,B08B9/00,B02C18/00,F04B17/00,E02F3/00,B60L50/00,B05B5/00,A61C17/00,F02C7/00,B21J7/00,D03D43/00,B62M6/00,B61C9/00,A01D34/00,F16C3/00,A01D78/00,F16D13/00,B63H23/00,E05F3/00,F26B11/00,B64C27/00,B60K5/00,F16H39/00,F16H37/00,F04D29/00,F16D55/00,F16D25/00,F16J1/00,A24B7/00,B62M1/00,B60K17/00,B26D1/00,A01D34/00,B26B19/00,B26B21/00,B26D5/00,A24B7/00,B24B3/00,B67B7/00,B26D7/00,B27B5/00,A63C1/00,A01D75/00,B26B13/00,B23D19/00,B62M6/00,F16D13/00,E01H5/00,B23D47/00,B23D71/00,D01G1/00</t>
+  </si>
+  <si>
+    <t>H02P3/00,D03D51/00,H01H73/00,H02P6/00,F16H48/00,B62M6/00,H02K7/00,A01D34/00,H01H33/00,B66D1/00,A01D34/00,F16C3/00,F16D13/00,B62M6/00,B61C9/00,B26D1/00,A01D34/00,B26D5/00,B26D7/00,B24B3/00</t>
+  </si>
+  <si>
+    <t>B01F25/00,B67D7/00,F24S10/00,B65G53/00,F17D1/00,F28D1/00,H01M50/00,B01F29/00,A61M5/00,B65D21/00,B65G35/00,G21C19/00,H01H29/00,F02F1/00,B30B9/00,B01D15/00,F27D3/00,F25B41/00,B05B11/00,B65G47/00,G07F11/00,B67D7/00,B01F29/00,B65D21/00,B01F31/00,B01F35/00,B30B9/00,B08B9/00,G21F5/00,B65B3/00,B65B43/00,E04H7/00,G11B15/00,G01F11/00,G21F9/00,H01J5/00,B65D6/00,B65D5/00,B65D88/00,A47F1/00,F16H61/00,F04F5/00,A61M60/00,F04D13/00,F04D29/00,F16D31/00,F16H39/00,F17D1/00,F15B9/00,F04F1/00,F04D25/00,F04B43/00,F01P5/00,B05B7/00,B05B9/00,H01M50/00,B21D26/00,F02M37/00,F24H15/00,G01N30/00,A61M60/00,A61M5/00,A61M1/00,B01F25/00,C12M1/00,F17D1/00,C12N15/00,G01P3/00,B01D15/00,H01M50/00,B05C9/00,A01D17/00,C01B3/00,B05D1/00,F04F5/00,G01N30/00,B08B9/00,B05B7/00,B65G53/00,G01N27/00,B67D7/00,C09B67/00,B05B7/00,G05D11/00,B01D17/00,G01K5/00,F17D1/00,B01J8/00,B05B12/00,G01N30/00,A47L1/00,B01F23/00,F16F9/00,F02C9/00,F16H47/00,C01B3/00,B03B5/00,B65G53/00,B05B5/00,B60S1/00</t>
+  </si>
+  <si>
+    <t>B01F25/00,B67D7/00,F17D1/00,B65G53/00,A61M5/00,B65D21/00,B67D7/00,B01F29/00,B01F31/00,B65B3/00,A61M60/00,F04D13/00,F04F5/00,F04F1/00,F04D29/00,C12M1/00,A61M1/00,A61M5/00,B01F25/00,B01D15/00,B67D7/00,B05B7/00,G05D11/00,B01D17/00,B05B12/00</t>
+  </si>
+  <si>
+    <t>C09K8/00,G03C1/00,A23L29/00,A23L33/00,A23P10/00,C04B103/00,B41M5/00,B01F23/00,D06P1/00,B02C4/00,A23G9/00,C09D11/00,E01C19/00,H01G11/00,A23L7/00,C12G3/00,A61L9/00,C08J3/00,C10M169/00,A61K8/00,A23L7/00,A23C9/00,A23L29/00,C01F7/00,A23K10/00,C09K8/00,A23L33/00,C09D1/00,A23F5/00,C08K9/00,A23G9/00,A23C19/00,A23P10/00,C12C7/00,C08B30/00,A21D13/00,A61K47/00,A23G1/00,A23L5/00,C07C231/00,B01F23/00,B22F1/00,B01F25/00,C08J3/00,B01J2/00,A61K9/00,F04F5/00,G01N15/00,A23P10/00,C08J9/00,C08F2/00,B05B1/00,B05D1/00,B29B9/00,C06B45/00,B05B7/00,B01J19/00,C09K8/00,A61M11/00,E21F5/00,B65B1/00,B65B11/00,B65B3/00,B65D21/00,B65D77/00,A23L3/00,B65B55/00,B05C7/00,H01L23/00,A23P20/00,H01J5/00,F16J15/00,B65D81/00,B01F29/00,B65B29/00,B65B5/00,B65B39/00,B65D75/00,B65B43/00,B65B31/00</t>
+  </si>
+  <si>
+    <t>A23L29/00,A23L33/00,A23P10/00,B01F23/00,B02C4/00,A23L7/00,A23L29/00,A23L33/00,A23C9/00,A23K10/00,B01F23/00,B01F25/00,C08J3/00,B01J2/00,A23P10/00,B65B3/00,B65B1/00,B65B55/00,A23L3/00,B65D21/00</t>
+  </si>
+  <si>
+    <t>A23B7/00,A23L3/00,C21D1/00,A23B9/00,G03B27/00,C01F7/00,A23B4/00,A23B5/00,A47J31/00,G03F7/00,G21C19/00,B09B3/00,D21F5/00,C10B21/00,D06M23/00,A45D4/00,F26B3/00,D21C1/00,B29C49/00,B29C70/00,C23C22/00,G03C7/00,C12G1/00,C01F7/00,B05C3/00,C08J11/00,C10K1/00,D06M23/00,B01J38/00,D06L1/00,A21D8/00,D06P1/00,C23F1/00,C07C31/00,D06B23/00,C30B7/00,C10G53/00,C22B9/00,C23F3/00,A62D3/00,C09B62/00,B41M5/00,D06P1/00,C12G3/00,A23L2/00,A23F3/00,D06P5/00,G03C7/00,A23L5/00,C12F3/00,C09D11/00,C12G1/00,B01F101/00,C12C12/00,G03C8/00,C09K8/00,A23F5/00,D06P3/00,C08F220/00,C08F120/00,H01M4/00,C10G53/00,C10G65/00,A23L2/00,A23F3/00,C12G1/00,C12G3/00,C10G67/00,C10G61/00,C12C11/00,C12C7/00,C08G69/00,C08J9/00,D04H1/00,C04B35/00,C08B1/00,C11D11/00,C10G69/00,C13B10/00,D06M23/00</t>
+  </si>
+  <si>
+    <t>A23B7/00,A23L3/00,C21D1/00,A23B9/00,A23B4/00,C12G1/00,B05C3/00,D06M23/00,C23C22/00,D06L1/00,C09B62/00,D06P1/00,C12G3/00,A23L5/00,A23F3/00,C12G3/00,A23L2/00,C12G1/00,A23F3/00,C12C11/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G23/00,G01G13/00,B07C5/00,B65B1/00,G01G3/00,G01G1/00,A01K39/00,G01N9/00,G01G21/00,G01G11/00,G01G17/00,G11B15/00,B65B3/00,G01G15/00,B65D41/00,B29B7/00,G01N5/00,A01K97/00,G01K17/00,G01G19/00,H04H60/00,G11B15/00,G01S13/00,A63F13/00,G11B27/00,G01V8/00,B60T8/00,A61B5/00,E05B81/00,G01G11/00,G06V20/00,G06V40/00,G07C9/00,G11B19/00,G01N29/00,B23Q35/00,G06F3/00,B65H63/00,G01C19/00,H04H60/00,G11B27/00,G07D7/00,G06K19/00,G11B15/00,H04W12/00,A61B5/00,A47G19/00,G01S13/00,G01P3/00,G06K21/00,G11B23/00,B60R25/00,G06F21/00,G06T7/00,B23Q35/00,G01D5/00,A63F13/00,B07C3/00,G01N29/00,G01G19/00,G01G23/00,B07C5/00,A23K50/00,G06F119/00,G01G13/00,G06G7/00,G01G1/00,B65B3/00,G01G15/00,A01M29/00,F16C23/00,F16C25/00,G01G21/00,G01G11/00,H04H60/00,A61B5/00,A01K39/00,A23K40/00,G01C11/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G13/00,G01G23/00,G01G3/00,A01K39/00,G01G19/00,A61B5/00,G01S13/00,G01V8/00,G11B15/00,A61B5/00,H04W12/00,G06K19/00,G01P3/00,A47G19/00,G01G19/00,G01G13/00,A23K50/00,G06F119/00,B07C5/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G23/00,B07C5/00,B65B1/00,G01G13/00,G01G3/00,G01N9/00,G01G1/00,G01G11/00,G01G17/00,G01L5/00,G01G21/00,G01G15/00,B65B37/00,G01N5/00,B65G69/00,G01F1/00,G01K17/00,B65H33/00,C12C1/00,A01F12/00,G07F11/00,C12C1/00,B65D21/00,B65D75/00,A01F25/00,B60K15/00,B63B25/00,B64D37/00,A24C5/00,B65D77/00,F15B1/00,E01B7/00,B02C7/00,A47B77/00,B65D25/00,F41A9/00,B62B1/00,G11B23/00,G21C3/00,B60P1/00,B65H39/00,B62B1/00,G07F11/00,E04G1/00,B66F7/00,A47C1/00,G09B1/00,F16L3/00,E21D15/00,E05D15/00,F16D65/00,B65G17/00,B60R9/00,H01L21/00,B60L5/00,E02F9/00,E01B21/00,G01L5/00,B65B43/00,G01G19/00,G01G23/00,G01G13/00,B07C5/00,G01G3/00,A01F12/00,B65B1/00,G01G11/00,G01G1/00,G01M1/00,G01G17/00,G01G21/00,G05B1/00,G01P3/00,G01N9/00,G05D11/00,G01G15/00,G10L21/00,G01N29/00,G01B9/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G13/00,G01G3/00,G01G23/00,G01G17/00,A01F12/00,A01F25/00,B65D21/00,B60K15/00,B63B25/00,B60P1/00,B66F7/00,F16L3/00,B62B1/00,E04G1/00,G01G19/00,G01G23/00,G01G13/00,G01G3/00,G01G11/00</t>
+  </si>
+  <si>
+    <t>E04G7/00,B23B31/00,F16L3/00,F22B37/00,F16L37/00,A45D2/00,H01R33/00,B65D43/00,F16B12/00,B27B29/00,E01B9/00,B27G13/00,B65D35/00,F16G11/00,B23D41/00,B25B5/00,B23Q1/00,B21C1/00,A45D6/00,B65B13/00,G01G19/00,G01L5/00,G01F1/00,G01G3/00,F16F1/00,G01G13/00,G01L23/00,G01L13/00,E21D15/00,A61M60/00,G01G23/00,B61K9/00,G01G11/00,D03D49/00,B21B19/00,B65G43/00,B60T8/00,G21C17/00,B65H63/00,G01L1/00,B65B11/00,F16L55/00,E21B47/00,F16L37/00,B65B9/00,A61F2/00,B65G51/00,B65D75/00,H01H33/00,B61L21/00,B61L23/00,A61M60/00,A63B41/00,E03C1/00,A61M39/00,F16K21/00,H01M10/00,F16L9/00,B31C1/00,H01J19/00,A61M60/00,B01D35/00,B01D61/00,A61B90/00,H02B1/00,A61B50/00,G21C19/00,F41A9/00,B01D25/00,E04B2/00,F16B12/00,C40B60/00,B21B39/00,F02M37/00,B41L38/00,B30B9/00,F22B37/00,B60K35/00,B01D29/00,A61M5/00</t>
+  </si>
+  <si>
+    <t>F16L3/00,B23B31/00,F16L37/00,B65D43/00,B27B29/00,G01G19/00,G01L5/00,G01F1/00,G01G3/00,G01L23/00,F16L55/00,A61F2/00,F16L37/00,B65G51/00,B65B11/00,A61M60/00,B01D61/00,A61B50/00,B01D35/00,A61B90/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,G05B19/00,B60K35/00,A63F7/00,H04N23/00,H01H13/00,G01S7/00,C01B21/00,A01B41/00,B41F33/00,B60L1/00,B64G1/00,B64D25/00,H04N19/00,H03K17/00,B60S9/00,B62M6/00,B60W50/00,A63J5/00,H04N21/00,A63F13/00,H03G9/00,B01D61/00,F16H61/00,H03G3/00,G05F1/00,H02M7/00,G05D1/00,G05B19/00,H01S3/00,B60K35/00,G06F3/00,G10H1/00,A61F13/00,B61L3/00,F24F11/00,B21D26/00,G03B7/00,B62M6/00,D06F34/00,A63F13/00,G09G5/00,B60K35/00,G06F3/00,H01J31/00,G05B19/00,G01S7/00,H02M7/00,G02F1/00,G09G3/00,G03B7/00,H04H60/00,G08G1/00,H04N9/00,G08B5/00,H04N21/00,G03G15/00,D06F34/00,G09G1/00,H04N13/00,G04C23/00,G06F1/00,G04B23/00,G04C21/00,H01H43/00,G08B5/00,G07C1/00,G01S3/00,F24F11/00,H04M1/00,H01H73/00,G04B21/00,B67D7/00,H04M15/00,H02P8/00,H03G9/00,G07C3/00,G03B7/00,G07C5/00,G10K1/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,G05B19/00,A63F7/00,B41F33/00,H01H13/00,A63F13/00,H03G9/00,H03G3/00,G05F1/00,G05B19/00,A63F13/00,G09G5/00,G06F3/00,G02F1/00,G09G3/00,G04C23/00,G06F1/00,H01H43/00,G07C1/00,G08B5/00</t>
+  </si>
+  <si>
+    <t>H03M1/00,H03K17/00,H04N25/00,H04N5/00,H04N9/00,G06F7/00,H04Q3/00,H04L27/00,H04L25/00,A63F13/00,H03F3/00,G01R31/00,H04N11/00,H04Q1/00,H02M7/00,H04N1/00,G11C16/00,G11C11/00,H04B3/00,A01B3/00,H03K17/00,H04B3/00,H04N25/00,H04N23/00,H04N5/00,G08B29/00,H04B1/00,H04L27/00,H04N9/00,H04M1/00,G11C16/00,H04N1/00,H02J3/00,G01C19/00,H04L25/00,H02M1/00,G10L21/00,H04N21/00,H03G1/00,F02D41/00,H03K17/00,H03K3/00,H05B45/00,G11C11/00,H01R12/00,G05F1/00,G09F11/00,H02M7/00,H02M1/00,H05B41/00,H04N5/00,G05B19/00,H04N25/00,F16H61/00,B60L15/00,G08B29/00,H03K21/00,H05B47/00,G11C7/00,H02P3/00,H02M7/00,H02J3/00,B60L1/00,B60L9/00,H02M1/00,H03K17/00,H02P27/00,H02J1/00,H04N3/00,G05F1/00,H01Q5/00,H02J9/00,G06F1/00,F21S9/00,H03K3/00,H05B7/00,H01Q9/00,H05B45/00,H04Q1/00,H02J50/00</t>
+  </si>
+  <si>
+    <t>H03K17/00,G06F7/00,H03M1/00,A63F13/00,H04L25/00,H03K17/00,H04B3/00,G08B29/00,H04B1/00,H04L27/00,H03K17/00,H03K3/00,G05F1/00,H01R12/00,H02M7/00,H02M7/00,H02J3/00,H02M1/00,H02J1/00,G05F1/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,H03K17/00,G05B19/00,G05D1/00,B60T8/00,B60W20/00,H04N5/00,B60W10/00,H02P1/00,H04L49/00,B60W30/00,G11B15/00,B61L27/00,F24F11/00,G05G7/00,H04H20/00,G21C7/00,B60L1/00,G03B7/00,G06F13/00,G05D1/00,B60W30/00,G09F11/00,E05B81/00,B60L15/00,B60W50/00,F15B9/00,B23Q15/00,H04N23/00,B60T8/00,B60W10/00,H04N5/00,A63F13/00,H02M3/00,B60K35/00,B61G1/00,H04N21/00,H02M7/00,B43K24/00,H03K17/00,H04N21/00,H04L47/00,H04L67/00,G06F13/00,H04W72/00,G06F21/00,H04N19/00,H04L45/00,H04L12/00,G05B19/00,G05D1/00,G06F12/00,G07D11/00,H03K17/00,G07C5/00,H02P8/00,H04W4/00,G07C3/00,G06F1/00,G11B19/00,A63F13/00,B60W10/00,A63F7/00,G09F11/00,G05B19/00,G05D1/00,B60W50/00,G04C23/00,E02F3/00,B61L27/00,H02M3/00,D06F33/00,B61G1/00,D06F34/00,B64C13/00,F02D11/00,B60W30/00,F15B11/00,A01D34/00,B64G1/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,G05B19/00,H03K17/00,H04N5/00,G05D1/00,G09F11/00,F15B9/00,B23Q15/00,B60W50/00,B60W30/00,H04N21/00,H04L47/00,H04L67/00,G06F13/00,G05B19/00,A63F13/00,A63F7/00,G05B19/00,G04C23/00,G09F11/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,H04N21/00,H04L67/00,H04L47/00,G06F1/00,B41B27/00,G05D1/00,H04N5/00,H04M1/00,G05B19/00,G11B20/00,B61G1/00,B60W30/00,B60T11/00,H04L41/00,G11B17/00,H01S3/00,G11B19/00,H04N1/00,H04Q3/00,A63F13/00,G08B5/00,G11B11/00,D03D51/00,H02P8/00,E06B9/00,H04L65/00,G05D1/00,H01H71/00,H01H73/00,H04L67/00,G06F1/00,H01H43/00,G10H3/00,B41B27/00,E01F9/00,H04N5/00,H04L41/00,H01M8/00,G11B20/00,A63F13/00,H04L12/00,H04N21/00,H04H60/00,H04L67/00,H04H20/00,H04M1/00,H04W88/00,G06F13/00,H04Q5/00,H04L47/00,H04L61/00,H04W68/00,H04W92/00,H04Q3/00,G06F15/00,H04L51/00,H02P5/00,H02K3/00,H10K59/00,A63F13/00,H04L65/00,H04L67/00,H04W68/00,G04C21/00,H04N21/00,H04M3/00,G06F13/00,G04C23/00,H04M1/00,H04L41/00,H04L47/00,H04W4/00,H04W76/00,H04H60/00,B64D17/00,D01H5/00,H04L45/00,H04W24/00,H04L69/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,H04N21/00,H04L67/00,G06F1/00,G05B19/00,A63F13/00,H04L65/00,G08B5/00,G11B11/00,G05D1/00,A63F13/00,H04L12/00,H04L67/00,G06F13/00,H04N21/00,A63F13/00,H04L65/00,H04W68/00,H04N21/00,H04L67/00</t>
+  </si>
+  <si>
+    <t>A47G25/00,D06F58/00,D06F33/00,A47H1/00,A47K10/00,E03C1/00,D06F71/00,A41F11/00,D06F105/00,D06F103/00,A47F7/00,D06F53/00,A45C13/00,D01H13/00,D06F59/00,A41D27/00,A41H9/00,A41D13/00,F16L3/00,D06F1/00,A47G25/00,H01R13/00,E05B67/00,B08B17/00,A41F11/00,B64C25/00,H01R4/00,E05C17/00,B60L5/00,A61F13/00,B65H31/00,A43B7/00,B66B5/00,B65D25/00,A47F7/00,A41H9/00,E04H17/00,H01R33/00,H02B1/00,B66C1/00,E06C1/00,B01F27/00,E04G1/00,E04G17/00,A47G25/00,F16D3/00,A47C20/00,D06F53/00,E21D15/00,A01D37/00,E01D15/00,F16S3/00,A61K31/00,E04F11/00,E05C9/00,D06F57/00,A47C23/00,C07D491/00,C07D497/00,C07D493/00,A47H1/00,A47G25/00,E05C17/00,E04G17/00,G09F7/00,A47H3/00,E05C19/00,D06F53/00,H01L23/00,F16J13/00,B65B43/00,E03C1/00,B65H9/00,D05C11/00,B60M1/00,E04H17/00,A43B21/00,H01Q1/00,D06F57/00,H02K1/00</t>
+  </si>
+  <si>
+    <t>A47G25/00,D06F58/00,A41F11/00,A47H1/00,D06F71/00,A47G25/00,A41F11/00,B08B17/00,E05C17/00,A61F13/00,A47G25/00,D06F53/00,E06C1/00,E04G1/00,E04G17/00,A47G25/00,D06F53/00,A47H3/00,A47H1/00,E05C17/00</t>
+  </si>
+  <si>
+    <t>G10H1/00,G10L13/00,A63F13/00,G10H5/00,G10L25/00,G10K11/00,G10L15/00,H03G9/00,H01S3/00,G10L19/00,G04C21/00,H04N5/00,H03K3/00,H03B5/00,G10L21/00,G10K15/00,G01S19/00,H03J7/00,H03G3/00,G04B23/00,H03L7/00,G10H1/00,G04C23/00,H04N5/00,H03G9/00,G04C21/00,A63F13/00,H04N21/00,H04N9/00,H03D3/00,H03K3/00,H03G3/00,H04N13/00,H03K5/00,H01S3/00,G08G1/00,H01H19/00,H03J1/00,G10L21/00,H04L47/00,A63F13/00,G10H1/00,B61G1/00,G10L13/00,G01S7/00,B60K35/00,H01S3/00,G10K15/00,A63J5/00,G10C3/00,H04M3/00,G11B17/00,G10K11/00,G10L25/00,A63H17/00,C10G9/00,G01F1/00,H04R3/00,C01B21/00,G06F9/00,A63F13/00,G10H1/00,H03G9/00,G09F11/00,G10L13/00,G10L25/00,H03G3/00,G10K11/00,H04M1/00,H04N5/00,H02M7/00,H03J7/00,B60K35/00,B60W50/00,H04H60/00,G10L21/00,H01S3/00,H04B1/00,F24F11/00,H04M3/00</t>
+  </si>
+  <si>
+    <t>G10H1/00,G10L13/00,G10H5/00,G10L19/00,A63F13/00,H03L7/00,G10H1/00,G04C23/00,H03G9/00,A63F13/00,A63F13/00,G10H1/00,G10K15/00,A63J5/00,G10L13/00,A63F13/00,G10H1/00,H03G9/00,G10L25/00,G10K11/00</t>
+  </si>
+  <si>
+    <t>H04N23/00,G03B17/00,F21K9/00,H04N5/00,G11B7/00,A61B6/00,G01C19/00,G02B27/00,H05K7/00,F04B1/00,B64D27/00,A61B90/00,G02F1/00,G16H30/00,B29B7/00,H01J37/00,A61B17/00,B62J6/00,G03G15/00,B64U20/00,H04N23/00,H04N25/00,G03B17/00,H04N13/00,G06V10/00,H04N5/00,H04N1/00,H01L31/00,G02B9/00,G03G15/00,G03C8/00,B41B15/00,H01J31/00,G03B37/00,G01C11/00,G02F1/00,H05G1/00,G03B19/00,G03B7/00,H01L27/00,G01C19/00,H01H19/00,B43K24/00,F41A3/00,H01H73/00,H01H3/00,F16K41/00,F16D1/00,G06F3/00,H01H33/00,E05F15/00,D01H7/00,B41J33/00,F16H15/00,G05G1/00,E04H6/00,H03J5/00,H01H9/00,H02K11/00,F16D3/00,H01H19/00,E05F15/00,H02P21/00,G04C23/00,H01H3/00,H02M7/00,G05G1/00,H01H73/00,F16D43/00,H01H41/00,H01H13/00,G06F3/00,G08B5/00,H01H15/00,G05G9/00,B41J33/00,G05G7/00,H01H33/00,H02P7/00,F16L37/00,H04N23/00,A61B6/00,A61B5/00,A61B3/00,A61B90/00,A61B1/00,A61B34/00,B64U101/00,A61M60/00,G02B27/00,B60R1/00,A61B50/00,G16H40/00,G16H30/00,H04N5/00,G02B7/00,E04B2/00,A61N5/00,G01R33/00,G16H50/00</t>
+  </si>
+  <si>
+    <t>H04N23/00,G03B17/00,A61B6/00,H05K7/00,G02B27/00,H04N23/00,H04N25/00,G03B17/00,H01L31/00,G02B9/00,G01C19/00,H01H19/00,G06F3/00,H01H3/00,F16D1/00,H01H19/00,H01H3/00,G05G1/00,H01H41/00,G04C23/00,H04N23/00,A61B6/00,A61B5/00,A61B90/00,A61B1/00</t>
+  </si>
+  <si>
+    <t>G05B19/00,G09G5/00,C09B35/00,G09G1/00,A63F13/00,H03K17/00,G05B11/00,B60K35/00,G09B1/00,G06V10/00,G06V30/00,H04L12/00,D03C3/00,G08B5/00,B61L25/00,G06F3/00,G07C1/00,H04N19/00,G03F7/00,B60L1/00,A63F7/00,A63F13/00,G06F9/00,A63F9/00,C03B9/00,H02M7/00,G01S3/00,B30B11/00,G06V30/00,D06F13/00,A63F5/00,A63F3/00,B41J5/00,F41J5/00,G06C9/00,H02M5/00,H02M3/00,G05B19/00,G07G1/00,D03C17/00,H01H43/00,D03D51/00,B65B57/00,G04C23/00,F01D21/00,A63F13/00,H02P8/00,H01H7/00,B41F33/00,B41J29/00,H04M1/00,G07C3/00,G04F7/00,H03K17/00,B43K24/00,H05G1/00,H04M15/00,G07C1/00,D06F105/00,G07C5/00,A63F13/00,A63F7/00,E05F15/00,B60K35/00,B64C13/00,G06F3/00,F16C23/00,F16C25/00,G04C23/00,D06F33/00,H03C3/00,A01B63/00,H02M7/00,H01C10/00,B60S9/00,B43K24/00,B60P1/00,B60N2/00,G06V30/00,F16D65/00</t>
+  </si>
+  <si>
+    <t>G05B19/00,G09G5/00,A63F13/00,G09G1/00,G05B11/00,A63F7/00,A63F13/00,A63F9/00,G06F9/00,G06V30/00,H01H43/00,D03D51/00,G04C23/00,A63F13/00,H01H7/00,A63F13/00,A63F7/00,G06F3/00,G04C23/00,E05F15/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,B60N2/00,B60R21/00,B64C1/00,H01M50/00,B29C63/00,A47C7/00,B62J1/00,A43B7/00,B65D88/00,F16H57/00,A47K13/00,E04F13/00,B65D51/00,F16K1/00,F23Q2/00,A47C17/00,G21C5/00,B64C3/00,B62J13/00,H01R13/00,B60R21/00,F16F15/00,A47C7/00,F16D3/00,B28B21/00,F16J15/00,B60G11/00,A47C23/00,F16F1/00,F16F3/00,B62K27/00,F16C1/00,B60C5/00,B65D41/00,E06B9/00,E21B33/00,H01H1/00,B60R19/00,B65D81/00,A61F13/00,D03D47/00,E04G7/00,D03C3/00,H01R13/00,A41D27/00,B65B43/00,E06B3/00,B65D71/00,H01M50/00,B60R21/00,A41F17/00,B65D63/00,A47G25/00,B21D26/00,F04C2/00,F04C18/00,F01C1/00,G03B9/00,B65D5/00,H01R13/00,F16D3/00,F16H15/00,A47C23/00,B66F3/00,F16D65/00,A47C7/00,E04B9/00,A61M60/00,E04B2/00,B28B21/00,G09F11/00,B60N2/00,B65D51/00,F16C7/00,H01J19/00,F16C1/00,B62D55/00,A47C3/00,B62K27/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,B29C63/00,A47C7/00,B60N2/00,B62J1/00,B60G11/00,F16F1/00,A47C7/00,A47C23/00,F16F15/00,A61F13/00,A41D27/00,D03D47/00,D03C3/00,E06B3/00,A47C23/00,A47C7/00,F16D3/00,E04B9/00,E04B2/00</t>
+  </si>
+  <si>
+    <t>A43B7/00,A43D3/00,A43D100/00,A63C10/00,A43D11/00,F24F1/00,A43B13/00,A43D25/00,A41B11/00,B64C25/00,A43B9/00,B60R1/00,A47L23/00,A43D1/00,A47G25/00,D01H7/00,F16H15/00,B63B19/00,A43C15/00,B60R19/00,A47L23/00,A43B7/00,A43D3/00,A63C10/00,A43D1/00,B65D75/00,A43B3/00,A43B23/00,A43B13/00,A43B9/00,G07D11/00,B65D77/00,B62D33/00,A63C1/00,B60R7/00,H04B1/00,A43D95/00,A47B77/00,A63C3/00,E05B83/00,A63C9/00,A43D25/00,A43B7/00,A43D3/00,A43D11/00,A43D100/00,A43D1/00,A43D95/00,A43B13/00,A47G25/00,A63C10/00,A63C1/00,A43D21/00,A47L23/00,A63C11/00,A43B9/00,G05G1/00,D06F81/00,B60R22/00,A63B27/00,A43B7/00,A43D3/00,E05B77/00,A63C9/00,A43B9/00,A43B3/00,A63C10/00,A43D21/00,A43D100/00,A47L23/00,A41B11/00,B60R22/00,A43B13/00,A43D1/00,A61F5/00,A43D25/00,A43B23/00,A43B17/00,A47G25/00,A63C1/00</t>
+  </si>
+  <si>
+    <t>A43B7/00,A43D11/00,A43B13/00,A43D3/00,A43D100/00,A43B7/00,A43B3/00,A43B23/00,A43B9/00,B65D75/00,A43B7/00,A43D11/00,A43D100/00,A43B13/00,A43D25/00,A43B7/00,A43B9/00,A43B3/00,A43D100/00,A47L23/00</t>
+  </si>
+  <si>
+    <t>A47L11/00,H01R39/00,A47L5/00,B08B1/00,E04B5/00,A47L9/00,A47L13/00,B01D33/00,A61C13/00,H02M7/00,B01D46/00,A47L23/00,A46B3/00,B08B9/00,A46B17/00,A61C17/00,C01B3/00,F24F1/00,B01D29/00,C14B1/00,A47L5/00,B65D35/00,H01J19/00,H01M50/00,B66C1/00,B65B43/00,B65D43/00,B65H3/00,E04H17/00,F16L59/00,F02M69/00,H01R33/00,B65D75/00,B65D47/00,F04B37/00,B67B7/00,E05C17/00,H01L23/00,E04B2/00,B65D5/00,A47L5/00,A47L11/00,B08B9/00,A47L15/00,H01R39/00,B01D33/00,B08B1/00,B01D46/00,A47L9/00,H02M7/00,A01G20/00,B65H39/00,B05B15/00,B43K24/00,C14B1/00,B01D29/00,B62J50/00,A46B13/00,A61C17/00,B01D47/00,A47L5/00,B01D46/00,F02M35/00,F02B25/00,A61C17/00,B04C5/00,B65H3/00,B08B5/00,F02M26/00,B65G53/00,A47L11/00,A47L7/00,A47L9/00,E21B21/00,F24F13/00,B65G23/00,F02C9/00,F26B13/00,B65B1/00,F02B31/00</t>
+  </si>
+  <si>
+    <t>A47L11/00,A47L5/00,A47L9/00,A47L13/00,B08B1/00,A47L5/00,B65D35/00,B65D43/00,B65B43/00,F16L59/00,A47L5/00,A47L11/00,A47L9/00,B08B1/00,B08B9/00,A47L5/00,B01D46/00,B08B5/00,B04C5/00,B65G53/00</t>
+  </si>
+  <si>
+    <t>A47C17/00,A61G7/00,E01B3/00,B62D33/00,E01B29/00,C10B49/00,E01B9/00,A47B23/00,B63B29/00,A61G1/00,H01M50/00,H05K7/00,A47B5/00,A47B3/00,B60P3/00,B01J49/00,E04H6/00,C10B55/00,E04G1/00,E04B5/00,B23Q1/00,G05B19/00,G05G9/00,B25B13/00,F03C2/00,H02M1/00,B23C1/00,G01F1/00,G05D13/00,F16H3/00,F16H48/00,H01Q3/00,G11B5/00,G06C15/00,D03D47/00,G01S1/00,H01H1/00,A63B51/00,G06M1/00,G06F3/00,H04N23/00,H04N25/00,H04N13/00,G05B19/00,H04N5/00,H05G1/00,H04N1/00,G03B7/00,G01C11/00,H01S3/00,G01J5/00,G03B35/00,B23Q35/00,B62M6/00,H02M1/00,H01J31/00,G03B39/00,G01S13/00,G03B21/00,H10K39/00,H05G1/00,H01J37/00,G01J1/00,G11B7/00,G01N23/00,G01T1/00,H01J31/00,H01J3/00,H01Q3/00,H01J29/00,G01S3/00,A61B6/00,G01J5/00,H01J35/00,H04N5/00,G09G1/00,H04N1/00,G01V5/00,G01J3/00,H01J25/00,H01Q3/00,H05G1/00,G01J5/00,B01D61/00,F16H55/00,H03K3/00,D01H5/00,G01R33/00,G01D5/00,B27B31/00,H04N1/00,H01J3/00,H03K17/00,G21K1/00,B60W50/00,H03B9/00,D01F9/00,G01S3/00,D21H23/00,C10G9/00</t>
+  </si>
+  <si>
+    <t>A61G7/00,A47C17/00,A47B23/00,A61G1/00,B62D33/00,G05B19/00,G05G9/00,G05D13/00,B23Q1/00,F16H3/00,H04N23/00,H04N25/00,H04N13/00,H05G1/00,G05B19/00,H05G1/00,G01N23/00,G01T1/00,H01J37/00,H01J3/00,H05G1/00,G01R33/00,G01D5/00,F16H55/00,H03K3/00</t>
+  </si>
+  <si>
+    <t>A61M60/00,B01D35/00,A61M1/00,B01D29/00,A61B5/00,B01D61/00,B01D33/00,B01D25/00,G16H10/00,B61G1/00,B60L1/00,G01N33/00,B07B11/00,B05B15/00,A47K7/00,B01D46/00,G16H30/00,F02M35/00,G16H50/00,A47L15/00,A61M60/00,B41J5/00,A61M1/00,G11B15/00,B01D61/00,B41B27/00,G11B27/00,F16H55/00,B01D29/00,G06F7/00,A23C9/00,H04N5/00,G11B7/00,G05B19/00,G11B25/00,B66B1/00,H04N21/00,G01D9/00,H04N1/00,A61B5/00,G06F16/00,G06V10/00,G06T7/00,G06F18/00,H04H60/00,G10L25/00,G01D9/00,G10L17/00,G11B27/00,G10L19/00,H04L41/00,G10L21/00,H04N21/00,H04M1/00,G06V30/00,G02F1/00,H04L67/00,G07D7/00,G06T5/00,G01N29/00,G04C23/00,G06V10/00,G06F18/00,G06T7/00,H03L7/00,H04N25/00,G10L19/00,A61B5/00,G10L21/00,G01D9/00,G01P3/00,G01N29/00,G04C21/00,G01F1/00,G08C19/00,H04L41/00,G10K1/00,F23N5/00,G01N30/00,H04M15/00,H04M1/00,B60K35/00,H04W68/00,G04C21/00,H04L41/00,B60G17/00,G08B29/00,H04N21/00,G06F11/00,G06M3/00,A61M60/00,B60W50/00,A61B5/00,G07C1/00,G16H10/00,G11B15/00,H04H60/00,F21V29/00,G03B7/00,B60L1/00</t>
+  </si>
+  <si>
+    <t>A61M60/00,B01D61/00,A61M1/00,G16H10/00,A61B5/00,A61M60/00,A61M1/00,B01D61/00,G06F7/00,G11B27/00,G06F16/00,G06F18/00,G01D9/00,G11B27/00,G06T7/00,G06F18/00,A61B5/00,G01D9/00,G06T7/00,G04C23/00,H04W68/00,G08B29/00,G06F11/00,G04C21/00,H04N21/00</t>
   </si>
 </sst>
 </file>
@@ -674,7 +667,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="1">
     <dxf>
       <font>
         <b val="0"/>
@@ -693,48 +686,6 @@
         <charset val="128"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -761,22 +712,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}" name="表2" displayName="表2" ref="I1:S26" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="I1:S26" xr:uid="{B09BA5AD-1E89-484C-9C68-7B403F3A0F56}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2082C9BA-CBF1-4F86-AD06-97A3396FFC3F}" name="表2" displayName="表2" ref="I1:S26" totalsRowShown="0">
+  <autoFilter ref="I1:S26" xr:uid="{2082C9BA-CBF1-4F86-AD06-97A3396FFC3F}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{668323CC-C691-4B3E-9439-CA42E7EA43F7}" name="middle_main_hit_count"/>
-    <tableColumn id="2" xr3:uid="{2AEC24EC-0005-48E6-A62B-724BD7DEF298}" name="middle_main_miss_count"/>
-    <tableColumn id="3" xr3:uid="{296F10EE-168B-4A76-91E8-AD2AA5FD245B}" name="middle_all_hit_count"/>
-    <tableColumn id="4" xr3:uid="{BCBCAEFC-B480-4DD8-AB56-2C6F0711A6EB}" name="middle_all_miss_count"/>
-    <tableColumn id="5" xr3:uid="{39AA68BB-B3B6-4BE5-A595-97711FFF28FE}" name="final_main_hit_count"/>
-    <tableColumn id="6" xr3:uid="{500C2E05-0458-4856-BBF7-E6CF48F9C67C}" name="final_main_miss_count"/>
-    <tableColumn id="7" xr3:uid="{039B68DD-843B-40BE-AE5A-D6757A744BB1}" name="final_all_hit_count"/>
-    <tableColumn id="8" xr3:uid="{06BC69B4-9933-4DBD-9834-D689A8B513BC}" name="final_all_miss_count"/>
-    <tableColumn id="9" xr3:uid="{E3C38C6F-432E-4566-8376-483C704A6042}" name="actual_all_ipc_count"/>
-    <tableColumn id="10" xr3:uid="{74934023-1831-42EC-996B-51104C7C684B}" name="middle_predicted_ipc_count"/>
-    <tableColumn id="15" xr3:uid="{242EE457-F26C-4D60-ABB9-6E6888A4AA7C}" name="final_predicted_ipc_count"/>
+    <tableColumn id="1" xr3:uid="{D0A4EA6B-EBB3-4AEF-97AA-D9F4EEFE61A8}" name="actual_all_ipc_count"/>
+    <tableColumn id="2" xr3:uid="{56EF71F3-3D01-4C5C-A94D-A7F2E43828CE}" name="middle_predicted_ipc_count"/>
+    <tableColumn id="3" xr3:uid="{54C8BBCA-28D2-4EE9-91DC-57A22859F15E}" name="middle_main_hit_count"/>
+    <tableColumn id="4" xr3:uid="{20A7E4E7-06BA-42CA-B498-96DFD833EFD9}" name="middle_main_miss_count"/>
+    <tableColumn id="5" xr3:uid="{AB95CAD9-E0C4-4E60-BC42-9D4823211F45}" name="middle_all_hit_count"/>
+    <tableColumn id="6" xr3:uid="{E747A284-031F-4278-934B-81318A5D0CE1}" name="middle_all_miss_count"/>
+    <tableColumn id="7" xr3:uid="{7CCB3695-2C3A-453E-A9F5-28AE4AA85186}" name="final_predicted_ipc_count"/>
+    <tableColumn id="8" xr3:uid="{12D608B1-FBDD-4C3E-8658-831EE5BB9DF4}" name="final_main_hit_count"/>
+    <tableColumn id="9" xr3:uid="{C0A99FDD-0D0B-4C51-A208-B1E1F955F177}" name="final_main_miss_count"/>
+    <tableColumn id="10" xr3:uid="{68A54F4C-9488-4E36-9D2C-29867F8FCF5B}" name="final_all_hit_count"/>
+    <tableColumn id="11" xr3:uid="{B4EB9896-267F-40CC-8DDD-92253A87B0D5}" name="final_all_miss_count"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1085,16 +1036,16 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.45" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" ht="18.45" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
@@ -1162,9 +1113,7 @@
     <col min="6" max="6" width="8.42578125" customWidth="1"/>
     <col min="7" max="7" width="19.92578125" customWidth="1"/>
     <col min="8" max="8" width="19.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.78515625" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.78515625" customWidth="1"/>
+    <col min="9" max="19" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
@@ -1193,37 +1142,37 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="K1" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="L1" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="M1" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="N1" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="O1" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="P1" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="Q1" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="R1" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="S1" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
@@ -1246,43 +1195,43 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>16</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
         <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>2</v>
-      </c>
-      <c r="Q2">
-        <v>3</v>
-      </c>
-      <c r="R2">
-        <v>76</v>
-      </c>
-      <c r="S2">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -1290,58 +1239,58 @@
         <v>2019000021</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F3" s="3">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>81</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
         <v>19</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>2</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>2</v>
-      </c>
-      <c r="R3">
-        <v>81</v>
-      </c>
       <c r="S3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -1349,31 +1298,29 @@
         <v>2019000028</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1382,25 +1329,25 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -1408,31 +1355,29 @@
         <v>2019000046</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1447,19 +1392,19 @@
         <v>1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
@@ -1467,31 +1412,29 @@
         <v>2019000051</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1506,19 +1449,19 @@
         <v>1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
@@ -1526,31 +1469,31 @@
         <v>2019000055</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1565,19 +1508,19 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
@@ -1585,58 +1528,58 @@
         <v>2019000059</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
@@ -1644,31 +1587,29 @@
         <v>2019000061</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1683,19 +1624,19 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
@@ -1703,58 +1644,58 @@
         <v>2019000064</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
         <v>1</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
@@ -1762,58 +1703,58 @@
         <v>2019000102</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>3</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
       <c r="O11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>3</v>
-      </c>
-      <c r="Q11">
-        <v>3</v>
-      </c>
-      <c r="R11">
-        <v>66</v>
-      </c>
-      <c r="S11">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
@@ -1821,31 +1762,29 @@
         <v>2019000125</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1860,19 +1799,19 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
@@ -1880,31 +1819,29 @@
         <v>2019000169</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1919,19 +1856,19 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
@@ -1939,46 +1876,46 @@
         <v>2019000190</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1987,10 +1924,10 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
@@ -1998,46 +1935,44 @@
         <v>2019000203</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2046,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
@@ -2057,46 +1992,44 @@
         <v>2019000223</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2105,10 +2038,10 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
@@ -2116,31 +2049,31 @@
         <v>2019000227</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -2155,19 +2088,19 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
@@ -2175,31 +2108,29 @@
         <v>2019000246</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2214,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2223,10 +2154,10 @@
         <v>1</v>
       </c>
       <c r="R18">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
@@ -2234,46 +2165,44 @@
         <v>2019000249</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2282,10 +2211,10 @@
         <v>1</v>
       </c>
       <c r="R19">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
@@ -2293,31 +2222,31 @@
         <v>2019000250</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2329,22 +2258,22 @@
         <v>1</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
@@ -2352,31 +2281,29 @@
         <v>2019000266</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2391,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2400,10 +2327,10 @@
         <v>1</v>
       </c>
       <c r="R21">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
@@ -2411,58 +2338,56 @@
         <v>2019000277</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="F22" s="2">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P22">
         <v>1</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
@@ -2470,37 +2395,35 @@
         <v>2019000293</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -2509,19 +2432,19 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P23">
         <v>1</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
@@ -2529,31 +2452,31 @@
         <v>2019000297</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2568,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
@@ -2588,31 +2511,31 @@
         <v>2019000302</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="F25" s="3">
         <v>1</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2627,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -2636,10 +2559,10 @@
         <v>1</v>
       </c>
       <c r="R25">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
@@ -2647,58 +2570,58 @@
         <v>2019000311</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I26">
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P26">
         <v>1</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="S26">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenhe\Desktop\Test\知财PoC\IPC_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CA53C9-CF57-4527-9E50-79E339E6C2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40544253-452F-4645-B2C5-D8CB70224A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{685DA10D-DEC5-4705-BAF0-A25F74872425}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="sample" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sample!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sample!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="192">
   <si>
     <t>publication-doc-number</t>
   </si>
@@ -205,54 +205,6 @@
   </si>
   <si>
     <t>A63F7/02</t>
-  </si>
-  <si>
-    <t>【課題】演出に関する設定について改良した遊技機を提供することを目的とする。 【解決手段】この遊技機は、メニュー状態を経由して制御された音量設定状態は、時間の経過で終了するため、いつまでも音量設定画像が液晶表示器５１に表示され続けることを防止することができ、さらに、遊技状態から直接的に制御された音量設定状態も、時間の経過で終了するため、いつまでも音量設定画像が液晶表示器５１に表示され続けることを防止することができる。</t>
-  </si>
-  <si>
-    <t>【課題】電気部品が意図せずに動作してしまうことを防止できる遊技機を提供すること。 【解決手段】シリアル／パラレル変換回路１には、該変換回路を動作させるための電源Ｖ ＣＣが接続されるとともに、該電源ＶＣＣは、シリアル制御信号１及びクロック信号１の 信号線のノイズを除去するためのノイズ除去回路１及びパラレル制御信号１、２の信号線 の電圧をプルアップさせるプルアップ抵抗１に接続されており、電源ＶＣＣは、２本の電 源線（ＶＣＣ１及びＶＣＣ２）を介して供給される。</t>
-  </si>
-  <si>
-    <t>【課題】従来とは異なる態様で遊技状態を移行させることで、遊技の幅を広げることができる遊技機を提供する。 【解決手段】遊技区間は、ＡＲＴを実行可能な有利区間と、ＡＲＴを実行できない通常区間と、を含み、ＡＲＴ制御手段は、ＡＲＴの実行権利を得たときに、非ＡＲＴ中であればＡＲＴを開始し、ＡＲＴ中であれば当該実行権利をストックするように構成されている。また、有利区間の終了後に移行する遊技状態には、実行権利のストック数が関連付けられている。</t>
-  </si>
-  <si>
-    <t>ゲームシステム</t>
-  </si>
-  <si>
-    <t>A63F13/493</t>
-  </si>
-  <si>
-    <t>A63F13/79;A63F13/70;A63F13/49;A63F13/792;A63F13/26</t>
-  </si>
-  <si>
-    <t>【課題】予約しているプレイヤを、待ち時間に、他のゲーム機でプレイするように促すゲームシステムを提供する。 【解決手段】ゲームシステム１、店舗内に配置されたゲーム機１０，ゲーム機２０と、ゲーム機１０のプレイ中において、次回以降のゲーム機１０のプレイの予約を予約ＩＤによって識別可能に受け付ける予約管理部４６ａとを備え、予約管理部４６ａは、ゲーム機１０でプレイが終了したことに応じてゲーム機２０でのプレイを中断し、予約ＩＤの入力に応じて、予約されたプレイをゲーム機１０で実行可能にし、予約ＩＤの入力に応じて、中断されたプレイをゲーム機２０で再開可能にする。</t>
-  </si>
-  <si>
-    <t>洗濯物干し具</t>
-  </si>
-  <si>
-    <t>D06F57/00</t>
-  </si>
-  <si>
-    <t>【課題】  多くの衣服ハンガーを識別性良く吊り下げることができ、且つ、吊り下げられた衣服ハンガーの下端部が地面に接触し難い洗濯物干し具を提供する。 【解決手段】  本発明の洗濯物干し具１０は、物干し竿３に吊り下げ可能な吊り部１３をそれぞれ有する一対の本体部材１と、前記一対の本体部材１に架設された第１架橋桿２１と、前記一対の本体部材１に架設され且つ前記第１架橋桿２１から間隔を空けて配置された第２架橋桿２２と、を有し、前記吊り部１３が、前記第１架橋桿２１と前記第２架橋桿２２の間に配設されており、前記吊り部１３を前記物干し竿３に吊り下げた際、前記第１架橋桿２１が前記第２架橋桿２２よりも上方に位置するように構成されている。</t>
-  </si>
-  <si>
-    <t>【課題】演出を好適に行うことが可能な遊技機を提供すること。 【解決手段】スロットマシン１０は、スピーカ装置６４による音演出が、各音源ＩＣによる音生成処理によって生成される音により行われる。各音源ＩＣにおいて、音生成処理は１０ｍｓｅｃ周期で更新され、所定の音情報に基づいて音の生成を行う。サブ制御装置は、音生成処理の更新周期と音演出を開始させるべき開始タイミングとのズレが生じている場合、当該ズレに相当する期間に亘って遊技者が把握困難又は把握不可となる音の生成が行われるように、音生成処理に用いられる音情報を設定する。</t>
-  </si>
-  <si>
-    <t>医療用撮像装置</t>
-  </si>
-  <si>
-    <t>A61B1/04</t>
-  </si>
-  <si>
-    <t>G02B23/24;A61B1/00</t>
-  </si>
-  <si>
-    <t>【課題】小型化及び軽量化を図りつつ、利便性の向上を図ることが可能な撮像装置を提供する。 【解決手段】医療用撮像装置５は、外装を構成するケーシング１１と、ケーシング１１内に収納され、被写体像を撮像する撮像部２１と、ケーシング１１の外面に回転可能に設けられた操作リング１４と、操作リング１４の回転を検知する検知部１７と、検知部１７の検知結果に基づいて、操作リング１４の回転方向及び回転量を算出する操作算出部２３２と、操作算出部２３２にて算出された操作リング１４の回転方向及び回転量に応じた第１の機能または第２の機能を実行する機能実行部２３３と、機能実行部２３３にて実行させる機能を第１の機能または第２の機能に切り替える機能切替部２３１とを備える。</t>
-  </si>
-  <si>
-    <t>【課題】技量に自信を持っている遊技者にとっても興趣に富んだ遊技機を提供すること。 【解決手段】第１の役が内部当籤役として決定された場合において特定の図柄表示手段に対する停止操作が第１のタイミングで行われた場合、特定の図柄表示手段において複数の図柄が第１の態様で停止表示され、その後第１の図柄組合せを停止表示させることができる。第２の役が内部当籤役として決定された場合において当該停止操作が第１のタイミングで行われた場合、特定の図柄表示手段において複数の図柄が第２の態様で停止表示され、その後第２の図柄組合せを停止表示させることができる。第３の役が内部当籤役として決定された場合において当該停止操作が第２のタイミングで行われた場合、特定の図柄表示手段において複数の図柄が第１の態様で停止表示され、その後第１の図柄組合せを停止表示させることができる。</t>
   </si>
   <si>
     <t>パンツタイプ使い捨ておむつ</t>
@@ -351,154 +303,331 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>A23C9/00,A21D13/00,C09K8/00,A23L7/00,A23C11/00,A23L29/00,A23C15/00,G03C1/00,A21D2/00,A21D8/00,C08F2/00,C04B103/00,C09D1/00,B32B27/00,A23F5/00,C08B30/00,A23C19/00,A61K47/00,D06L4/00,B05D7/00,C09K8/00,G01N33/00,B01F101/00,A23C15/00,A23L33/00,C11C3/00,C08G63/00,A21D8/00,A21D10/00,C10M127/00,C10G71/00,C08K13/00,C10N30/00,B65D85/00,A23D9/00,A23C19/00,A23P10/00,C10M101/00,A23G1/00,A23D7/00,C12N9/00,C12P19/00,C12Q1/00,C23G1/00,D21H23/00,A23C9/00,A21D8/00,C09D1/00,C09K8/00,C12G1/00,A23L13/00,A23C19/00,A21D2/00,A23L2/00,C12N15/00,A23K10/00,C09D7/00,A23L3/00,A23K30/00,A23C13/00,C23C22/00,C09K8/00,A23L33/00,A21D2/00,A21D13/00,C09D1/00,C12Q1/00,C08G63/00,C04B35/00,C07F9/00,C07C47/00,A21D8/00,C09K23/00,C08K13/00,C07C51/00,C09B43/00,D01F6/00,C11D3/00,A23C9/00,A61K31/00,A23L7/00,B29C48/00,B28B21/00,A21D13/00,B65B25/00,A21D8/00,C08J9/00,B29C70/00,B28B11/00,A23G3/00,A21C3/00,A23P10/00,B21D22/00,C03B23/00,B23P9/00,B21D26/00,B01D25/00,D21H23/00,B29C44/00,B31D5/00</t>
-  </si>
-  <si>
-    <t>A21D13/00,A21D2/00,A21D8/00,A23L7/00,A23L29/00,A21D8/00,A21D10/00,A23L33/00,C11C3/00,B01F101/00,C12N9/00,C12P19/00,C12Q1/00,A21D8/00,A23C9/00,A23L33/00,A21D2/00,A21D13/00,C12Q1/00,C09K8/00,A23L7/00,A21D13/00,A21D8/00,C08J9/00,B29C48/00</t>
-  </si>
-  <si>
-    <t>A23G3/00,H01M50/00,C09K8/00,B32B37/00,B29C48/00,A23P20/00,C03C25/00,A23G1/00,A21D13/00,B65D75/00,D04H1/00,H01M8/00,B29C64/00,C08G63/00,G11B7/00,B29C43/00,B29C39/00,B29C41/00,B32B25/00,B29C63/00,C09K8/00,A23G1/00,A23F5/00,D21H23/00,A21D13/00,A23C19/00,C08F2/00,A23P20/00,A23G3/00,C12C7/00,B29C70/00,B01J19/00,B01D53/00,C08F20/00,C08F120/00,C08F220/00,B41M5/00,A61P17/00,A01N25/00,D21H19/00,A61K31/00,C07H3/00,C12P19/00,C07H19/00,C12C7/00,C08F2/00,C08G18/00,C09K23/00,A23C19/00,C06B45/00,A61K9/00,A23G3/00,B01F101/00,C13B50/00,C12Q1/00,A23L33/00,C08G63/00,A23P20/00,C13K1/00,A23G9/00,C23C8/00,C21D1/00,B29C53/00,C25D5/00,C08J7/00,C23C22/00,H01L21/00,B05D5/00,C03B27/00,B24C1/00,C23C18/00,C23C10/00,C23C2/00,B28B1/00,C03C15/00,C10L9/00,C21D5/00,B05D3/00,C23D13/00,C23C16/00,A21D13/00,C09K8/00,A23L33/00,A23G3/00,A23B4/00,A23C15/00,C10N30/00,A23B7/00,A23P10/00,B01F101/00,A23C19/00,A23B9/00,A23B5/00,A23G1/00,A23L7/00,A23D9/00,G01N33/00,A23D7/00,A23P20/00,A01J27/00</t>
-  </si>
-  <si>
-    <t>A23G3/00,A23P20/00,A23G1/00,A21D13/00,B32B37/00,A23G1/00,A21D13/00,A23P20/00,A23G3/00,A23C19/00,C07H3/00,C12P19/00,C07H19/00,C09K23/00,C06B45/00,C21D1/00,B05D5/00,C08J7/00,C03B27/00,B24C1/00,A21D13/00,A23L33/00,A23G3/00,A23P10/00,A23B4/00</t>
-  </si>
-  <si>
-    <t>B65G53/00,C10J3/00,F24F3/00,A23L3/00,B65B55/00,C10B21/00,C23C16/00,F23D14/00,F27D7/00,C02F1/00,C12M1/00,H01J61/00,B07B11/00,B01J38/00,A61M16/00,F16F9/00,H01J7/00,F27B7/00,F27B5/00,B01D53/00,F24F1/00,H01M50/00,H01R13/00,H02B11/00,E06B3/00,H01P1/00,G21C19/00,B04C5/00,E04B2/00,E06B9/00,F01N1/00,H01F41/00,B65H3/00,E06B7/00,B03C3/00,F02C7/00,H01L21/00,F16L59/00,H01B7/00,E04B1/00,F24F3/00,F24F1/00,B01D46/00,A47L5/00,F01N3/00,F01P5/00,F02M35/00,F02M26/00,F24F11/00,F23N1/00,F24F7/00,F02F1/00,B60H1/00,F01P7/00,F23D14/00,B01D35/00,F23C10/00,F04D25/00,E03D9/00,A47L15/00,F24F1/00,B01D29/00,B01D33/00,B29C45/00,F27B7/00,F27B5/00,B01D25/00,F27B15/00,F27B1/00,B29C48/00,F02B25/00,G05B11/00,F23C10/00,B05B14/00,F23K5/00,F27B14/00,F27B9/00,F02M35/00,F02C6/00,F23C7/00</t>
-  </si>
-  <si>
-    <t>F24F3/00,F27D7/00,A23L3/00,B65B55/00,B65G53/00,F24F1/00,E06B3/00,E06B9/00,E04B2/00,B04C5/00,F24F3/00,F24F1/00,B01D46/00,F24F11/00,F01N3/00,F24F1/00,B01D29/00,B01D33/00,B01D25/00,B29C45/00</t>
-  </si>
-  <si>
-    <t>A61F13/00,B41M5/00,B32B5/00,H01M50/00,D21H27/00,F24S70/00,B65D81/00,B62J1/00,A61F5/00,A61L15/00,B32B3/00,G09F11/00,G03F1/00,C04B41/00,B01D24/00,D01G15/00,B32B25/00,B65B11/00,B41J17/00,B29C63/00,H01M50/00,B29C63/00,B65D90/00,B29C73/00,B65H63/00,B29C48/00,B67D7/00,B01J19/00,B05B15/00,B23K35/00,A23L3/00,G09F11/00,G01N23/00,B65B1/00,F42B3/00,E04F13/00,F01D5/00,F16L55/00,G02B1/00,F16L11/00,E04B2/00,B60R21/00,A61F13/00,B64D25/00,B60V1/00,F02K1/00,A47C1/00,B29C48/00,B60J10/00,B62J1/00,B65D81/00,B60N2/00,B65D75/00,B65D90/00,F16K1/00,C01B3/00,A47C7/00,A47C4/00,G01L5/00,B29C64/00,A61F13/00,A61L15/00,B65B35/00,H01M4/00,B65B41/00,B65B43/00,F24S70/00,B65D81/00,A61L17/00,C07C7/00,B65B1/00,B01D39/00,H01J29/00,A01N25/00,G21F9/00,B01J47/00,F16L59/00,C09K8/00,B01D24/00,D06B23/00</t>
-  </si>
-  <si>
-    <t>A61F13/00,B32B5/00,A61L15/00,D21H27/00,F24S70/00,B29C63/00,B29C73/00,B01J19/00,B65D90/00,B29C48/00,A61F13/00,B29C48/00,B60J10/00,E04B2/00,B60R21/00,A61F13/00,A61L15/00,F24S70/00,A61L17/00,B65D81/00</t>
-  </si>
-  <si>
-    <t>A23L7/00,H01F1/00,A23P10/00,A23P20/00,A61K9/00,A61L15/00,A23L29/00,H01M8/00,B24D3/00,C23C10/00,C09K8/00,A23G9/00,C06B45/00,B05D1/00,A61L9/00,A61K47/00,C08C1/00,D06P1/00,B29B9/00,F28C3/00,H01M50/00,A23L7/00,C08J3/00,D04H1/00,G03F7/00,G03C1/00,C08B30/00,A21D13/00,C08F2/00,H01F1/00,B05D1/00,D06P1/00,B01F35/00,A23P10/00,C10M169/00,A23L29/00,B29B7/00,C09C1/00,B01J20/00,B29C70/00,C08F2/00,C09K8/00,B01F101/00,G01N33/00,C08J3/00,C11D10/00,A61K8/00,B01F23/00,A23P10/00,G03C1/00,C10N50/00,A23L33/00,C07C17/00,C10G71/00,A61L15/00,D06L4/00,C10M169/00,G05D11/00,A23G1/00,C08K9/00,C08J9/00,G03C1/00,A23L7/00,A23P10/00,B02C4/00,B01J2/00,C08B30/00,C07C51/00,D06P1/00,C08J5/00,C08K9/00,C08J3/00,B05D1/00,A23L29/00,B29C44/00,C23C10/00,A21D13/00,G03C7/00,E01C19/00,G03F7/00,F04B15/00,A47J31/00,H01M10/00,C10J1/00,F01P7/00,C07C4/00,F02F1/00,F24H15/00,C01F7/00,B65G53/00,G01M3/00,B01F35/00,F24F6/00,F02C1/00,G01L5/00,F24S60/00,H01L23/00,F01K25/00,F23D11/00,G01N25/00</t>
-  </si>
-  <si>
-    <t>A23L7/00,A23P10/00,A23P20/00,A23L29/00,A61K9/00,A23L7/00,C08B30/00,C08J3/00,A21D13/00,C08F2/00,B01F23/00,A23P10/00,B01F101/00,C08J3/00,C08F2/00,A23L7/00,C08B30/00,A23P10/00,B01J2/00,B02C4/00,A47J31/00,F24H15/00,B65G53/00,C10J1/00,F04B15/00</t>
-  </si>
-  <si>
-    <t>H02P3/00,D03D51/00,H01H73/00,H02P6/00,D05B69/00,B61L5/00,B65B57/00,A01B35/00,G01D11/00,F16H48/00,B43K24/00,B65G51/00,B25B23/00,B65H59/00,G05G5/00,D01H7/00,H01H3/00,B41J29/00,B61F17/00,F16H33/00,F41A19/00,B62M6/00,B66D1/00,H01H33/00,A61M60/00,H02K7/00,A01D34/00,E05F15/00,B60S9/00,F42B19/00,B08B9/00,B02C18/00,F04B17/00,E02F3/00,B60L50/00,B05B5/00,A61C17/00,F02C7/00,B21J7/00,D03D43/00,B62M6/00,B61C9/00,A01D34/00,F16C3/00,A01D78/00,F16D13/00,B63H23/00,E05F3/00,F26B11/00,B64C27/00,B60K5/00,F16H39/00,F16H37/00,F04D29/00,F16D55/00,F16D25/00,F16J1/00,A24B7/00,B62M1/00,B60K17/00,B26D1/00,A01D34/00,B26B19/00,B26B21/00,B26D5/00,A24B7/00,B24B3/00,B67B7/00,B26D7/00,B27B5/00,A63C1/00,A01D75/00,B26B13/00,B23D19/00,B62M6/00,F16D13/00,E01H5/00,B23D47/00,B23D71/00,D01G1/00</t>
-  </si>
-  <si>
-    <t>H02P3/00,D03D51/00,H01H73/00,H02P6/00,F16H48/00,B62M6/00,H02K7/00,A01D34/00,H01H33/00,B66D1/00,A01D34/00,F16C3/00,F16D13/00,B62M6/00,B61C9/00,B26D1/00,A01D34/00,B26D5/00,B26D7/00,B24B3/00</t>
-  </si>
-  <si>
-    <t>B01F25/00,B67D7/00,F24S10/00,B65G53/00,F17D1/00,F28D1/00,H01M50/00,B01F29/00,A61M5/00,B65D21/00,B65G35/00,G21C19/00,H01H29/00,F02F1/00,B30B9/00,B01D15/00,F27D3/00,F25B41/00,B05B11/00,B65G47/00,G07F11/00,B67D7/00,B01F29/00,B65D21/00,B01F31/00,B01F35/00,B30B9/00,B08B9/00,G21F5/00,B65B3/00,B65B43/00,E04H7/00,G11B15/00,G01F11/00,G21F9/00,H01J5/00,B65D6/00,B65D5/00,B65D88/00,A47F1/00,F16H61/00,F04F5/00,A61M60/00,F04D13/00,F04D29/00,F16D31/00,F16H39/00,F17D1/00,F15B9/00,F04F1/00,F04D25/00,F04B43/00,F01P5/00,B05B7/00,B05B9/00,H01M50/00,B21D26/00,F02M37/00,F24H15/00,G01N30/00,A61M60/00,A61M5/00,A61M1/00,B01F25/00,C12M1/00,F17D1/00,C12N15/00,G01P3/00,B01D15/00,H01M50/00,B05C9/00,A01D17/00,C01B3/00,B05D1/00,F04F5/00,G01N30/00,B08B9/00,B05B7/00,B65G53/00,G01N27/00,B67D7/00,C09B67/00,B05B7/00,G05D11/00,B01D17/00,G01K5/00,F17D1/00,B01J8/00,B05B12/00,G01N30/00,A47L1/00,B01F23/00,F16F9/00,F02C9/00,F16H47/00,C01B3/00,B03B5/00,B65G53/00,B05B5/00,B60S1/00</t>
-  </si>
-  <si>
-    <t>B01F25/00,B67D7/00,F17D1/00,B65G53/00,A61M5/00,B65D21/00,B67D7/00,B01F29/00,B01F31/00,B65B3/00,A61M60/00,F04D13/00,F04F5/00,F04F1/00,F04D29/00,C12M1/00,A61M1/00,A61M5/00,B01F25/00,B01D15/00,B67D7/00,B05B7/00,G05D11/00,B01D17/00,B05B12/00</t>
-  </si>
-  <si>
-    <t>C09K8/00,G03C1/00,A23L29/00,A23L33/00,A23P10/00,C04B103/00,B41M5/00,B01F23/00,D06P1/00,B02C4/00,A23G9/00,C09D11/00,E01C19/00,H01G11/00,A23L7/00,C12G3/00,A61L9/00,C08J3/00,C10M169/00,A61K8/00,A23L7/00,A23C9/00,A23L29/00,C01F7/00,A23K10/00,C09K8/00,A23L33/00,C09D1/00,A23F5/00,C08K9/00,A23G9/00,A23C19/00,A23P10/00,C12C7/00,C08B30/00,A21D13/00,A61K47/00,A23G1/00,A23L5/00,C07C231/00,B01F23/00,B22F1/00,B01F25/00,C08J3/00,B01J2/00,A61K9/00,F04F5/00,G01N15/00,A23P10/00,C08J9/00,C08F2/00,B05B1/00,B05D1/00,B29B9/00,C06B45/00,B05B7/00,B01J19/00,C09K8/00,A61M11/00,E21F5/00,B65B1/00,B65B11/00,B65B3/00,B65D21/00,B65D77/00,A23L3/00,B65B55/00,B05C7/00,H01L23/00,A23P20/00,H01J5/00,F16J15/00,B65D81/00,B01F29/00,B65B29/00,B65B5/00,B65B39/00,B65D75/00,B65B43/00,B65B31/00</t>
-  </si>
-  <si>
-    <t>A23L29/00,A23L33/00,A23P10/00,B01F23/00,B02C4/00,A23L7/00,A23L29/00,A23L33/00,A23C9/00,A23K10/00,B01F23/00,B01F25/00,C08J3/00,B01J2/00,A23P10/00,B65B3/00,B65B1/00,B65B55/00,A23L3/00,B65D21/00</t>
-  </si>
-  <si>
-    <t>A23B7/00,A23L3/00,C21D1/00,A23B9/00,G03B27/00,C01F7/00,A23B4/00,A23B5/00,A47J31/00,G03F7/00,G21C19/00,B09B3/00,D21F5/00,C10B21/00,D06M23/00,A45D4/00,F26B3/00,D21C1/00,B29C49/00,B29C70/00,C23C22/00,G03C7/00,C12G1/00,C01F7/00,B05C3/00,C08J11/00,C10K1/00,D06M23/00,B01J38/00,D06L1/00,A21D8/00,D06P1/00,C23F1/00,C07C31/00,D06B23/00,C30B7/00,C10G53/00,C22B9/00,C23F3/00,A62D3/00,C09B62/00,B41M5/00,D06P1/00,C12G3/00,A23L2/00,A23F3/00,D06P5/00,G03C7/00,A23L5/00,C12F3/00,C09D11/00,C12G1/00,B01F101/00,C12C12/00,G03C8/00,C09K8/00,A23F5/00,D06P3/00,C08F220/00,C08F120/00,H01M4/00,C10G53/00,C10G65/00,A23L2/00,A23F3/00,C12G1/00,C12G3/00,C10G67/00,C10G61/00,C12C11/00,C12C7/00,C08G69/00,C08J9/00,D04H1/00,C04B35/00,C08B1/00,C11D11/00,C10G69/00,C13B10/00,D06M23/00</t>
-  </si>
-  <si>
-    <t>A23B7/00,A23L3/00,C21D1/00,A23B9/00,A23B4/00,C12G1/00,B05C3/00,D06M23/00,C23C22/00,D06L1/00,C09B62/00,D06P1/00,C12G3/00,A23L5/00,A23F3/00,C12G3/00,A23L2/00,C12G1/00,A23F3/00,C12C11/00</t>
-  </si>
-  <si>
-    <t>G01G19/00,G01G23/00,G01G13/00,B07C5/00,B65B1/00,G01G3/00,G01G1/00,A01K39/00,G01N9/00,G01G21/00,G01G11/00,G01G17/00,G11B15/00,B65B3/00,G01G15/00,B65D41/00,B29B7/00,G01N5/00,A01K97/00,G01K17/00,G01G19/00,H04H60/00,G11B15/00,G01S13/00,A63F13/00,G11B27/00,G01V8/00,B60T8/00,A61B5/00,E05B81/00,G01G11/00,G06V20/00,G06V40/00,G07C9/00,G11B19/00,G01N29/00,B23Q35/00,G06F3/00,B65H63/00,G01C19/00,H04H60/00,G11B27/00,G07D7/00,G06K19/00,G11B15/00,H04W12/00,A61B5/00,A47G19/00,G01S13/00,G01P3/00,G06K21/00,G11B23/00,B60R25/00,G06F21/00,G06T7/00,B23Q35/00,G01D5/00,A63F13/00,B07C3/00,G01N29/00,G01G19/00,G01G23/00,B07C5/00,A23K50/00,G06F119/00,G01G13/00,G06G7/00,G01G1/00,B65B3/00,G01G15/00,A01M29/00,F16C23/00,F16C25/00,G01G21/00,G01G11/00,H04H60/00,A61B5/00,A01K39/00,A23K40/00,G01C11/00</t>
-  </si>
-  <si>
-    <t>G01G19/00,G01G13/00,G01G23/00,G01G3/00,A01K39/00,G01G19/00,A61B5/00,G01S13/00,G01V8/00,G11B15/00,A61B5/00,H04W12/00,G06K19/00,G01P3/00,A47G19/00,G01G19/00,G01G13/00,A23K50/00,G06F119/00,B07C5/00</t>
-  </si>
-  <si>
-    <t>G01G19/00,G01G23/00,B07C5/00,B65B1/00,G01G13/00,G01G3/00,G01N9/00,G01G1/00,G01G11/00,G01G17/00,G01L5/00,G01G21/00,G01G15/00,B65B37/00,G01N5/00,B65G69/00,G01F1/00,G01K17/00,B65H33/00,C12C1/00,A01F12/00,G07F11/00,C12C1/00,B65D21/00,B65D75/00,A01F25/00,B60K15/00,B63B25/00,B64D37/00,A24C5/00,B65D77/00,F15B1/00,E01B7/00,B02C7/00,A47B77/00,B65D25/00,F41A9/00,B62B1/00,G11B23/00,G21C3/00,B60P1/00,B65H39/00,B62B1/00,G07F11/00,E04G1/00,B66F7/00,A47C1/00,G09B1/00,F16L3/00,E21D15/00,E05D15/00,F16D65/00,B65G17/00,B60R9/00,H01L21/00,B60L5/00,E02F9/00,E01B21/00,G01L5/00,B65B43/00,G01G19/00,G01G23/00,G01G13/00,B07C5/00,G01G3/00,A01F12/00,B65B1/00,G01G11/00,G01G1/00,G01M1/00,G01G17/00,G01G21/00,G05B1/00,G01P3/00,G01N9/00,G05D11/00,G01G15/00,G10L21/00,G01N29/00,G01B9/00</t>
-  </si>
-  <si>
-    <t>G01G19/00,G01G13/00,G01G3/00,G01G23/00,G01G17/00,A01F12/00,A01F25/00,B65D21/00,B60K15/00,B63B25/00,B60P1/00,B66F7/00,F16L3/00,B62B1/00,E04G1/00,G01G19/00,G01G23/00,G01G13/00,G01G3/00,G01G11/00</t>
-  </si>
-  <si>
-    <t>E04G7/00,B23B31/00,F16L3/00,F22B37/00,F16L37/00,A45D2/00,H01R33/00,B65D43/00,F16B12/00,B27B29/00,E01B9/00,B27G13/00,B65D35/00,F16G11/00,B23D41/00,B25B5/00,B23Q1/00,B21C1/00,A45D6/00,B65B13/00,G01G19/00,G01L5/00,G01F1/00,G01G3/00,F16F1/00,G01G13/00,G01L23/00,G01L13/00,E21D15/00,A61M60/00,G01G23/00,B61K9/00,G01G11/00,D03D49/00,B21B19/00,B65G43/00,B60T8/00,G21C17/00,B65H63/00,G01L1/00,B65B11/00,F16L55/00,E21B47/00,F16L37/00,B65B9/00,A61F2/00,B65G51/00,B65D75/00,H01H33/00,B61L21/00,B61L23/00,A61M60/00,A63B41/00,E03C1/00,A61M39/00,F16K21/00,H01M10/00,F16L9/00,B31C1/00,H01J19/00,A61M60/00,B01D35/00,B01D61/00,A61B90/00,H02B1/00,A61B50/00,G21C19/00,F41A9/00,B01D25/00,E04B2/00,F16B12/00,C40B60/00,B21B39/00,F02M37/00,B41L38/00,B30B9/00,F22B37/00,B60K35/00,B01D29/00,A61M5/00</t>
-  </si>
-  <si>
-    <t>F16L3/00,B23B31/00,F16L37/00,B65D43/00,B27B29/00,G01G19/00,G01L5/00,G01F1/00,G01G3/00,G01L23/00,F16L55/00,A61F2/00,F16L37/00,B65G51/00,B65B11/00,A61M60/00,B01D61/00,A61B50/00,B01D35/00,A61B90/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G05B19/00,B60K35/00,A63F7/00,H04N23/00,H01H13/00,G01S7/00,C01B21/00,A01B41/00,B41F33/00,B60L1/00,B64G1/00,B64D25/00,H04N19/00,H03K17/00,B60S9/00,B62M6/00,B60W50/00,A63J5/00,H04N21/00,A63F13/00,H03G9/00,B01D61/00,F16H61/00,H03G3/00,G05F1/00,H02M7/00,G05D1/00,G05B19/00,H01S3/00,B60K35/00,G06F3/00,G10H1/00,A61F13/00,B61L3/00,F24F11/00,B21D26/00,G03B7/00,B62M6/00,D06F34/00,A63F13/00,G09G5/00,B60K35/00,G06F3/00,H01J31/00,G05B19/00,G01S7/00,H02M7/00,G02F1/00,G09G3/00,G03B7/00,H04H60/00,G08G1/00,H04N9/00,G08B5/00,H04N21/00,G03G15/00,D06F34/00,G09G1/00,H04N13/00,G04C23/00,G06F1/00,G04B23/00,G04C21/00,H01H43/00,G08B5/00,G07C1/00,G01S3/00,F24F11/00,H04M1/00,H01H73/00,G04B21/00,B67D7/00,H04M15/00,H02P8/00,H03G9/00,G07C3/00,G03B7/00,G07C5/00,G10K1/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G05B19/00,A63F7/00,B41F33/00,H01H13/00,A63F13/00,H03G9/00,H03G3/00,G05F1/00,G05B19/00,A63F13/00,G09G5/00,G06F3/00,G02F1/00,G09G3/00,G04C23/00,G06F1/00,H01H43/00,G07C1/00,G08B5/00</t>
-  </si>
-  <si>
-    <t>H03M1/00,H03K17/00,H04N25/00,H04N5/00,H04N9/00,G06F7/00,H04Q3/00,H04L27/00,H04L25/00,A63F13/00,H03F3/00,G01R31/00,H04N11/00,H04Q1/00,H02M7/00,H04N1/00,G11C16/00,G11C11/00,H04B3/00,A01B3/00,H03K17/00,H04B3/00,H04N25/00,H04N23/00,H04N5/00,G08B29/00,H04B1/00,H04L27/00,H04N9/00,H04M1/00,G11C16/00,H04N1/00,H02J3/00,G01C19/00,H04L25/00,H02M1/00,G10L21/00,H04N21/00,H03G1/00,F02D41/00,H03K17/00,H03K3/00,H05B45/00,G11C11/00,H01R12/00,G05F1/00,G09F11/00,H02M7/00,H02M1/00,H05B41/00,H04N5/00,G05B19/00,H04N25/00,F16H61/00,B60L15/00,G08B29/00,H03K21/00,H05B47/00,G11C7/00,H02P3/00,H02M7/00,H02J3/00,B60L1/00,B60L9/00,H02M1/00,H03K17/00,H02P27/00,H02J1/00,H04N3/00,G05F1/00,H01Q5/00,H02J9/00,G06F1/00,F21S9/00,H03K3/00,H05B7/00,H01Q9/00,H05B45/00,H04Q1/00,H02J50/00</t>
-  </si>
-  <si>
-    <t>H03K17/00,G06F7/00,H03M1/00,A63F13/00,H04L25/00,H03K17/00,H04B3/00,G08B29/00,H04B1/00,H04L27/00,H03K17/00,H03K3/00,G05F1/00,H01R12/00,H02M7/00,H02M7/00,H02J3/00,H02M1/00,H02J1/00,G05F1/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,H03K17/00,G05B19/00,G05D1/00,B60T8/00,B60W20/00,H04N5/00,B60W10/00,H02P1/00,H04L49/00,B60W30/00,G11B15/00,B61L27/00,F24F11/00,G05G7/00,H04H20/00,G21C7/00,B60L1/00,G03B7/00,G06F13/00,G05D1/00,B60W30/00,G09F11/00,E05B81/00,B60L15/00,B60W50/00,F15B9/00,B23Q15/00,H04N23/00,B60T8/00,B60W10/00,H04N5/00,A63F13/00,H02M3/00,B60K35/00,B61G1/00,H04N21/00,H02M7/00,B43K24/00,H03K17/00,H04N21/00,H04L47/00,H04L67/00,G06F13/00,H04W72/00,G06F21/00,H04N19/00,H04L45/00,H04L12/00,G05B19/00,G05D1/00,G06F12/00,G07D11/00,H03K17/00,G07C5/00,H02P8/00,H04W4/00,G07C3/00,G06F1/00,G11B19/00,A63F13/00,B60W10/00,A63F7/00,G09F11/00,G05B19/00,G05D1/00,B60W50/00,G04C23/00,E02F3/00,B61L27/00,H02M3/00,D06F33/00,B61G1/00,D06F34/00,B64C13/00,F02D11/00,B60W30/00,F15B11/00,A01D34/00,B64G1/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,G05B19/00,H03K17/00,H04N5/00,G05D1/00,G09F11/00,F15B9/00,B23Q15/00,B60W50/00,B60W30/00,H04N21/00,H04L47/00,H04L67/00,G06F13/00,G05B19/00,A63F13/00,A63F7/00,G05B19/00,G04C23/00,G09F11/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,H04N21/00,H04L67/00,H04L47/00,G06F1/00,B41B27/00,G05D1/00,H04N5/00,H04M1/00,G05B19/00,G11B20/00,B61G1/00,B60W30/00,B60T11/00,H04L41/00,G11B17/00,H01S3/00,G11B19/00,H04N1/00,H04Q3/00,A63F13/00,G08B5/00,G11B11/00,D03D51/00,H02P8/00,E06B9/00,H04L65/00,G05D1/00,H01H71/00,H01H73/00,H04L67/00,G06F1/00,H01H43/00,G10H3/00,B41B27/00,E01F9/00,H04N5/00,H04L41/00,H01M8/00,G11B20/00,A63F13/00,H04L12/00,H04N21/00,H04H60/00,H04L67/00,H04H20/00,H04M1/00,H04W88/00,G06F13/00,H04Q5/00,H04L47/00,H04L61/00,H04W68/00,H04W92/00,H04Q3/00,G06F15/00,H04L51/00,H02P5/00,H02K3/00,H10K59/00,A63F13/00,H04L65/00,H04L67/00,H04W68/00,G04C21/00,H04N21/00,H04M3/00,G06F13/00,G04C23/00,H04M1/00,H04L41/00,H04L47/00,H04W4/00,H04W76/00,H04H60/00,B64D17/00,D01H5/00,H04L45/00,H04W24/00,H04L69/00</t>
-  </si>
-  <si>
-    <t>A63F13/00,H04N21/00,H04L67/00,G06F1/00,G05B19/00,A63F13/00,H04L65/00,G08B5/00,G11B11/00,G05D1/00,A63F13/00,H04L12/00,H04L67/00,G06F13/00,H04N21/00,A63F13/00,H04L65/00,H04W68/00,H04N21/00,H04L67/00</t>
-  </si>
-  <si>
-    <t>A47G25/00,D06F58/00,D06F33/00,A47H1/00,A47K10/00,E03C1/00,D06F71/00,A41F11/00,D06F105/00,D06F103/00,A47F7/00,D06F53/00,A45C13/00,D01H13/00,D06F59/00,A41D27/00,A41H9/00,A41D13/00,F16L3/00,D06F1/00,A47G25/00,H01R13/00,E05B67/00,B08B17/00,A41F11/00,B64C25/00,H01R4/00,E05C17/00,B60L5/00,A61F13/00,B65H31/00,A43B7/00,B66B5/00,B65D25/00,A47F7/00,A41H9/00,E04H17/00,H01R33/00,H02B1/00,B66C1/00,E06C1/00,B01F27/00,E04G1/00,E04G17/00,A47G25/00,F16D3/00,A47C20/00,D06F53/00,E21D15/00,A01D37/00,E01D15/00,F16S3/00,A61K31/00,E04F11/00,E05C9/00,D06F57/00,A47C23/00,C07D491/00,C07D497/00,C07D493/00,A47H1/00,A47G25/00,E05C17/00,E04G17/00,G09F7/00,A47H3/00,E05C19/00,D06F53/00,H01L23/00,F16J13/00,B65B43/00,E03C1/00,B65H9/00,D05C11/00,B60M1/00,E04H17/00,A43B21/00,H01Q1/00,D06F57/00,H02K1/00</t>
-  </si>
-  <si>
-    <t>A47G25/00,D06F58/00,A41F11/00,A47H1/00,D06F71/00,A47G25/00,A41F11/00,B08B17/00,E05C17/00,A61F13/00,A47G25/00,D06F53/00,E06C1/00,E04G1/00,E04G17/00,A47G25/00,D06F53/00,A47H3/00,A47H1/00,E05C17/00</t>
-  </si>
-  <si>
-    <t>G10H1/00,G10L13/00,A63F13/00,G10H5/00,G10L25/00,G10K11/00,G10L15/00,H03G9/00,H01S3/00,G10L19/00,G04C21/00,H04N5/00,H03K3/00,H03B5/00,G10L21/00,G10K15/00,G01S19/00,H03J7/00,H03G3/00,G04B23/00,H03L7/00,G10H1/00,G04C23/00,H04N5/00,H03G9/00,G04C21/00,A63F13/00,H04N21/00,H04N9/00,H03D3/00,H03K3/00,H03G3/00,H04N13/00,H03K5/00,H01S3/00,G08G1/00,H01H19/00,H03J1/00,G10L21/00,H04L47/00,A63F13/00,G10H1/00,B61G1/00,G10L13/00,G01S7/00,B60K35/00,H01S3/00,G10K15/00,A63J5/00,G10C3/00,H04M3/00,G11B17/00,G10K11/00,G10L25/00,A63H17/00,C10G9/00,G01F1/00,H04R3/00,C01B21/00,G06F9/00,A63F13/00,G10H1/00,H03G9/00,G09F11/00,G10L13/00,G10L25/00,H03G3/00,G10K11/00,H04M1/00,H04N5/00,H02M7/00,H03J7/00,B60K35/00,B60W50/00,H04H60/00,G10L21/00,H01S3/00,H04B1/00,F24F11/00,H04M3/00</t>
-  </si>
-  <si>
-    <t>G10H1/00,G10L13/00,G10H5/00,G10L19/00,A63F13/00,H03L7/00,G10H1/00,G04C23/00,H03G9/00,A63F13/00,A63F13/00,G10H1/00,G10K15/00,A63J5/00,G10L13/00,A63F13/00,G10H1/00,H03G9/00,G10L25/00,G10K11/00</t>
-  </si>
-  <si>
-    <t>H04N23/00,G03B17/00,F21K9/00,H04N5/00,G11B7/00,A61B6/00,G01C19/00,G02B27/00,H05K7/00,F04B1/00,B64D27/00,A61B90/00,G02F1/00,G16H30/00,B29B7/00,H01J37/00,A61B17/00,B62J6/00,G03G15/00,B64U20/00,H04N23/00,H04N25/00,G03B17/00,H04N13/00,G06V10/00,H04N5/00,H04N1/00,H01L31/00,G02B9/00,G03G15/00,G03C8/00,B41B15/00,H01J31/00,G03B37/00,G01C11/00,G02F1/00,H05G1/00,G03B19/00,G03B7/00,H01L27/00,G01C19/00,H01H19/00,B43K24/00,F41A3/00,H01H73/00,H01H3/00,F16K41/00,F16D1/00,G06F3/00,H01H33/00,E05F15/00,D01H7/00,B41J33/00,F16H15/00,G05G1/00,E04H6/00,H03J5/00,H01H9/00,H02K11/00,F16D3/00,H01H19/00,E05F15/00,H02P21/00,G04C23/00,H01H3/00,H02M7/00,G05G1/00,H01H73/00,F16D43/00,H01H41/00,H01H13/00,G06F3/00,G08B5/00,H01H15/00,G05G9/00,B41J33/00,G05G7/00,H01H33/00,H02P7/00,F16L37/00,H04N23/00,A61B6/00,A61B5/00,A61B3/00,A61B90/00,A61B1/00,A61B34/00,B64U101/00,A61M60/00,G02B27/00,B60R1/00,A61B50/00,G16H40/00,G16H30/00,H04N5/00,G02B7/00,E04B2/00,A61N5/00,G01R33/00,G16H50/00</t>
-  </si>
-  <si>
-    <t>H04N23/00,G03B17/00,A61B6/00,H05K7/00,G02B27/00,H04N23/00,H04N25/00,G03B17/00,H01L31/00,G02B9/00,G01C19/00,H01H19/00,G06F3/00,H01H3/00,F16D1/00,H01H19/00,H01H3/00,G05G1/00,H01H41/00,G04C23/00,H04N23/00,A61B6/00,A61B5/00,A61B90/00,A61B1/00</t>
-  </si>
-  <si>
-    <t>G05B19/00,G09G5/00,C09B35/00,G09G1/00,A63F13/00,H03K17/00,G05B11/00,B60K35/00,G09B1/00,G06V10/00,G06V30/00,H04L12/00,D03C3/00,G08B5/00,B61L25/00,G06F3/00,G07C1/00,H04N19/00,G03F7/00,B60L1/00,A63F7/00,A63F13/00,G06F9/00,A63F9/00,C03B9/00,H02M7/00,G01S3/00,B30B11/00,G06V30/00,D06F13/00,A63F5/00,A63F3/00,B41J5/00,F41J5/00,G06C9/00,H02M5/00,H02M3/00,G05B19/00,G07G1/00,D03C17/00,H01H43/00,D03D51/00,B65B57/00,G04C23/00,F01D21/00,A63F13/00,H02P8/00,H01H7/00,B41F33/00,B41J29/00,H04M1/00,G07C3/00,G04F7/00,H03K17/00,B43K24/00,H05G1/00,H04M15/00,G07C1/00,D06F105/00,G07C5/00,A63F13/00,A63F7/00,E05F15/00,B60K35/00,B64C13/00,G06F3/00,F16C23/00,F16C25/00,G04C23/00,D06F33/00,H03C3/00,A01B63/00,H02M7/00,H01C10/00,B60S9/00,B43K24/00,B60P1/00,B60N2/00,G06V30/00,F16D65/00</t>
-  </si>
-  <si>
-    <t>G05B19/00,G09G5/00,A63F13/00,G09G1/00,G05B11/00,A63F7/00,A63F13/00,A63F9/00,G06F9/00,G06V30/00,H01H43/00,D03D51/00,G04C23/00,A63F13/00,H01H7/00,A63F13/00,A63F7/00,G06F3/00,G04C23/00,E05F15/00</t>
-  </si>
-  <si>
-    <t>A61F13/00,B60N2/00,B60R21/00,B64C1/00,H01M50/00,B29C63/00,A47C7/00,B62J1/00,A43B7/00,B65D88/00,F16H57/00,A47K13/00,E04F13/00,B65D51/00,F16K1/00,F23Q2/00,A47C17/00,G21C5/00,B64C3/00,B62J13/00,H01R13/00,B60R21/00,F16F15/00,A47C7/00,F16D3/00,B28B21/00,F16J15/00,B60G11/00,A47C23/00,F16F1/00,F16F3/00,B62K27/00,F16C1/00,B60C5/00,B65D41/00,E06B9/00,E21B33/00,H01H1/00,B60R19/00,B65D81/00,A61F13/00,D03D47/00,E04G7/00,D03C3/00,H01R13/00,A41D27/00,B65B43/00,E06B3/00,B65D71/00,H01M50/00,B60R21/00,A41F17/00,B65D63/00,A47G25/00,B21D26/00,F04C2/00,F04C18/00,F01C1/00,G03B9/00,B65D5/00,H01R13/00,F16D3/00,F16H15/00,A47C23/00,B66F3/00,F16D65/00,A47C7/00,E04B9/00,A61M60/00,E04B2/00,B28B21/00,G09F11/00,B60N2/00,B65D51/00,F16C7/00,H01J19/00,F16C1/00,B62D55/00,A47C3/00,B62K27/00</t>
-  </si>
-  <si>
-    <t>A61F13/00,B29C63/00,A47C7/00,B60N2/00,B62J1/00,B60G11/00,F16F1/00,A47C7/00,A47C23/00,F16F15/00,A61F13/00,A41D27/00,D03D47/00,D03C3/00,E06B3/00,A47C23/00,A47C7/00,F16D3/00,E04B9/00,E04B2/00</t>
-  </si>
-  <si>
-    <t>A43B7/00,A43D3/00,A43D100/00,A63C10/00,A43D11/00,F24F1/00,A43B13/00,A43D25/00,A41B11/00,B64C25/00,A43B9/00,B60R1/00,A47L23/00,A43D1/00,A47G25/00,D01H7/00,F16H15/00,B63B19/00,A43C15/00,B60R19/00,A47L23/00,A43B7/00,A43D3/00,A63C10/00,A43D1/00,B65D75/00,A43B3/00,A43B23/00,A43B13/00,A43B9/00,G07D11/00,B65D77/00,B62D33/00,A63C1/00,B60R7/00,H04B1/00,A43D95/00,A47B77/00,A63C3/00,E05B83/00,A63C9/00,A43D25/00,A43B7/00,A43D3/00,A43D11/00,A43D100/00,A43D1/00,A43D95/00,A43B13/00,A47G25/00,A63C10/00,A63C1/00,A43D21/00,A47L23/00,A63C11/00,A43B9/00,G05G1/00,D06F81/00,B60R22/00,A63B27/00,A43B7/00,A43D3/00,E05B77/00,A63C9/00,A43B9/00,A43B3/00,A63C10/00,A43D21/00,A43D100/00,A47L23/00,A41B11/00,B60R22/00,A43B13/00,A43D1/00,A61F5/00,A43D25/00,A43B23/00,A43B17/00,A47G25/00,A63C1/00</t>
-  </si>
-  <si>
-    <t>A43B7/00,A43D11/00,A43B13/00,A43D3/00,A43D100/00,A43B7/00,A43B3/00,A43B23/00,A43B9/00,B65D75/00,A43B7/00,A43D11/00,A43D100/00,A43B13/00,A43D25/00,A43B7/00,A43B9/00,A43B3/00,A43D100/00,A47L23/00</t>
-  </si>
-  <si>
-    <t>A47L11/00,H01R39/00,A47L5/00,B08B1/00,E04B5/00,A47L9/00,A47L13/00,B01D33/00,A61C13/00,H02M7/00,B01D46/00,A47L23/00,A46B3/00,B08B9/00,A46B17/00,A61C17/00,C01B3/00,F24F1/00,B01D29/00,C14B1/00,A47L5/00,B65D35/00,H01J19/00,H01M50/00,B66C1/00,B65B43/00,B65D43/00,B65H3/00,E04H17/00,F16L59/00,F02M69/00,H01R33/00,B65D75/00,B65D47/00,F04B37/00,B67B7/00,E05C17/00,H01L23/00,E04B2/00,B65D5/00,A47L5/00,A47L11/00,B08B9/00,A47L15/00,H01R39/00,B01D33/00,B08B1/00,B01D46/00,A47L9/00,H02M7/00,A01G20/00,B65H39/00,B05B15/00,B43K24/00,C14B1/00,B01D29/00,B62J50/00,A46B13/00,A61C17/00,B01D47/00,A47L5/00,B01D46/00,F02M35/00,F02B25/00,A61C17/00,B04C5/00,B65H3/00,B08B5/00,F02M26/00,B65G53/00,A47L11/00,A47L7/00,A47L9/00,E21B21/00,F24F13/00,B65G23/00,F02C9/00,F26B13/00,B65B1/00,F02B31/00</t>
-  </si>
-  <si>
-    <t>A47L11/00,A47L5/00,A47L9/00,A47L13/00,B08B1/00,A47L5/00,B65D35/00,B65D43/00,B65B43/00,F16L59/00,A47L5/00,A47L11/00,A47L9/00,B08B1/00,B08B9/00,A47L5/00,B01D46/00,B08B5/00,B04C5/00,B65G53/00</t>
-  </si>
-  <si>
-    <t>A47C17/00,A61G7/00,E01B3/00,B62D33/00,E01B29/00,C10B49/00,E01B9/00,A47B23/00,B63B29/00,A61G1/00,H01M50/00,H05K7/00,A47B5/00,A47B3/00,B60P3/00,B01J49/00,E04H6/00,C10B55/00,E04G1/00,E04B5/00,B23Q1/00,G05B19/00,G05G9/00,B25B13/00,F03C2/00,H02M1/00,B23C1/00,G01F1/00,G05D13/00,F16H3/00,F16H48/00,H01Q3/00,G11B5/00,G06C15/00,D03D47/00,G01S1/00,H01H1/00,A63B51/00,G06M1/00,G06F3/00,H04N23/00,H04N25/00,H04N13/00,G05B19/00,H04N5/00,H05G1/00,H04N1/00,G03B7/00,G01C11/00,H01S3/00,G01J5/00,G03B35/00,B23Q35/00,B62M6/00,H02M1/00,H01J31/00,G03B39/00,G01S13/00,G03B21/00,H10K39/00,H05G1/00,H01J37/00,G01J1/00,G11B7/00,G01N23/00,G01T1/00,H01J31/00,H01J3/00,H01Q3/00,H01J29/00,G01S3/00,A61B6/00,G01J5/00,H01J35/00,H04N5/00,G09G1/00,H04N1/00,G01V5/00,G01J3/00,H01J25/00,H01Q3/00,H05G1/00,G01J5/00,B01D61/00,F16H55/00,H03K3/00,D01H5/00,G01R33/00,G01D5/00,B27B31/00,H04N1/00,H01J3/00,H03K17/00,G21K1/00,B60W50/00,H03B9/00,D01F9/00,G01S3/00,D21H23/00,C10G9/00</t>
-  </si>
-  <si>
-    <t>A61G7/00,A47C17/00,A47B23/00,A61G1/00,B62D33/00,G05B19/00,G05G9/00,G05D13/00,B23Q1/00,F16H3/00,H04N23/00,H04N25/00,H04N13/00,H05G1/00,G05B19/00,H05G1/00,G01N23/00,G01T1/00,H01J37/00,H01J3/00,H05G1/00,G01R33/00,G01D5/00,F16H55/00,H03K3/00</t>
-  </si>
-  <si>
-    <t>A61M60/00,B01D35/00,A61M1/00,B01D29/00,A61B5/00,B01D61/00,B01D33/00,B01D25/00,G16H10/00,B61G1/00,B60L1/00,G01N33/00,B07B11/00,B05B15/00,A47K7/00,B01D46/00,G16H30/00,F02M35/00,G16H50/00,A47L15/00,A61M60/00,B41J5/00,A61M1/00,G11B15/00,B01D61/00,B41B27/00,G11B27/00,F16H55/00,B01D29/00,G06F7/00,A23C9/00,H04N5/00,G11B7/00,G05B19/00,G11B25/00,B66B1/00,H04N21/00,G01D9/00,H04N1/00,A61B5/00,G06F16/00,G06V10/00,G06T7/00,G06F18/00,H04H60/00,G10L25/00,G01D9/00,G10L17/00,G11B27/00,G10L19/00,H04L41/00,G10L21/00,H04N21/00,H04M1/00,G06V30/00,G02F1/00,H04L67/00,G07D7/00,G06T5/00,G01N29/00,G04C23/00,G06V10/00,G06F18/00,G06T7/00,H03L7/00,H04N25/00,G10L19/00,A61B5/00,G10L21/00,G01D9/00,G01P3/00,G01N29/00,G04C21/00,G01F1/00,G08C19/00,H04L41/00,G10K1/00,F23N5/00,G01N30/00,H04M15/00,H04M1/00,B60K35/00,H04W68/00,G04C21/00,H04L41/00,B60G17/00,G08B29/00,H04N21/00,G06F11/00,G06M3/00,A61M60/00,B60W50/00,A61B5/00,G07C1/00,G16H10/00,G11B15/00,H04H60/00,F21V29/00,G03B7/00,B60L1/00</t>
-  </si>
-  <si>
-    <t>A61M60/00,B01D61/00,A61M1/00,G16H10/00,A61B5/00,A61M60/00,A61M1/00,B01D61/00,G06F7/00,G11B27/00,G06F16/00,G06F18/00,G01D9/00,G11B27/00,G06T7/00,G06F18/00,A61B5/00,G01D9/00,G06T7/00,G04C23/00,H04W68/00,G08B29/00,G06F11/00,G04C21/00,H04N21/00</t>
+    <t>topics_with_codes</t>
+  </si>
+  <si>
+    <t>A23C9/00,A21D13/00,C09K8/00,A23L7/00,A23C11/00,A23L29/00,A23C15/00,G03C1/00,A21D2/00,A21D8/00,C08F2/00,C09D1/00,A23F5/00,C08B30/00,A23C19/00,G03F7/00,C04B103/00,A23C13/00,A61K47/00,D06L4/00,C09K8/00,B01F101/00,A23C15/00,A21D13/00,C08J9/00,A23G1/00,A21D8/00,A23P20/00,C08G63/00,A23L33/00,C11C3/00,A61K9/00,A62D1/00,A21D10/00,C10N30/00,C08K13/00,B65D85/00,A23P10/00,A21B5/00,A23G9/00,C12N9/00,C09K8/00,A21D8/00,D21H23/00,A23L7/00,C12P19/00,D06L4/00,C08L3/00,C09D103/00,A23C9/00,C09D1/00,C09J103/00,A23K10/00,A21D2/00,C04B38/00,C12Q1/00,C08B35/00,B01D19/00,C07K1/00,C08B33/00,B29C48/00,A21D13/00,A23L7/00,B65B25/00,B28B21/00,A21D8/00,C08G69/00,B28B3/00,B21D5/00,A23G3/00,A23P20/00,B28B11/00,B21D22/00,A21C3/00,A21C15/00,C03B23/00,B23P9/00,B22F3/00,B29B11/00,B29C44/00,C09K8/00,C23G1/00,C07C47/00,A21D13/00,A21D2/00,C23C22/00,C09D1/00,C01B15/00,C07F9/00,A23L2/00,C11D3/00,C10L9/00,C09B43/00,C07D307/00,C07D501/00,B01J38/00,C07C57/00,C04B35/00,D06L4/00,C10M145/00</t>
+  </si>
+  <si>
+    <t>合成乳化剤無添加パン生地: A23C9/00,A21D13/00,C09K8/00,A23L7/00,A23C11/00,A23L29/00,A23C15/00,G03C1/00,A21D2/00,A21D8/00,C08F2/00,C09D1/00,A23F5/00,C08B30/00,A23C19/00,G03F7/00,C04B103/00,A23C13/00,A61K47/00,D06L4/00; 油脂組成物の特性: C09K8/00,B01F101/00,A23C15/00,A21D13/00,C08J9/00,A23G1/00,A21D8/00,A23P20/00,C08G63/00,A23L33/00,C11C3/00,A61K9/00,A62D1/00,A21D10/00,C10N30/00,C08K13/00,B65D85/00,A23P10/00,A21B5/00,A23G9/00; アミラーゼ添加技術: C12N9/00,C09K8/00,A21D8/00,D21H23/00,A23L7/00,C12P19/00,D06L4/00,C08L3/00,C09D103/00,A23C9/00,C09D1/00,C09J103/00,A23K10/00,A21D2/00,C04B38/00,C12Q1/00,C08B35/00,B01D19/00,C07K1/00,C08B33/00; パン生地の作業性向上: B29C48/00,A21D13/00,A23L7/00,B65B25/00,B28B21/00,A21D8/00,C08G69/00,B28B3/00,B21D5/00,A23G3/00,A23P20/00,B28B11/00,B21D22/00,A21C3/00,A21C15/00,C03B23/00,B23P9/00,B22F3/00,B29B11/00,B29C44/00; L-アスコルビン酸の配合制御: C09K8/00,C23G1/00,C07C47/00,A21D13/00,A21D2/00,C23C22/00,C09D1/00,C01B15/00,C07F9/00,A23L2/00,C11D3/00,C10L9/00,C09B43/00,C07D307/00,C07D501/00,B01J38/00,C07C57/00,C04B35/00,D06L4/00,C10M145/00</t>
+  </si>
+  <si>
+    <t>A21D13/00,A21D2/00,A21D8/00,A23L7/00,A23L29/00,A21D8/00,A21D13/00,A23L33/00,A23C15/00,B01F101/00,C12N9/00,A21D8/00,A23L7/00,C08L3/00,C12P19/00,A21D8/00,A21D13/00,A23L7/00,B29C48/00,B28B3/00,A21D2/00,A21D13/00,C07C47/00,A23L2/00,C01B15/00</t>
+  </si>
+  <si>
+    <t>A23G3/00,H01M50/00,C09K8/00,B32B37/00,B29C48/00,A23P20/00,C03C25/00,A23G1/00,A21D13/00,B65D75/00,D04H1/00,H01M8/00,B29C64/00,C08G63/00,G11B7/00,B29C43/00,B29C39/00,B29C41/00,B32B25/00,B29C63/00,A23G1/00,C09K8/00,A23F5/00,D21H23/00,A21D13/00,A23C19/00,C08F2/00,A23P20/00,A23G3/00,C12C7/00,B29C70/00,B01J19/00,B01D53/00,C08F20/00,C08F220/00,C08F120/00,B41M5/00,A61P17/00,A01N25/00,D21H19/00,A61K31/00,C07H3/00,C12P19/00,C07H19/00,C12C7/00,C08F2/00,C08G18/00,C09K23/00,A23C19/00,C06B45/00,A61K9/00,A23G3/00,B01F101/00,C13B50/00,C12Q1/00,A23L33/00,C08G63/00,A23P20/00,C13K1/00,A23G9/00,C23C8/00,C21D1/00,C23C10/00,B29C53/00,C25D5/00,C08J7/00,C23C22/00,H01L21/00,B05D5/00,C03B27/00,H05K3/00,B24C1/00,C23C18/00,C23C2/00,B22F1/00,C03C15/00,B28B1/00,B05D3/00,C03B37/00,C21D5/00,B32B5/00,B29C48/00,A23P20/00,B29C70/00,B32B3/00,A21D13/00,B32B37/00,H01M50/00,D05C15/00,B60J10/00,A23K40/00,A23L7/00,B22F10/00,H01M8/00,B31B50/00,F24S80/00,B29D35/00,D21H19/00,F16J15/00,A23G9/00</t>
+  </si>
+  <si>
+    <t>複合油脂性菓子構造: A23G3/00,H01M50/00,C09K8/00,B32B37/00,B29C48/00,A23P20/00,C03C25/00,A23G1/00,A21D13/00,B65D75/00,D04H1/00,H01M8/00,B29C64/00,C08G63/00,G11B7/00,B29C43/00,B29C39/00,B29C41/00,B32B25/00,B29C63/00; 内層の水分制御: A23G1/00,C09K8/00,A23F5/00,D21H23/00,A21D13/00,A23C19/00,C08F2/00,A23P20/00,A23G3/00,C12C7/00,B29C70/00,B01J19/00,B01D53/00,C08F20/00,C08F220/00,C08F120/00,B41M5/00,A61P17/00,A01N25/00,D21H19/00; 外層の糖組成: A61K31/00,C07H3/00,C12P19/00,C07H19/00,C12C7/00,C08F2/00,C08G18/00,C09K23/00,A23C19/00,C06B45/00,A61K9/00,A23G3/00,B01F101/00,C13B50/00,C12Q1/00,A23L33/00,C08G63/00,A23P20/00,C13K1/00,A23G9/00; 外層表面の熱変性処理: C23C8/00,C21D1/00,C23C10/00,B29C53/00,C25D5/00,C08J7/00,C23C22/00,H01L21/00,B05D5/00,C03B27/00,H05K3/00,B24C1/00,C23C18/00,C23C2/00,B22F1/00,C03C15/00,B28B1/00,B05D3/00,C03B37/00,C21D5/00; 食感変化の設計: B32B5/00,B29C48/00,A23P20/00,B29C70/00,B32B3/00,A21D13/00,B32B37/00,H01M50/00,D05C15/00,B60J10/00,A23K40/00,A23L7/00,B22F10/00,H01M8/00,B31B50/00,F24S80/00,B29D35/00,D21H19/00,F16J15/00,A23G9/00</t>
+  </si>
+  <si>
+    <t>A23G3/00,A23P20/00,A23G1/00,B32B37/00,A21D13/00,A23G3/00,A23P20/00,A23G1/00,A21D13/00,A23C19/00,C07H3/00,C12P19/00,C07H19/00,C09K23/00,A61K31/00,B05D5/00,C08J7/00,C21D1/00,C03B27/00,B29C53/00,A23P20/00,A21D13/00,B32B5/00,B32B3/00,B29C48/00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>C23C16/00,C10B21/00,B65G53/00,C12M1/00,B01F23/00,F27D7/00,H01J61/00,F24F3/00,F16F9/00,G01N27/00,B65B55/00,F23D14/00,B01J38/00,A61L9/00,F26B3/00,B07B11/00,C02F1/00,C10J3/00,A61M16/00,F23D11/00,F24F1/00,H01M50/00,H01R13/00,H02B11/00,E06B3/00,H01P1/00,F16K3/00,B04C5/00,F01N1/00,E04B2/00,E06B9/00,F02P7/00,H01F41/00,B65H3/00,G21C19/00,E06B7/00,B03C3/00,F02C7/00,H01L21/00,F16L59/00,F24F3/00,A61M60/00,B01F25/00,F24F1/00,F02M26/00,F01P5/00,A47L5/00,A23L3/00,F23N1/00,F24F7/00,F27D7/00,F01N3/00,A23B7/00,F21V29/00,F23R3/00,H01C1/00,F24F11/00,F23C10/00,A23B9/00,C21D1/00,B01D46/00,B01D33/00,B01D25/00,B01D35/00,B01D24/00,B29C48/00,F24F1/00,B05B14/00,F02M37/00,H01M50/00,F24F13/00,A47L9/00,B21D26/00,E04B2/00,F24F8/00,F22B37/00,B01F25/00,H04N19/00,B03C3/00,B65H3/00</t>
+  </si>
+  <si>
+    <t>滅菌ガス供給: C23C16/00,C10B21/00,B65G53/00,C12M1/00,B01F23/00,F27D7/00,H01J61/00,F24F3/00,F16F9/00,G01N27/00,B65B55/00,F23D14/00,B01J38/00,A61L9/00,F26B3/00,B07B11/00,C02F1/00,C10J3/00,A61M16/00,F23D11/00; アイソレータ構造: F24F1/00,H01M50/00,H01R13/00,H02B11/00,E06B3/00,H01P1/00,F16K3/00,B04C5/00,F01N1/00,E04B2/00,E06B9/00,F02P7/00,H01F41/00,B65H3/00,G21C19/00,E06B7/00,B03C3/00,F02C7/00,H01L21/00,F16L59/00; 循環用ファン・空気循環: F24F3/00,A61M60/00,B01F25/00,F24F1/00,F02M26/00,F01P5/00,A47L5/00,A23L3/00,F23N1/00,F24F7/00,F27D7/00,F01N3/00,A23B7/00,F21V29/00,F23R3/00,H01C1/00,F24F11/00,F23C10/00,A23B9/00,C21D1/00; エアフィルタ・パンチング板配置: B01D46/00,B01D33/00,B01D25/00,B01D35/00,B01D24/00,B29C48/00,F24F1/00,B05B14/00,F02M37/00,H01M50/00,F24F13/00,A47L9/00,B21D26/00,E04B2/00,F24F8/00,F22B37/00,B01F25/00,H04N19/00,B03C3/00,B65H3/00</t>
+  </si>
+  <si>
+    <t>B01F23/00,F27D7/00,F24F3/00,C12M1/00,B65G53/00,F24F1/00,E06B3/00,F16K3/00,E04B2/00,B04C5/00,F24F3/00,F24F1/00,F24F7/00,B01F25/00,A23L3/00,B01D46/00,B01D33/00,B01D25/00,B01D35/00,F24F1/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,B32B5/00,D21H27/00,F24S70/00,B65D81/00,A61L15/00,B62J1/00,B32B3/00,B41M5/00,G03F1/00,G09F11/00,H01L29/00,B63B32/00,A47C27/00,B60R21/00,B65B41/00,B29C73/00,H01M50/00,A61F5/00,B62D1/00,C06B45/00,H01M50/00,A61F13/00,B29C73/00,B65D35/00,B65H63/00,A61L15/00,B41M5/00,B65D81/00,F24S10/00,B28B21/00,G03F1/00,B60R21/00,H01L23/00,B29C63/00,B60J10/00,B65D75/00,E04F13/00,A23L3/00,F24S70/00,E04B2/00,B65D75/00,B65D43/00,B29C63/00,B23B31/00,B65B43/00,G01L5/00,F16B5/00,B66C1/00,B65H3/00,A43B7/00,E05C17/00,A61L15/00,H01R13/00,B65B41/00,B23B29/00,A47C7/00,B25B5/00,B32B3/00,A63C1/00,A61F13/00,H01J1/00,B65D81/00,H01G11/00,H01S3/00,A61L15/00,F24S70/00,F24S10/00,B29C70/00,C09K8/00,G03F1/00,H01J19/00,F24S80/00,F16F1/00,B22D41/00,C08J9/00,H01K1/00,G03C1/00,B29C73/00,B65D41/00</t>
+  </si>
+  <si>
+    <t>ペット用吸収性シート構造: A61F13/00,B32B5/00,D21H27/00,F24S70/00,B65D81/00,A61L15/00,B62J1/00,B32B3/00,B41M5/00,G03F1/00,G09F11/00,H01L29/00,B63B32/00,A47C27/00,B60R21/00,B65B41/00,B29C73/00,H01M50/00,A61F5/00,B62D1/00; 機能性材料の流出抑制技術: C06B45/00,H01M50/00,A61F13/00,B29C73/00,B65D35/00,B65H63/00,A61L15/00,B41M5/00,B65D81/00,F24S10/00,B28B21/00,G03F1/00,B60R21/00,H01L23/00,B29C63/00,B60J10/00,B65D75/00,E04F13/00,A23L3/00,F24S70/00; 凹部による材料保持構造: E04B2/00,B65D75/00,B65D43/00,B29C63/00,B23B31/00,B65B43/00,G01L5/00,F16B5/00,B66C1/00,B65H3/00,A43B7/00,E05C17/00,A61L15/00,H01R13/00,B65B41/00,B23B29/00,A47C7/00,B25B5/00,B32B3/00,A63C1/00; 吸収体の材料・構造: A61F13/00,H01J1/00,B65D81/00,H01G11/00,H01S3/00,A61L15/00,F24S70/00,F24S10/00,B29C70/00,C09K8/00,G03F1/00,H01J19/00,F24S80/00,F16F1/00,B22D41/00,C08J9/00,H01K1/00,G03C1/00,B29C73/00,B65D41/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,A61L15/00,B32B5/00,B32B3/00,D21H27/00,A61F13/00,A61L15/00,C06B45/00,B29C73/00,B65D81/00,B65D75/00,B65B43/00,B29C63/00,B65D43/00,E04B2/00,A61F13/00,A61L15/00,B29C70/00,F24S70/00,B65D81/00</t>
+  </si>
+  <si>
+    <t>A23L7/00,H01F1/00,A23P10/00,A23P20/00,A61K9/00,A61K47/00,A61L15/00,D06P1/00,A23L29/00,H01M8/00,B24D3/00,G03C1/00,C23C10/00,C09K8/00,A23G9/00,C06B45/00,B05D1/00,C08C1/00,B01J2/00,B29B9/00,A23L7/00,C12C7/00,G03C1/00,C08J9/00,C08B30/00,A21D13/00,B05D1/00,C01F7/00,C04B103/00,D21H21/00,B41M5/00,D21H23/00,G03F7/00,B01F35/00,A23P10/00,G05D11/00,C10M169/00,A23L29/00,A61L27/00,A23K10/00,C09K8/00,C08F2/00,A23P10/00,A23C9/00,C03C25/00,A23G1/00,A61K9/00,A23G9/00,B01J2/00,C08K13/00,E01C19/00,C10G71/00,D01F2/00,B65B3/00,C09D11/00,C06B45/00,G01N30/00,C10N50/00,D06P1/00,G05D11/00,A23L3/00,F26B5/00,B65D90/00,B65G53/00,C10J1/00,F01K25/00,A23L7/00,A23B5/00,H01M10/00,A47J27/00,F04B15/00,A47J31/00,C01F7/00,C03C25/00,G01L5/00,A23B9/00,G01D5/00,B67C3/00,G01N3/00,A23L11/00</t>
+  </si>
+  <si>
+    <t>顆粒状組成物: A23L7/00,H01F1/00,A23P10/00,A23P20/00,A61K9/00,A61K47/00,A61L15/00,D06P1/00,A23L29/00,H01M8/00,B24D3/00,G03C1/00,C23C10/00,C09K8/00,A23G9/00,C06B45/00,B05D1/00,C08C1/00,B01J2/00,B29B9/00; 未α化澱粉・α化澱粉の配合比: A23L7/00,C12C7/00,G03C1/00,C08J9/00,C08B30/00,A21D13/00,B05D1/00,C01F7/00,C04B103/00,D21H21/00,B41M5/00,D21H23/00,G03F7/00,B01F35/00,A23P10/00,G05D11/00,C10M169/00,A23L29/00,A61L27/00,A23K10/00; 油脂および乳化剤の含有制御: C09K8/00,C08F2/00,A23P10/00,A23C9/00,C03C25/00,A23G1/00,A61K9/00,A23G9/00,B01J2/00,C08K13/00,E01C19/00,C10G71/00,D01F2/00,B65B3/00,C09D11/00,C06B45/00,G01N30/00,C10N50/00,D06P1/00,G05D11/00; 低温調理による粘性発現: A23L3/00,F26B5/00,B65D90/00,B65G53/00,C10J1/00,F01K25/00,A23L7/00,A23B5/00,H01M10/00,A47J27/00,F04B15/00,A47J31/00,C01F7/00,C03C25/00,G01L5/00,A23B9/00,G01D5/00,B67C3/00,G01N3/00,A23L11/00</t>
+  </si>
+  <si>
+    <t>A23L7/00,A23P10/00,A23P20/00,A23L29/00,A61K9/00,A23L7/00,C08B30/00,A21D13/00,C08J9/00,C12C7/00,A23P10/00,A23C9/00,A23G1/00,A23G9/00,B01J2/00,A23L3/00,A23L7/00,A47J27/00,F26B5/00,B65D90/00</t>
+  </si>
+  <si>
+    <t>H02P3/00,D03D51/00,H01H73/00,H02P6/00,D05B69/00,B61L5/00,B65B57/00,A01B35/00,G01D11/00,F16H48/00,B43K24/00,B65G51/00,B25B23/00,B65H59/00,G05G5/00,D01H7/00,H01H3/00,B41J29/00,B61F17/00,F16H33/00,F41A19/00,B62M6/00,B66D1/00,H01H33/00,A61M60/00,H02K7/00,A01D34/00,E05F15/00,B60S9/00,F42B19/00,B08B9/00,B02C18/00,F04B17/00,E02F3/00,B60L50/00,B05B5/00,A61C17/00,F02C7/00,B21J7/00,D03D43/00,B61C9/00,B60K17/00,B62M6/00,B63H23/00,F16H39/00,H02K7/00,B66D1/00,F16D13/00,A01D34/00,B60K5/00,E05F3/00,B64C27/00,B62M1/00,B62L1/00,F02N15/00,B27B5/00,E05D7/00,F01B9/00,F04D29/00,F16H3/00,A01D34/00,B41J23/00,A24B7/00,G10K1/00,B26D5/00,B23D17/00,B62M6/00,B43K24/00,B27B11/00,E05F3/00,B02C18/00,B23D19/00,A01D78/00,B26D1/00,G06C23/00,B01D21/00,B64C27/00,F26B11/00,B60S9/00,B21J7/00</t>
+  </si>
+  <si>
+    <t>回転抑制装置: H02P3/00,D03D51/00,H01H73/00,H02P6/00,D05B69/00,B61L5/00,B65B57/00,A01B35/00,G01D11/00,F16H48/00,B43K24/00,B65G51/00,B25B23/00,B65H59/00,G05G5/00,D01H7/00,H01H3/00,B41J29/00,B61F17/00,F16H33/00; 原動機: F41A19/00,B62M6/00,B66D1/00,H01H33/00,A61M60/00,H02K7/00,A01D34/00,E05F15/00,B60S9/00,F42B19/00,B08B9/00,B02C18/00,F04B17/00,E02F3/00,B60L50/00,B05B5/00,A61C17/00,F02C7/00,B21J7/00,D03D43/00; 駆動軸構造: B61C9/00,B60K17/00,B62M6/00,B63H23/00,F16H39/00,H02K7/00,B66D1/00,F16D13/00,A01D34/00,B60K5/00,E05F3/00,B64C27/00,B62M1/00,B62L1/00,F02N15/00,B27B5/00,E05D7/00,F01B9/00,F04D29/00,F16H3/00; 草刈刃回転機構: A01D34/00,B41J23/00,A24B7/00,G10K1/00,B26D5/00,B23D17/00,B62M6/00,B43K24/00,B27B11/00,E05F3/00,B02C18/00,B23D19/00,A01D78/00,B26D1/00,G06C23/00,B01D21/00,B64C27/00,F26B11/00,B60S9/00,B21J7/00</t>
+  </si>
+  <si>
+    <t>H02P3/00,D03D51/00,H01H73/00,H02P6/00,A01B35/00,A01D34/00,H02K7/00,B62M6/00,H01H33/00,B66D1/00,A01D34/00,F16D13/00,H02K7/00,B60K17/00,F16H39/00,A01D34/00,B26D5/00,B23D17/00,E05F3/00,B27B11/00</t>
+  </si>
+  <si>
+    <t>B01F35/00,G07F11/00,B65D21/00,B01F25/00,B67D7/00,B01F29/00,B01F33/00,G01N9/00,A47L1/00,B01F31/00,B65D77/00,F04F5/00,B07B9/00,B65D41/00,B01D24/00,B67D3/00,A61F13/00,G21F9/00,B65D5/00,B02C17/00,B01F25/00,B67D7/00,F17D1/00,B65G53/00,F24S10/00,A61M5/00,F04B9/00,F16N7/00,F22B21/00,B01D15/00,F16L3/00,B05B9/00,F16L41/00,F16L25/00,B65G51/00,F02F1/00,H01M50/00,F16H47/00,F04B1/00,A61J1/00,F16H61/00,F04F5/00,A61M60/00,F04B43/00,F04D13/00,F04D29/00,F16D31/00,F16H39/00,F17D1/00,F15B9/00,F04F1/00,F04D25/00,F01P5/00,B05B7/00,B05B9/00,H01M50/00,B21D26/00,F02M37/00,F24H15/00,F01M1/00,A61M60/00,B01F25/00,A61M5/00,A61M1/00,F17D1/00,B01D33/00,C12N15/00,G01P3/00,C12M1/00,H01M50/00,B01F31/00,G21C19/00,H01J13/00,B05C11/00,A61B5/00,B05B7/00,B67D7/00,B05C9/00,B65G53/00,F04F5/00,B01F25/00,B01F33/00,B01F27/00,B01F23/00,B29B7/00,B28C5/00,B01F35/00,B03B5/00,A47L1/00,B01F29/00,G05D11/00,B05C3/00,B02C23/00,B05C1/00,B01D17/00,F04F5/00,B01F101/00,G01F11/00,F16K21/00,B05C11/00</t>
+  </si>
+  <si>
+    <t>多液体容器構成: B01F35/00,G07F11/00,B65D21/00,B01F25/00,B67D7/00,B01F29/00,B01F33/00,G01N9/00,A47L1/00,B01F31/00,B65D77/00,F04F5/00,B07B9/00,B65D41/00,B01D24/00,B67D3/00,A61F13/00,G21F9/00,B65D5/00,B02C17/00; 送液管路システム: B01F25/00,B67D7/00,F17D1/00,B65G53/00,F24S10/00,A61M5/00,F04B9/00,F16N7/00,F22B21/00,B01D15/00,F16L3/00,B05B9/00,F16L41/00,F16L25/00,B65G51/00,F02F1/00,H01M50/00,F16H47/00,F04B1/00,A61J1/00; 送液ポンプ制御: F16H61/00,F04F5/00,A61M60/00,F04B43/00,F04D13/00,F04D29/00,F16D31/00,F16H39/00,F17D1/00,F15B9/00,F04F1/00,F04D25/00,F01P5/00,B05B7/00,B05B9/00,H01M50/00,B21D26/00,F02M37/00,F24H15/00,F01M1/00; 細胞培養装置への応用: A61M60/00,B01F25/00,A61M5/00,A61M1/00,F17D1/00,B01D33/00,C12N15/00,G01P3/00,C12M1/00,H01M50/00,B01F31/00,G21C19/00,H01J13/00,B05C11/00,A61B5/00,B05B7/00,B67D7/00,B05C9/00,B65G53/00,F04F5/00; 液体混合・分配技術: B01F25/00,B01F33/00,B01F27/00,B01F23/00,B29B7/00,B28C5/00,B01F35/00,B03B5/00,A47L1/00,B01F29/00,G05D11/00,B05C3/00,B02C23/00,B05C1/00,B01D17/00,F04F5/00,B01F101/00,G01F11/00,F16K21/00,B05C11/00</t>
+  </si>
+  <si>
+    <t>B01F35/00,B65D21/00,B67D7/00,B01F25/00,B01F33/00,F17D1/00,B01F25/00,B67D7/00,B65G53/00,F04B9/00,A61M60/00,F04B43/00,F04D13/00,F04F5/00,F16H61/00,C12M1/00,A61M1/00,A61M5/00,B01F25/00,F17D1/00,B01F25/00,B01F33/00,B01F27/00,B01F23/00,B01F35/00</t>
+  </si>
+  <si>
+    <t>C09K8/00,B01F23/00,B01J2/00,C04B103/00,G03C1/00,B02C4/00,D21H21/00,A23P10/00,G21C3/00,C09D11/00,E01C19/00,C08F2/00,B41M5/00,C30B31/00,H01M8/00,C10N30/00,A61L9/00,A23L33/00,C10K1/00,C06B47/00,A23L7/00,A23L29/00,A23C9/00,C12C7/00,C01F7/00,A23P10/00,A23K10/00,A23L33/00,A21D13/00,B05D1/00,D21H13/00,C08K9/00,A23C19/00,D06P1/00,A21D8/00,C08B30/00,C09K8/00,C07C57/00,C09D11/00,A23J1/00,B22F1/00,C09K8/00,B01F23/00,B01J8/00,C08J3/00,B01J2/00,H01F1/00,C03C25/00,C10N50/00,E01C19/00,C08F2/00,B01D46/00,C08J9/00,C09K23/00,G01N33/00,C10G45/00,C10G71/00,B41M5/00,C09D11/00,C10G47/00,B65B3/00,B65B1/00,B65B11/00,A23L3/00,B65D77/00,B65B55/00,A23P20/00,B65B39/00,B65B31/00,B65D21/00,B65B25/00,B65D85/00,B05C3/00,B05C7/00,B65B29/00,B65B5/00,B65D75/00,B65B43/00,B65D41/00,B05C5/00</t>
+  </si>
+  <si>
+    <t>水分散性食品組成物: C09K8/00,B01F23/00,B01J2/00,C04B103/00,G03C1/00,B02C4/00,D21H21/00,A23P10/00,G21C3/00,C09D11/00,E01C19/00,C08F2/00,B41M5/00,C30B31/00,H01M8/00,C10N30/00,A61L9/00,A23L33/00,C10K1/00,C06B47/00; α化していない澱粉の利用: A23L7/00,A23L29/00,A23C9/00,C12C7/00,C01F7/00,A23P10/00,A23K10/00,A23L33/00,A21D13/00,B05D1/00,D21H13/00,C08K9/00,A23C19/00,D06P1/00,A21D8/00,C08B30/00,C09K8/00,C07C57/00,C09D11/00,A23J1/00; 油脂の微細分散: B22F1/00,C09K8/00,B01F23/00,B01J8/00,C08J3/00,B01J2/00,H01F1/00,C03C25/00,C10N50/00,E01C19/00,C08F2/00,B01D46/00,C08J9/00,C09K23/00,G01N33/00,C10G45/00,C10G71/00,B41M5/00,C09D11/00,C10G47/00; 容器入り食品包装: B65B3/00,B65B1/00,B65B11/00,A23L3/00,B65D77/00,B65B55/00,A23P20/00,B65B39/00,B65B31/00,B65D21/00,B65B25/00,B65D85/00,B05C3/00,B05C7/00,B65B29/00,B65B5/00,B65D75/00,B65B43/00,B65D41/00,B05C5/00</t>
+  </si>
+  <si>
+    <t>A23P10/00,B01F23/00,B01J2/00,B02C4/00,C09K8/00,A23L7/00,A23L29/00,A23C9/00,A23L33/00,A23P10/00,B01F23/00,C08J3/00,B01J2/00,B01J8/00,C09K8/00,B65B3/00,B65B55/00,A23L3/00,B65D77/00,A23P20/00</t>
+  </si>
+  <si>
+    <t>A23L3/00,C21D1/00,A23B7/00,A23B4/00,A23B9/00,C01F7/00,B29C70/00,A23B5/00,A47J31/00,C10B57/00,G03B27/00,F26B3/00,A24B3/00,A45D4/00,G03F7/00,C08J11/00,C10B21/00,D06M23/00,D21F5/00,G21C19/00,C09K8/00,C12G3/00,C12G1/00,C07C51/00,C12C7/00,B01D15/00,C10G19/00,C07C45/00,C07C41/00,C23C22/00,D06L1/00,C10K1/00,C07C47/00,G03C7/00,C10G17/00,C08F6/00,B05C1/00,C23F1/00,C01F11/00,B28C1/00,C12G3/00,A23L2/00,C12G1/00,C25D3/00,H01J1/00,B01F101/00,H01M10/00,B23K35/00,A23F3/00,H01M4/00,C12F3/00,C12C12/00,C01F7/00,C08K5/00,H01H33/00,B01F35/00,C07C31/00,H01L23/00,C02F1/00,D06L4/00,D06P1/00,C04B41/00,B29C70/00,B65D81/00,B01J38/00,A23L13/00,B05C1/00,B28B21/00,C10J1/00,D06B9/00,B65B3/00,A23L3/00,B27K3/00,A23B4/00,G01D5/00,G03C7/00,D06M23/00,B05D7/00,B65D85/00,D06B3/00,C10G53/00,C10G65/00,H01M4/00,B21B1/00,C10G67/00,A23F3/00,C12G1/00,C10G61/00,C12C7/00,C08G69/00,C12G3/00,B29C70/00,B21B17/00,C01F7/00,C08B1/00,C10G69/00,C12F3/00,C13B10/00,C01B25/00,B29C64/00</t>
+  </si>
+  <si>
+    <t>減圧加熱処理: A23L3/00,C21D1/00,A23B7/00,A23B4/00,A23B9/00,C01F7/00,B29C70/00,A23B5/00,A47J31/00,C10B57/00,G03B27/00,F26B3/00,A24B3/00,A45D4/00,G03F7/00,C08J11/00,C10B21/00,D06M23/00,D21F5/00,G21C19/00; 処理液体組成: C09K8/00,C12G3/00,C12G1/00,C07C51/00,C12C7/00,B01D15/00,C10G19/00,C07C45/00,C07C41/00,C23C22/00,D06L1/00,C10K1/00,C07C47/00,G03C7/00,C10G17/00,C08F6/00,B05C1/00,C23F1/00,C01F11/00,B28C1/00; 花材選定: C12G3/00,A23L2/00,C12G1/00,C25D3/00,H01J1/00,B01F101/00,H01M10/00,B23K35/00,A23F3/00,H01M4/00,C12F3/00,C12C12/00,C01F7/00,C08K5/00,H01H33/00,B01F35/00,C07C31/00,H01L23/00,C02F1/00,D06L4/00; 含浸技術: D06P1/00,C04B41/00,B29C70/00,B65D81/00,B01J38/00,A23L13/00,B05C1/00,B28B21/00,C10J1/00,D06B9/00,B65B3/00,A23L3/00,B27K3/00,A23B4/00,G01D5/00,G03C7/00,D06M23/00,B05D7/00,B65D85/00,D06B3/00; 製造工程の短縮: C10G53/00,C10G65/00,H01M4/00,B21B1/00,C10G67/00,A23F3/00,C12G1/00,C10G61/00,C12C7/00,C08G69/00,C12G3/00,B29C70/00,B21B17/00,C01F7/00,C08B1/00,C10G69/00,C12F3/00,C13B10/00,C01B25/00,B29C64/00</t>
+  </si>
+  <si>
+    <t>A23L3/00,A23B7/00,C21D1/00,A47J31/00,A23B9/00,C12G3/00,C12G1/00,C12C7/00,C07C51/00,B01D15/00,C12G3/00,A23L2/00,C12G1/00,A23F3/00,B01F101/00,D06P1/00,B05C1/00,A23L13/00,B65D81/00,D06B9/00,A23F3/00,C12G1/00,C12C7/00,C08G69/00,C10G53/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G23/00,G01G13/00,B07C5/00,B65B1/00,G01G3/00,G01G21/00,G01N9/00,G01G1/00,G01G11/00,G01G17/00,G01N5/00,B65B3/00,G01G15/00,G01L5/00,B65D41/00,A47G19/00,G01V7/00,G01K17/00,G01G5/00,G01S13/00,G06V10/00,G11B27/00,G06V20/00,B23Q35/00,G01V8/00,G06F18/00,E05B81/00,H04N19/00,A63F13/00,G01G19/00,B60T8/00,G11B15/00,G06V30/00,G01S15/00,G07C9/00,A61B5/00,G06T7/00,G11B19/00,G06V40/00,H04H60/00,H04W12/00,G11B27/00,G01S13/00,G07D7/00,G11B15/00,G06F21/00,B07C3/00,G06V30/00,B23Q35/00,G01P3/00,G06K21/00,G06K19/00,B60R25/00,G06T7/00,A61B5/00,G07C9/00,A47G19/00,A63F13/00,F24F1/00,G01G19/00,G06F119/00,B07C5/00,G01G23/00,G01G13/00,A23K50/00,G01J1/00,F24H15/00,A61B5/00,G01G1/00,H04N19/00,B65B1/00,G06G7/00,B65B3/00,G01G15/00,G06V30/00,G07F15/00,A23K40/00,G01C11/00,G06F30/00</t>
+  </si>
+  <si>
+    <t>食器重量測定: G01G19/00,G01G23/00,G01G13/00,B07C5/00,B65B1/00,G01G3/00,G01G21/00,G01N9/00,G01G1/00,G01G11/00,G01G17/00,G01N5/00,B65B3/00,G01G15/00,G01L5/00,B65D41/00,A47G19/00,G01V7/00,G01K17/00,G01G5/00; 食器動作検知: G01S13/00,G06V10/00,G11B27/00,G06V20/00,B23Q35/00,G01V8/00,G06F18/00,E05B81/00,H04N19/00,A63F13/00,G01G19/00,B60T8/00,G11B15/00,G06V30/00,G01S15/00,G07C9/00,A61B5/00,G06T7/00,G11B19/00,G06V40/00; 個体識別技術: H04H60/00,H04W12/00,G11B27/00,G01S13/00,G07D7/00,G11B15/00,G06F21/00,B07C3/00,G06V30/00,B23Q35/00,G01P3/00,G06K21/00,G06K19/00,B60R25/00,G06T7/00,A61B5/00,G07C9/00,A47G19/00,A63F13/00,F24F1/00; 最適食事量算出: G01G19/00,G06F119/00,B07C5/00,G01G23/00,G01G13/00,A23K50/00,G01J1/00,F24H15/00,A61B5/00,G01G1/00,H04N19/00,B65B1/00,G06G7/00,B65B3/00,G01G15/00,G06V30/00,G07F15/00,A23K40/00,G01C11/00,G06F30/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G13/00,G01G23/00,G01G3/00,B07C5/00,G06F18/00,G06V10/00,G01S13/00,G01V8/00,G06V20/00,G06V30/00,G01S13/00,H04W12/00,G06F21/00,B07C3/00,G01G19/00,G06F119/00,A23K50/00,A61B5/00,G01G13/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G23/00,B07C5/00,G01G13/00,B65B1/00,G01G3/00,G01N9/00,G01G1/00,G01G17/00,G01G11/00,G01L5/00,G01G21/00,G01G15/00,G11B15/00,G04B1/00,B65G69/00,B65H33/00,G07D11/00,G01K17/00,C12C1/00,B60K15/00,B64D37/00,B65D21/00,B62D21/00,B62D33/00,B63B27/00,C12C1/00,A01F12/00,F16L3/00,G21F5/00,B65G65/00,F22B13/00,B62J9/00,B65G67/00,B01F29/00,F41B11/00,F15B1/00,F42B39/00,B65D25/00,H01M8/00,B60P1/00,F16M11/00,B62B1/00,A47C1/00,E21D15/00,H05K7/00,B66F7/00,G09B1/00,B01F29/00,H01L21/00,B60K17/00,F16L3/00,B60J1/00,E04B1/00,B65H39/00,B65G67/00,G01L5/00,B60P3/00,B62D33/00,E01B21/00,G01G19/00,G01G23/00,G01G13/00,G01G1/00,B07C5/00,G01G3/00,B65B1/00,A01F12/00,G01G11/00,G01G21/00,G01M1/00,G01N9/00,G01P3/00,B63B43/00,G01G17/00,G01G15/00,H03K3/00,A01D41/00,F16D43/00,B66F9/00</t>
+  </si>
+  <si>
+    <t>ロードセルによる重量検出: G01G19/00,G01G23/00,B07C5/00,G01G13/00,B65B1/00,G01G3/00,G01N9/00,G01G1/00,G01G17/00,G01G11/00,G01L5/00,G01G21/00,G01G15/00,G11B15/00,G04B1/00,B65G69/00,B65H33/00,G07D11/00,G01K17/00,C12C1/00; グレンタンク構造・搭載方法: B60K15/00,B64D37/00,B65D21/00,B62D21/00,B62D33/00,B63B27/00,C12C1/00,A01F12/00,F16L3/00,G21F5/00,B65G65/00,F22B13/00,B62J9/00,B65G67/00,B01F29/00,F41B11/00,F15B1/00,F42B39/00,B65D25/00,H01M8/00; 載置支持部の設計: B60P1/00,F16M11/00,B62B1/00,A47C1/00,E21D15/00,H05K7/00,B66F7/00,G09B1/00,B01F29/00,H01L21/00,B60K17/00,F16L3/00,B60J1/00,E04B1/00,B65H39/00,B65G67/00,G01L5/00,B60P3/00,B62D33/00,E01B21/00; 重量検出精度向上手法: G01G19/00,G01G23/00,G01G13/00,G01G1/00,B07C5/00,G01G3/00,B65B1/00,A01F12/00,G01G11/00,G01G21/00,G01M1/00,G01N9/00,G01P3/00,B63B43/00,G01G17/00,G01G15/00,H03K3/00,A01D41/00,F16D43/00,B66F9/00</t>
+  </si>
+  <si>
+    <t>G01G19/00,G01G13/00,G01G3/00,G01G23/00,G01G17/00,B62D21/00,B65D21/00,B62D33/00,A01F12/00,F16L3/00,F16M11/00,B60P1/00,B66F7/00,E21D15/00,B62B1/00,G01G19/00,G01G23/00,G01G3/00,G01G21/00,A01F12/00</t>
+  </si>
+  <si>
+    <t>B65B11/00,E04G7/00,B65D5/00,F16L55/00,F16L37/00,F16L3/00,F16L33/00,A61B17/00,F16B12/00,B27B29/00,F16L29/00,B65D43/00,B27G13/00,A45D2/00,A61F2/00,B21D39/00,B23B31/00,F16D1/00,B23Q1/00,F16K31/00,G01L5/00,G01G19/00,G01G3/00,F16F1/00,A61M60/00,E21B47/00,G01F1/00,G01L13/00,E21D15/00,G01L23/00,G01G11/00,G11B3/00,E05F15/00,G01G13/00,F16J15/00,E21B19/00,B66C1/00,B21B19/00,H01J41/00,G11B15/00,B65B11/00,F16L55/00,E21B47/00,F16L37/00,A61F2/00,B65G51/00,B65D75/00,B21D26/00,E03C1/00,B29C48/00,B61L21/00,B61L23/00,A61M60/00,B65B9/00,A63B41/00,H01J37/00,A61M39/00,B31C1/00,H01J19/00,F16L9/00,A61M60/00,B01D35/00,F24F1/00,H02B1/00,F41A9/00,B01D33/00,B01D25/00,B01D29/00,B61G9/00,F02B13/00,B65H39/00,B21B39/00,A61B90/00,G01G19/00,C40B60/00,A61F2/00,F16B12/00,A61B17/00,B60K35/00,F22B37/00</t>
+  </si>
+  <si>
+    <t>クランプユニット構造: B65B11/00,E04G7/00,B65D5/00,F16L55/00,F16L37/00,F16L3/00,F16L33/00,A61B17/00,F16B12/00,B27B29/00,F16L29/00,B65D43/00,B27G13/00,A45D2/00,A61F2/00,B21D39/00,B23B31/00,F16D1/00,B23Q1/00,F16K31/00; 荷重検出部: G01L5/00,G01G19/00,G01G3/00,F16F1/00,A61M60/00,E21B47/00,G01F1/00,G01L13/00,E21D15/00,G01L23/00,G01G11/00,G11B3/00,E05F15/00,G01G13/00,F16J15/00,E21B19/00,B66C1/00,B21B19/00,H01J41/00,G11B15/00; チューブ閉塞判定方法: B65B11/00,F16L55/00,E21B47/00,F16L37/00,A61F2/00,B65G51/00,B65D75/00,B21D26/00,E03C1/00,B29C48/00,B61L21/00,B61L23/00,A61M60/00,B65B9/00,A63B41/00,H01J37/00,A61M39/00,B31C1/00,H01J19/00,F16L9/00; 透析装置への組み込み: A61M60/00,B01D35/00,F24F1/00,H02B1/00,F41A9/00,B01D33/00,B01D25/00,B01D29/00,B61G9/00,F02B13/00,B65H39/00,B21B39/00,A61B90/00,G01G19/00,C40B60/00,A61F2/00,F16B12/00,A61B17/00,B60K35/00,F22B37/00</t>
+  </si>
+  <si>
+    <t>F16L3/00,F16L55/00,A61B17/00,F16L37/00,F16L33/00,G01L5/00,G01G19/00,G01G3/00,A61M60/00,G01L13/00,F16L55/00,A61F2/00,E21B47/00,B65G51/00,F16L37/00,A61M60/00,B01D35/00,B01D33/00,B01D25/00,B01D29/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,B62J1/00,H01M50/00,B60R21/00,B65D5/00,B29C63/00,B60N2/00,F16H57/00,A47C7/00,B64C1/00,A43B7/00,B62J13/00,B65D88/00,A47K13/00,B05B12/00,B65F1/00,A47C1/00,G21C5/00,A47C17/00,A41B9/00,B60R21/00,A47C7/00,F16D3/00,A47C23/00,H01R13/00,F16F15/00,B28B21/00,H01M50/00,B62J1/00,E04F13/00,B60B7/00,F16F1/00,B60C5/00,H01L23/00,B64C25/00,A47C1/00,H01H1/00,B65D81/00,B60G3/00,B62D55/00,A61F13/00,D03C3/00,H01R13/00,A41D27/00,B65D71/00,A47G25/00,E04G7/00,E06B3/00,A41F3/00,B60R21/00,B21D26/00,E06B9/00,F28F1/00,A41F9/00,G03B9/00,A47B57/00,E06B1/00,B65D17/00,G05G15/00,B65D75/00,H01R13/00,F16D3/00,H01M50/00,H01J19/00,B66F3/00,A61M60/00,E04B9/00,G01L5/00,E04F13/00,E01B11/00,G01B5/00,A63B21/00,B31B150/00,A47C23/00,F16H15/00,F16F15/00,B60R21/00,F24S25/00,E04B2/00,A47C7/00</t>
+  </si>
+  <si>
+    <t>臀部カバー部の構造: A61F13/00,B62J1/00,H01M50/00,B60R21/00,B65D5/00,B29C63/00,B60N2/00,F16H57/00,A47C7/00,B64C1/00,A43B7/00,B62J13/00,B65D88/00,A47K13/00,B05B12/00,B65F1/00,A47C1/00,G21C5/00,A47C17/00,A41B9/00; カバー部弾性部材の配置: B60R21/00,A47C7/00,F16D3/00,A47C23/00,H01R13/00,F16F15/00,B28B21/00,H01M50/00,B62J1/00,E04F13/00,B60B7/00,F16F1/00,B60C5/00,H01L23/00,B64C25/00,A47C1/00,H01H1/00,B65D81/00,B60G3/00,B62D55/00; ウエスト開口・脚開口との関係: A61F13/00,D03C3/00,H01R13/00,A41D27/00,B65D71/00,A47G25/00,E04G7/00,E06B3/00,A41F3/00,B60R21/00,B21D26/00,E06B9/00,F28F1/00,A41F9/00,G03B9/00,A47B57/00,E06B1/00,B65D17/00,G05G15/00,B65D75/00; 寸法・間隔条件: H01R13/00,F16D3/00,H01M50/00,H01J19/00,B66F3/00,A61M60/00,E04B9/00,G01L5/00,E04F13/00,E01B11/00,G01B5/00,A63B21/00,B31B150/00,A47C23/00,F16H15/00,F16F15/00,B60R21/00,F24S25/00,E04B2/00,A47C7/00</t>
+  </si>
+  <si>
+    <t>A61F13/00,B62J1/00,B60R21/00,B29C63/00,B65D5/00,A47C7/00,A47C23/00,B62J1/00,F16F15/00,F16D3/00,A61F13/00,A41D27/00,A41F3/00,A47G25/00,D03C3/00,F16D3/00,G01L5/00,E04B9/00,E04F13/00,E01B11/00</t>
+  </si>
+  <si>
+    <t>A43B7/00,A43D3/00,A43D25/00,A43D11/00,A63C10/00,A43B9/00,A43D1/00,A43D100/00,A43B13/00,F24F1/00,A41B11/00,A43D21/00,B29D35/00,A63C11/00,A47G25/00,A63C9/00,A43B3/00,B65D90/00,F02M26/00,B60R1/00,A43B7/00,A47L23/00,A43D3/00,A63C10/00,A43D25/00,B65D75/00,A43D1/00,A43B9/00,H01M50/00,A43D95/00,A41B11/00,B65G1/00,A43D11/00,A43B3/00,A43B13/00,A43B17/00,E06B9/00,A43D21/00,B65D81/00,A43B23/00,A43B7/00,A43D25/00,A43B9/00,A43D11/00,A43D3/00,A63C10/00,A43B13/00,A63C11/00,A63C9/00,A43D1/00,A43B3/00,A43D100/00,F02M26/00,A63C1/00,G01B3/00,A47L23/00,A47G25/00,B41J29/00,A43D21/00,H01H3/00,A43B7/00,A43B9/00,A43D3/00,A63C9/00,A43B3/00,A63C10/00,A43D1/00,A43D21/00,A47G25/00,A43D100/00,A43D25/00,A41B11/00,A47L23/00,E05B77/00,A43B23/00,A61F5/00,A63C1/00,A43B13/00,A43B17/00,A43C11/00</t>
+  </si>
+  <si>
+    <t>オーバーシューズユニット構造: A43B7/00,A43D3/00,A43D25/00,A43D11/00,A63C10/00,A43B9/00,A43D1/00,A43D100/00,A43B13/00,F24F1/00,A41B11/00,A43D21/00,B29D35/00,A63C11/00,A47G25/00,A63C9/00,A43B3/00,B65D90/00,F02M26/00,B60R1/00; 収納部・収納空間: A43B7/00,A47L23/00,A43D3/00,A63C10/00,A43D25/00,B65D75/00,A43D1/00,A43B9/00,H01M50/00,A43D95/00,A41B11/00,B65G1/00,A43D11/00,A43B3/00,A43B13/00,A43B17/00,E06B9/00,A43D21/00,B65D81/00,A43B23/00; オーバーシューズ着脱方法: A43B7/00,A43D25/00,A43B9/00,A43D11/00,A43D3/00,A63C10/00,A43B13/00,A63C11/00,A63C9/00,A43D1/00,A43B3/00,A43D100/00,F02M26/00,A63C1/00,G01B3/00,A47L23/00,A47G25/00,B41J29/00,A43D21/00,H01H3/00; 持参忘れ防止機能: A43B7/00,A43B9/00,A43D3/00,A63C9/00,A43B3/00,A63C10/00,A43D1/00,A43D21/00,A47G25/00,A43D100/00,A43D25/00,A41B11/00,A47L23/00,E05B77/00,A43B23/00,A61F5/00,A63C1/00,A43B13/00,A43B17/00,A43C11/00</t>
+  </si>
+  <si>
+    <t>A43B7/00,A43B9/00,A43D11/00,A43D100/00,A43B13/00,A43B7/00,A43B9/00,A43D3/00,A43D25/00,B65D75/00,A43B7/00,A43B9/00,A43D11/00,A43B13/00,A43D25/00,A43B7/00,A43B9/00,A43B3/00,A43D100/00,A47G25/00</t>
+  </si>
+  <si>
+    <t>A47L11/00,E04B5/00,H01R39/00,A47L23/00,A47L13/00,A47L5/00,F24F1/00,A47C17/00,H02M7/00,E02F3/00,A46B3/00,A47L9/00,A46B17/00,A61C17/00,C10G45/00,C10G47/00,C10G49/00,B62J50/00,A61C13/00,B08B1/00,A47L5/00,F02M35/00,F02M26/00,B04C5/00,B65G53/00,B60T13/00,A61C17/00,A47L11/00,B65B35/00,B65B43/00,B65D5/00,B31B50/00,B65H29/00,A47J31/00,F02M7/00,F02M69/00,B07B11/00,A61F13/00,F16L59/00,B65H5/00,A47L11/00,A47L5/00,B08B9/00,B01D33/00,B01D46/00,A47L9/00,H01R39/00,H02M7/00,B43K24/00,F01D1/00,B05B15/00,A47L15/00,A63B21/00,B26F1/00,A47J17/00,B01D29/00,C14B1/00,D06F43/00,A46B13/00,B62J50/00,A47L5/00,B01D46/00,F02B25/00,F02M35/00,F02M26/00,A61C17/00,A47L9/00,B04C5/00,B65H3/00,B65G53/00,A47L11/00,E21B21/00,F01C20/00,B65B1/00,F02B31/00,F01N3/00,F02C9/00,F24F13/00,F27B3/00,B62J40/00</t>
+  </si>
+  <si>
+    <t>床ブラシ構造: A47L11/00,E04B5/00,H01R39/00,A47L23/00,A47L13/00,A47L5/00,F24F1/00,A47C17/00,H02M7/00,E02F3/00,A46B3/00,A47L9/00,A46B17/00,A61C17/00,C10G45/00,C10G47/00,C10G49/00,B62J50/00,A61C13/00,B08B1/00; 真空度保持体: A47L5/00,F02M35/00,F02M26/00,B04C5/00,B65G53/00,B60T13/00,A61C17/00,A47L11/00,B65B35/00,B65B43/00,B65D5/00,B31B50/00,B65H29/00,A47J31/00,F02M7/00,F02M69/00,B07B11/00,A61F13/00,F16L59/00,B65H5/00; 回転ブラシ機構: A47L11/00,A47L5/00,B08B9/00,B01D33/00,B01D46/00,A47L9/00,H01R39/00,H02M7/00,B43K24/00,F01D1/00,B05B15/00,A47L15/00,A63B21/00,B26F1/00,A47J17/00,B01D29/00,C14B1/00,D06F43/00,A46B13/00,B62J50/00; 塵埃吸引効率: A47L5/00,B01D46/00,F02B25/00,F02M35/00,F02M26/00,A61C17/00,A47L9/00,B04C5/00,B65H3/00,B65G53/00,A47L11/00,E21B21/00,F01C20/00,B65B1/00,F02B31/00,F01N3/00,F02C9/00,F24F13/00,F27B3/00,B62J40/00</t>
+  </si>
+  <si>
+    <t>A47L11/00,A47L5/00,A47L13/00,A47L23/00,E04B5/00,A47L5/00,A47L11/00,A61C17/00,B04C5/00,B65G53/00,A47L11/00,A47L5/00,A47L9/00,B08B9/00,B01D33/00,A47L5/00,A47L9/00,B01D46/00,B04C5/00,B65G53/00</t>
+  </si>
+  <si>
+    <t>A47C17/00,E04H6/00,A61G7/00,C10B49/00,A63G1/00,A61G1/00,A47B23/00,B23B29/00,B63B29/00,B66B17/00,A01B35/00,B65G47/00,B66F7/00,E01B29/00,B03B4/00,B22C11/00,B26D1/00,A47B3/00,C14B1/00,A47B91/00,F16D3/00,F04C18/00,F16D1/00,F16H3/00,B23Q1/00,F03C2/00,G01F1/00,B29B7/00,F04C3/00,H01H33/00,G02B6/00,E05D7/00,F16L27/00,G06C15/00,F04C2/00,F16H48/00,H01H1/00,D03D47/00,H01L23/00,F04D29/00,H04N23/00,H04N13/00,H04N25/00,H05G1/00,G03B7/00,G01C11/00,H04N5/00,H04N1/00,H02M1/00,H01S3/00,G03F7/00,G05B19/00,G06T7/00,G01S3/00,B23B31/00,G08G1/00,H01Q3/00,G01R33/00,G03B35/00,G10L21/00,H01Q3/00,B01D61/00,G01J5/00,F16H55/00,D01H5/00,G01S3/00,H05G1/00,C10G9/00,G01R33/00,B27B31/00,G08B13/00,D01F9/00,A61B6/00,G21F5/00,G01N23/00,G04C23/00,H03K17/00,H03B9/00,G01S13/00,D21H23/00,H05G1/00,G11B7/00,H01J37/00,G01T1/00,G01J1/00,H01J31/00,H01J29/00,G01J5/00,G01N23/00,G21C19/00,G01S3/00,A61B6/00,H01J25/00,G01D5/00,H01J3/00,H01Q3/00,G01N29/00,H04N1/00,G01J3/00,H01J35/00</t>
+  </si>
+  <si>
+    <t>寝台装置構造: A47C17/00,E04H6/00,A61G7/00,C10B49/00,A63G1/00,A61G1/00,A47B23/00,B23B29/00,B63B29/00,B66B17/00,A01B35/00,B65G47/00,B66F7/00,E01B29/00,B03B4/00,B22C11/00,B26D1/00,A47B3/00,C14B1/00,A47B91/00; ガントリ交差セット機構: F16D3/00,F04C18/00,F16D1/00,F16H3/00,B23Q1/00,F03C2/00,G01F1/00,B29B7/00,F04C3/00,H01H33/00,G02B6/00,E05D7/00,F16L27/00,G06C15/00,F04C2/00,F16H48/00,H01H1/00,D03D47/00,H01L23/00,F04D29/00; 撮像制御手段: H04N23/00,H04N13/00,H04N25/00,H05G1/00,G03B7/00,G01C11/00,H04N5/00,H04N1/00,H02M1/00,H01S3/00,G03F7/00,G05B19/00,G06T7/00,G01S3/00,B23B31/00,G08G1/00,H01Q3/00,G01R33/00,G03B35/00,G10L21/00; セット・退避時間短縮技術: H01Q3/00,B01D61/00,G01J5/00,F16H55/00,D01H5/00,G01S3/00,H05G1/00,C10G9/00,G01R33/00,B27B31/00,G08B13/00,D01F9/00,A61B6/00,G21F5/00,G01N23/00,G04C23/00,H03K17/00,H03B9/00,G01S13/00,D21H23/00; X線管・検出器配置: H05G1/00,G11B7/00,H01J37/00,G01T1/00,G01J1/00,H01J31/00,H01J29/00,G01J5/00,G01N23/00,G21C19/00,G01S3/00,A61B6/00,H01J25/00,G01D5/00,H01J3/00,H01Q3/00,G01N29/00,H04N1/00,G01J3/00,H01J35/00</t>
+  </si>
+  <si>
+    <t>A61G7/00,A47C17/00,A61G1/00,A47B23/00,B66B17/00,F16D3/00,F16D1/00,B23Q1/00,F16H3/00,F04C3/00,H04N23/00,H04N25/00,H05G1/00,G03B7/00,H04N13/00,H05G1/00,G01S3/00,F16H55/00,G01J5/00,B27B31/00,H05G1/00,G01T1/00,G01N23/00,H01J37/00,H01J31/00</t>
+  </si>
+  <si>
+    <t>A61M60/00,A61M1/00,A61B5/00,B01D29/00,B01D35/00,B01D61/00,B01D33/00,G01N33/00,B01D25/00,B01D46/00,G16H50/00,G16H10/00,B05B15/00,A47L15/00,F22B37/00,A47L9/00,G16H30/00,A23C9/00,C10G31/00,G16H20/00,A61M60/00,B41J5/00,G11B27/00,A61M1/00,G11B15/00,B01D61/00,B41B27/00,F16H55/00,A61B5/00,B01D29/00,G11B7/00,H04N5/00,A23C9/00,B66B1/00,G01N33/00,G01D9/00,G01P1/00,G06F7/00,C07C51/00,H04L67/00,G06F16/00,G06V10/00,G06F18/00,G06T7/00,H04N19/00,H04H60/00,G10L25/00,H04N21/00,G11B27/00,G10L17/00,G10L19/00,H04L41/00,G10L21/00,H04M1/00,B41B27/00,H04L27/00,H04L67/00,G02F1/00,G06V20/00,G10H3/00,G06F18/00,G06T7/00,G10L19/00,G06V10/00,G10L25/00,H04N25/00,G01N29/00,G04C23/00,A61B5/00,G01D9/00,G10L21/00,G01P3/00,G01N30/00,H03L7/00,G01S7/00,G01F1/00,G08C19/00,G01R23/00,H04L41/00,F23N5/00,H04M1/00,B60K35/00,H04W68/00,G04C21/00,H04L41/00,B60G17/00,G08B29/00,F24F11/00,H04N21/00,G06F11/00,G06M3/00,A61M60/00,B60W50/00,A61B5/00,G07C1/00,G11B15/00,H04H60/00,G03B7/00,F21V29/00,B03C3/00</t>
+  </si>
+  <si>
+    <t>血液浄化治療システム: A61M60/00,A61M1/00,A61B5/00,B01D29/00,B01D35/00,B01D61/00,B01D33/00,G01N33/00,B01D25/00,B01D46/00,G16H50/00,G16H10/00,B05B15/00,A47L15/00,F22B37/00,A47L9/00,G16H30/00,A23C9/00,C10G31/00,G16H20/00; 過去情報記憶・蓄積手段: A61M60/00,B41J5/00,G11B27/00,A61M1/00,G11B15/00,B01D61/00,B41B27/00,F16H55/00,A61B5/00,B01D29/00,G11B7/00,H04N5/00,A23C9/00,B66B1/00,G01N33/00,G01D9/00,G01P1/00,G06F7/00,C07C51/00,H04L67/00; 特定事項抽出・検索手段: G06F16/00,G06V10/00,G06F18/00,G06T7/00,H04N19/00,H04H60/00,G10L25/00,H04N21/00,G11B27/00,G10L17/00,G10L19/00,H04L41/00,G10L21/00,H04M1/00,B41B27/00,H04L27/00,H04L67/00,G02F1/00,G06V20/00,G10H3/00; 多発時間算出・分析手段: G06F18/00,G06T7/00,G10L19/00,G06V10/00,G10L25/00,H04N25/00,G01N29/00,G04C23/00,A61B5/00,G01D9/00,G10L21/00,G01P3/00,G01N30/00,H03L7/00,G01S7/00,G01F1/00,G08C19/00,G01R23/00,H04L41/00,F23N5/00; 表示制御・通知手段: H04M1/00,B60K35/00,H04W68/00,G04C21/00,H04L41/00,B60G17/00,G08B29/00,F24F11/00,H04N21/00,G06F11/00,G06M3/00,A61M60/00,B60W50/00,A61B5/00,G07C1/00,G11B15/00,H04H60/00,G03B7/00,F21V29/00,B03C3/00</t>
+  </si>
+  <si>
+    <t>A61M60/00,A61M1/00,B01D61/00,A61B5/00,B01D35/00,A61M60/00,A61M1/00,B01D61/00,A61B5/00,G11B27/00,G06F16/00,G06F18/00,G06V10/00,G11B27/00,H04N21/00,G06F18/00,A61B5/00,G01D9/00,G04C23/00,G06T7/00,H04W68/00,G08B29/00,H04N21/00,G06F11/00,H04L41/00</t>
+  </si>
+  <si>
+    <t>【課題】遊技者の注意を喚起する注意喚起表示を効果的に行うことが可能な遊技機を提供すること。 【解決手段】遊技機１では、遊技者に有利な特別遊技を実行するか否かが判定され、特別遊技を実行すると判定された場合に、特別遊技が実行される。また、遊技が進行していない客待ち状態において、のめり込み注意喚起表示と他の表示とを含む複数の表示を所定の順番で行うことが可能であり、のめり込み注意喚起表示に係る画像が重畳表示される背景画像の表示態様と、他の表示に係る画像が重畳表示される背景画像の表示態様とが共通している。</t>
+  </si>
+  <si>
+    <t>A63F13/00,G01F23/00,B60K35/00,E01F9/00,A63F7/00,B62J6/00,B60Q1/00,G08B21/00,G04C21/00,H04W68/00,H04M1/00,B60R21/00,G07B5/00,B66C15/00,G06F3/00,G07F17/00,F41A3/00,G09G5/00,B41J29/00,B60W50/00,A63F13/00,G05B19/00,H04M1/00,A63F7/00,G06F9/00,F24F11/00,F21V29/00,G11B3/00,H01H41/00,H04H60/00,G06F30/00,B23Q15/00,B41J19/00,G11B19/00,G06V30/00,B60W50/00,G06F21/00,G01G19/00,G07D7/00,B07C5/00,A63F13/00,G09G5/00,G05D1/00,G05B19/00,B60K35/00,A63F7/00,H03K17/00,G06F13/00,H04L67/00,H04M3/00,B60N2/00,H04N21/00,B23B31/00,B61G1/00,B60L1/00,B60W20/00,B25J9/00,H04N25/00,H04N19/00,B41B27/00,H04N13/00,H04N19/00,H04N1/00,G09G5/00,G06T3/00,G06V10/00,G06T7/00,H04N25/00,H04N23/00,A63F13/00,G06T5/00,H10K59/00,G06V30/00,B60Q1/00,B60K35/00,G06F3/00,H04N5/00,G03F7/00,G11B23/00,H01J31/00</t>
+  </si>
+  <si>
+    <t>注意喚起表示: A63F13/00,G01F23/00,B60K35/00,E01F9/00,A63F7/00,B62J6/00,B60Q1/00,G08B21/00,G04C21/00,H04W68/00,H04M1/00,B60R21/00,G07B5/00,B66C15/00,G06F3/00,G07F17/00,F41A3/00,G09G5/00,B41J29/00,B60W50/00; 特別遊技判定・実行: A63F13/00,G05B19/00,H04M1/00,A63F7/00,G06F9/00,F24F11/00,F21V29/00,G11B3/00,H01H41/00,H04H60/00,G06F30/00,B23Q15/00,B41J19/00,G11B19/00,G06V30/00,B60W50/00,G06F21/00,G01G19/00,G07D7/00,B07C5/00; 客待ち状態制御: A63F13/00,G09G5/00,G05D1/00,G05B19/00,B60K35/00,A63F7/00,H03K17/00,G06F13/00,H04L67/00,H04M3/00,B60N2/00,H04N21/00,B23B31/00,B61G1/00,B60L1/00,B60W20/00,B25J9/00,H04N25/00,H04N19/00,B41B27/00; 背景画像表示態様: H04N13/00,H04N19/00,H04N1/00,G09G5/00,G06T3/00,G06V10/00,G06T7/00,H04N25/00,H04N23/00,A63F13/00,G06T5/00,H10K59/00,G06V30/00,B60Q1/00,B60K35/00,G06F3/00,H04N5/00,G03F7/00,G11B23/00,H01J31/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,G08B21/00,A63F7/00,E01F9/00,H04W68/00,A63F13/00,A63F7/00,G05B19/00,G06F9/00,H04H60/00,A63F13/00,G09G5/00,A63F7/00,G05B19/00,G06F13/00,G09G5/00,G06T3/00,A63F13/00,H04N13/00,G06T7/00</t>
+  </si>
+  <si>
+    <t>衣類乾燥機</t>
+  </si>
+  <si>
+    <t>D06F58/02</t>
+  </si>
+  <si>
+    <t>【課題】ヒートポンプ装置を使った衣類乾燥機において、消費電力量の低減と乾燥性能の向上を実現する。 【解決手段】本発明の衣類乾燥機は、冷媒を圧縮する圧縮機２１と圧縮された冷媒の熱を放熱する放熱器２２と高圧の冷媒の圧力を減圧する絞り部２３と減圧されて低圧となった冷媒によって周囲から熱を奪う第一の吸熱器２４と第二の吸熱器２５とを冷媒が循環可能に管路で連結したヒートポンプ装置２０の第一の吸熱器２４と放熱器２２を循環風路７中に、第二の吸熱器２５を排気風路１０中にそれぞれ配置するとともに、第一の吸熱器２４と第二の吸熱器２５とは、並列関係をなすように２つに分岐された管路にそれぞれ接続したことにより、循環風路７外からの採熱効果を高めるとともに圧縮機２１の吸入冷媒圧力を高めることで消費電力量の低減と乾燥性能の向上を実現することができる。</t>
+  </si>
+  <si>
+    <t>F24F1/00,D06F58/00,D06F33/00,F01P5/00,A45D20/00,F24H15/00,F01P3/00,F24F3/00,D06F105/00,F25B41/00,F27B3/00,F02M26/00,D06F103/00,F24F11/00,F27B15/00,F27B7/00,F01P11/00,H01L23/00,F01P7/00,F27B5/00,F02M26/00,F24S10/00,F24F1/00,F24F3/00,F01K23/00,G21C15/00,F27B1/00,F28D1/00,F27B3/00,F22G5/00,H02M7/00,B60G11/00,A45D20/00,B01F25/00,E03B7/00,H02K1/00,F16L3/00,B61C5/00,F16H47/00,F27B15/00,F24H15/00,G06F1/00,F16H61/00,F24F11/00,F01P5/00,H02J3/00,H01S3/00,H02P23/00,H05G1/00,F02B37/00,F01P3/00,F04B45/00,F04F5/00,F22D1/00,H01L23/00,B63H11/00,F25B30/00,B60G13/00,F04D13/00,F04B43/00,D06F58/00,D06F33/00,F24F1/00,D21F5/00,D06F101/00,F26B3/00,A23L3/00,D06B3/00,A45D20/00,A23B7/00,D06F105/00,D01F2/00,D06F75/00,D01D5/00,A47K10/00,B01D53/00,B41F15/00,C14B1/00,D21J1/00,C10B57/00,F24F3/00,H02K9/00,F24F1/00,F24F11/00,F27B1/00,A45D20/00,G21C15/00,A47L5/00,F23B80/00,F02M31/00,F24D5/00,E21F1/00,F23R3/00,F27B15/00,F27B3/00,F24F13/00,C10B21/00,F24F7/00,F25D17/00,A23L3/00</t>
+  </si>
+  <si>
+    <t>ヒートポンプ回路構成: F24F1/00,D06F58/00,D06F33/00,F01P5/00,A45D20/00,F24H15/00,F01P3/00,F24F3/00,D06F105/00,F25B41/00,F27B3/00,F02M26/00,D06F103/00,F24F11/00,F27B15/00,F27B7/00,F01P11/00,H01L23/00,F01P7/00,F27B5/00; 吸熱器の並列配置: F02M26/00,F24S10/00,F24F1/00,F24F3/00,F01K23/00,G21C15/00,F27B1/00,F28D1/00,F27B3/00,F22G5/00,H02M7/00,B60G11/00,A45D20/00,B01F25/00,E03B7/00,H02K1/00,F16L3/00,B61C5/00,F16H47/00,F27B15/00; 消費電力低減技術: F24H15/00,G06F1/00,F16H61/00,F24F11/00,F01P5/00,H02J3/00,H01S3/00,H02P23/00,H05G1/00,F02B37/00,F01P3/00,F04B45/00,F04F5/00,F22D1/00,H01L23/00,B63H11/00,F25B30/00,B60G13/00,F04D13/00,F04B43/00; 乾燥性能向上技術: D06F58/00,D06F33/00,F24F1/00,D21F5/00,D06F101/00,F26B3/00,A23L3/00,D06B3/00,A45D20/00,A23B7/00,D06F105/00,D01F2/00,D06F75/00,D01D5/00,A47K10/00,B01D53/00,B41F15/00,C14B1/00,D21J1/00,C10B57/00; 風路設計・配置: F24F3/00,H02K9/00,F24F1/00,F24F11/00,F27B1/00,A45D20/00,G21C15/00,A47L5/00,F23B80/00,F02M31/00,F24D5/00,E21F1/00,F23R3/00,F27B15/00,F27B3/00,F24F13/00,C10B21/00,F24F7/00,F25D17/00,A23L3/00</t>
+  </si>
+  <si>
+    <t>D06F58/00,F25B41/00,F01P5/00,F24H15/00,D06F33/00,F28D1/00,F24F1/00,F24F3/00,F24S10/00,F01K23/00,F24H15/00,F24F11/00,F01P5/00,H02P23/00,F16H61/00,D06F58/00,D06F33/00,F26B3/00,D06F101/00,F24F1/00,F24F3/00,F24F1/00,F24F11/00,F23B80/00,F02M31/00</t>
+  </si>
+  <si>
+    <t>電気掃除機</t>
+  </si>
+  <si>
+    <t>A47L9/00</t>
+  </si>
+  <si>
+    <t>【課題】ホースの収納時にホースへの荷重負担が少ない電気掃除機を提供する。 【解決手段】被係止部Ａ８を有する掃除機本体２と、一端が掃除機本体２に接続され他端に吸込把持部５を有するホース３と、一端が吸込把持部５に接続され他端に床用吸込具７が接続される延長管６と、延長管６に設けられ、スタンド収納時に被係止部Ａ８に係止されるフック９と、吸込把持部５の後端部に設けられた被掛止部Ｂ２０と、ホース３に取り付けられたホース掛止具４とを備え、ホース掛止具４にホース３の収納時に被掛止部Ｂ２０に着脱自在に掛止させるフック部１５を設けたもので、スタンド収納時に、ホース掛止具４のフック部１５を被掛止部Ｂ２０に掛止めすることで、ホース掛止具４からのホース３への荷重が分散され、ホース３の寿命が長い電気掃除機１を実現できる。</t>
+  </si>
+  <si>
+    <t>A47L5/00,B08B9/00,F16L33/00,A01D34/00,B66C13/00,A47L23/00,B65H75/00,A47L11/00,A47L9/00,B04C5/00,B65H39/00,A01D75/00,B65G45/00,B62J50/00,D01G15/00,A47K10/00,B66D1/00,B60S1/00,B63B21/00,F28G15/00,F16L33/00,F16F1/00,F16L3/00,F16L11/00,H01R33/00,A62C33/00,F22B17/00,F16L13/00,F16D3/00,F16C19/00,B65G39/00,F16K27/00,E04H12/00,D01H5/00,G21C5/00,E21D15/00,E04B1/00,B65H31/00,B65D63/00,B01D33/00,F16L33/00,F16L37/00,H01R13/00,F16L55/00,F16L41/00,H01R33/00,B65H75/00,B62B1/00,F04B9/00,F16D13/00,B01F35/00,F16L29/00,B65H29/00,F21V21/00,A61M39/00,F16L13/00,B23Q1/00,F16B12/00,F16D3/00,B23B31/00,A47L5/00,A47L11/00,A47L9/00,B65H39/00,B08B9/00,B08B1/00,H01R39/00,B05B15/00,B62H1/00,A47L23/00,A63B60/00,A61C17/00,F16M11/00,A47L13/00,A01D34/00,B60N2/00,F03D13/00,B65H31/00,A47F5/00,B65G45/00</t>
+  </si>
+  <si>
+    <t>ホース収納機構: A47L5/00,B08B9/00,F16L33/00,A01D34/00,B66C13/00,A47L23/00,B65H75/00,A47L11/00,A47L9/00,B04C5/00,B65H39/00,A01D75/00,B65G45/00,B62J50/00,D01G15/00,A47K10/00,B66D1/00,B60S1/00,B63B21/00,F28G15/00; 荷重分散構造: F16L33/00,F16F1/00,F16L3/00,F16L11/00,H01R33/00,A62C33/00,F22B17/00,F16L13/00,F16D3/00,F16C19/00,B65G39/00,F16K27/00,E04H12/00,D01H5/00,G21C5/00,E21D15/00,E04B1/00,B65H31/00,B65D63/00,B01D33/00; 着脱可能な掛止機構: F16L33/00,F16L37/00,H01R13/00,F16L55/00,F16L41/00,H01R33/00,B65H75/00,B62B1/00,F04B9/00,F16D13/00,B01F35/00,F16L29/00,B65H29/00,F21V21/00,A61M39/00,F16L13/00,B23Q1/00,F16B12/00,F16D3/00,B23B31/00; 掃除機スタンド収納構造: A47L5/00,A47L11/00,A47L9/00,B65H39/00,B08B9/00,B08B1/00,H01R39/00,B05B15/00,B62H1/00,A47L23/00,A63B60/00,A61C17/00,F16M11/00,A47L13/00,A01D34/00,B60N2/00,F03D13/00,B65H31/00,A47F5/00,B65G45/00</t>
+  </si>
+  <si>
+    <t>A47L5/00,A47L9/00,F16L33/00,B65H75/00,B66C13/00,F16L33/00,F16L3/00,F16L11/00,A62C33/00,F16F1/00,F16L33/00,F16L37/00,F16L55/00,F16L41/00,B65H75/00,A47L5/00,A47L9/00,A47L11/00,B62H1/00,B08B1/00</t>
+  </si>
+  <si>
+    <t>遊技台</t>
+  </si>
+  <si>
+    <t>【課題】報知状態かどうかを区別することが可能で、遊技者に誤解や不快感を与えることを防止する遊技台の提供。 【解決手段】第一の制御手段は、第一の表示手段を制御する第一の表示制御手段を備え、第二の制御手段は、第二の表示手段を制御する第二の表示制御手段を備え、報知状態でない第一の遊技では、第一の表示制御手段は、停止操作を示す情報を第一の表示態様で表示し、第二の表示制御手段は、停止操作を示す情報を第二の表示態様で表示し、報知状態である第二の遊技では、第一の表示制御手段は、停止操作を示す情報を第一の表示態様で表示し、第二の表示制御手段は、停止操作を示す情報を第三の表示態様で表示し、第二の表示態様の表示期間は、第三の表示態様の表示期間よりも短く、第一の表示制御手段は、第一の遊技において第二の表示手段による停止操作を示す情報の表示を終了しても、第一の表示手段による停止操作を示す情報の表示を継続する。</t>
+  </si>
+  <si>
+    <t>A63F13/00,H04H60/00,G11B15/00,H03K17/00,B60K35/00,G08B29/00,G06F11/00,G11B19/00,G05B19/00,F24F11/00,D06F34/00,G01R19/00,B60T8/00,B61G1/00,G05D1/00,H03K21/00,F02D41/00,H04N21/00,B60L1/00,H01J37/00,A63F13/00,B60K35/00,G05B19/00,G09G5/00,G01S7/00,H02M7/00,G06F3/00,G09G3/00,G07C1/00,G01R13/00,H04N19/00,H04N21/00,G03G15/00,G05F1/00,F04B27/00,B62M6/00,F21V29/00,H03K17/00,D06F34/00,B61G1/00,D03D51/00,A63F13/00,H02P8/00,G01F23/00,B65B57/00,B41L39/00,H01H71/00,G01S7/00,D06F105/00,B41J21/00,E06B9/00,G06M3/00,B60K35/00,B41J29/00,F01D21/00,D01H13/00,F02D17/00,G09F11/00,G04F7/00,B23D33/00,A63F13/00,B60K35/00,H04M1/00,G01S7/00,B60W50/00,A63F7/00,H05B41/00,G06F21/00,H05B45/00,H04N23/00,B60L1/00,H04N21/00,D06F34/00,H02G15/00,G07D11/00,H01H13/00,F41A3/00,H04H60/00,H04M3/00,H04W12/00</t>
+  </si>
+  <si>
+    <t>報知状態判別制御: A63F13/00,H04H60/00,G11B15/00,H03K17/00,B60K35/00,G08B29/00,G06F11/00,G11B19/00,G05B19/00,F24F11/00,D06F34/00,G01R19/00,B60T8/00,B61G1/00,G05D1/00,H03K21/00,F02D41/00,H04N21/00,B60L1/00,H01J37/00; 表示制御手段: A63F13/00,B60K35/00,G05B19/00,G09G5/00,G01S7/00,H02M7/00,G06F3/00,G09G3/00,G07C1/00,G01R13/00,H04N19/00,H04N21/00,G03G15/00,G05F1/00,F04B27/00,B62M6/00,F21V29/00,H03K17/00,D06F34/00,B61G1/00; 停止操作情報表示: D03D51/00,A63F13/00,H02P8/00,G01F23/00,B65B57/00,B41L39/00,H01H71/00,G01S7/00,D06F105/00,B41J21/00,E06B9/00,G06M3/00,B60K35/00,B41J29/00,F01D21/00,D01H13/00,F02D17/00,G09F11/00,G04F7/00,B23D33/00; 遊技者への誤解・不快感防止: A63F13/00,B60K35/00,H04M1/00,G01S7/00,B60W50/00,A63F7/00,H05B41/00,G06F21/00,H05B45/00,H04N23/00,B60L1/00,H04N21/00,D06F34/00,H02G15/00,G07D11/00,H01H13/00,F41A3/00,H04H60/00,H04M3/00,H04W12/00</t>
+  </si>
+  <si>
+    <t>A63F13/00,G08B29/00,G05B19/00,G06F11/00,H04H60/00,A63F13/00,G09G5/00,G09G3/00,G06F3/00,G05B19/00,A63F13/00,D03D51/00,B41L39/00,B65B57/00,H01H71/00,A63F13/00,A63F7/00,H05B45/00,H05B41/00,H04N23/00</t>
+  </si>
+  <si>
+    <t>内視鏡制御装置、内視鏡システム及びプログラム</t>
+  </si>
+  <si>
+    <t>A61B1/005</t>
+  </si>
+  <si>
+    <t>A61B1/00;A61B1/045;G02B23/24</t>
+  </si>
+  <si>
+    <t>【課題】内視鏡検査に用いられる湾曲操作指示をシームレスに行うことができる内視鏡制御装置を提供する。 【解決手段】内視鏡制御装置としてのスマートフォン３は、内視鏡装置２の挿入部４の湾曲部４ｂの湾曲操作を制御する。スマートフォン３は、ユーザにより把持される筐体３ａの所定の軸回りの回動及び筐体３ａの所定の方向への移動を検出し、検出された回動又は移動に基づいて第１の動作の有無又は第１の動作とは異なる第２の動作の有無を判定し、第１の動作があったときは第１の動作に割り当てられた湾曲部４ｂに対する第１の湾曲操作の第１の実行指示を、第２の動作があったときは第２の動作に割り当てられた湾曲部４ｂに対する第２の湾曲操作の第２の実行指示を内視鏡装置２へ送信する。</t>
+  </si>
+  <si>
+    <t>A61B1/00,F41A17/00,E05F15/00,H04N23/00,B63B23/00,D05C11/00,B65H23/00,E21B34/00,H04N3/00,B62D9/00,B61D9/00,B23Q15/00,G11B17/00,B60L1/00,B63H20/00,G02F1/00,G02B5/00,F42B19/00,G11B7/00,D04C3/00,H04N13/00,E05F15/00,G06F3/00,H04N19/00,G01C19/00,B62M9/00,A63F13/00,B60R22/00,H01H25/00,H01H19/00,B43K24/00,G01S13/00,F16L3/00,H02P21/00,G01K13/00,D06F23/00,B60R25/00,G07D11/00,H02P6/00,G06V20/00,H04N13/00,H04N23/00,A61B90/00,A61B1/00,G01F23/00,E05F15/00,A61B34/00,F24F11/00,G16H40/00,H04N21/00,G01Q60/00,A01D34/00,H04M1/00,H04L67/00,H04B1/00,H04B10/00,B62M6/00,G01L3/00,F41G5/00,B23B31/00,B43K24/00,E05F15/00,F41A17/00,B26D1/00,H01H17/00,H01H41/00,F16L3/00,E06B9/00,H04N23/00,E05D15/00,B63H20/00,A61B1/00,B21B39/00,A01D19/00,H03J5/00,H01H19/00,G01D5/00,G01L5/00,G06F3/00,F15B13/00</t>
+  </si>
+  <si>
+    <t>湾曲操作制御: A61B1/00,F41A17/00,E05F15/00,H04N23/00,B63B23/00,D05C11/00,B65H23/00,E21B34/00,H04N3/00,B62D9/00,B61D9/00,B23Q15/00,G11B17/00,B60L1/00,B63H20/00,G02F1/00,G02B5/00,F42B19/00,G11B7/00,D04C3/00; 動作検出・判定: H04N13/00,E05F15/00,G06F3/00,H04N19/00,G01C19/00,B62M9/00,A63F13/00,B60R22/00,H01H25/00,H01H19/00,B43K24/00,G01S13/00,F16L3/00,H02P21/00,G01K13/00,D06F23/00,B60R25/00,G07D11/00,H02P6/00,G06V20/00; スマートフォン連携制御: H04N13/00,H04N23/00,A61B90/00,A61B1/00,G01F23/00,E05F15/00,A61B34/00,F24F11/00,G16H40/00,H04N21/00,G01Q60/00,A01D34/00,H04M1/00,H04L67/00,H04B1/00,H04B10/00,B62M6/00,G01L3/00,F41G5/00,B23B31/00; シームレス操作: B43K24/00,E05F15/00,F41A17/00,B26D1/00,H01H17/00,H01H41/00,F16L3/00,E06B9/00,H04N23/00,E05D15/00,B63H20/00,A61B1/00,B21B39/00,A01D19/00,H03J5/00,H01H19/00,G01D5/00,G01L5/00,G06F3/00,F15B13/00</t>
+  </si>
+  <si>
+    <t>A61B1/00,H04N23/00,B62D9/00,F41A17/00,E05F15/00,G06F3/00,G01C19/00,H01H25/00,H01H19/00,H04N13/00,A61B1/00,A61B90/00,A61B34/00,G16H40/00,H04N23/00,H01H41/00,H01H17/00,H04N23/00,E05F15/00,B43K24/00</t>
+  </si>
+  <si>
+    <t>【課題】遊技の多様化を好適に実現することができる遊技機を提供する。 【解決手段】遊技盤ユニットは、遊技領域が形成されている遊技盤を有している。遊技領域の下部には、通常よりも遊技者に有利な特別遊技状態に移行した場合に入球対象となる可変入賞ユニット８３Ｒが配設されている。可変入賞ユニット８３Ｒは、左右に並設された第１入球部３３１及び第２入球部３４１と、それら入球部３３１，３４１の間に配設された可動体４５０Ｒとを有している。可動体４５０Ｒは遊技盤の前面に沿って左右に回動可能に保持されており、その上面４５２Ｒが遊技球用の転動面となっている。可動体４５０Ｒを回動させて上面４５２Ｒが第１入球部３３１及び第２入球部３４１の何れかへ下り傾斜となるように姿勢を変更させることにより、両入球部３３１，３４１の間にそれら入球部３３１，３４１の一方へ遊技球を案内する案内経路が形成される。</t>
+  </si>
+  <si>
+    <t>A63F7/00,A47C4/00,F04D29/00,F04C14/00,B21D37/00,F04C28/00,A61M60/00,B62B1/00,B41J19/00,H01R4/00,A43B7/00,F41A9/00,G11B3/00,B62D7/00,B61H13/00,B60K35/00,G08C19/00,A63D1/00,A63F9/00,B23Q1/00,A63F7/00,G01C19/00,A63G1/00,A47C17/00,E05B37/00,F16D3/00,H01H19/00,B65H5/00,B28B1/00,F26B11/00,F42C15/00,B30B11/00,F16H13/00,B60C25/00,G11B17/00,F16H19/00,B06B1/00,B01F29/00,F16D55/00,B01F27/00,A63F7/00,E05F15/00,F16D3/00,G11B5/00,H01Q3/00,F27B9/00,E05D15/00,B62D9/00,H01H17/00,A63F13/00,G11B3/00,G05G9/00,F23H7/00,B43K24/00,B23Q5/00,A63B60/00,G03B7/00,B01J8/00,E06B9/00,H01C10/00,A63F7/00,H04N19/00,A63F13/00,F04B1/00,H01L21/00,B29B7/00,C03B9/00,B23B39/00,H01L31/00,B41F3/00,G08B5/00,G05B19/00,B23D37/00,B60K35/00,G11B7/00,B01F27/00,B23Q41/00,H02B1/00,F04D25/00,H01H13/00</t>
+  </si>
+  <si>
+    <t>可変入賞ユニット構造: A63F7/00,A47C4/00,F04D29/00,F04C14/00,B21D37/00,F04C28/00,A61M60/00,B62B1/00,B41J19/00,H01R4/00,A43B7/00,F41A9/00,G11B3/00,B62D7/00,B61H13/00,B60K35/00,G08C19/00,A63D1/00,A63F9/00,B23Q1/00; 可動体の回動機構: A63F7/00,G01C19/00,A63G1/00,A47C17/00,E05B37/00,F16D3/00,H01H19/00,B65H5/00,B28B1/00,F26B11/00,F42C15/00,B30B11/00,F16H13/00,B60C25/00,G11B17/00,F16H19/00,B06B1/00,B01F29/00,F16D55/00,B01F27/00; 入球案内経路形成: A63F7/00,E05F15/00,F16D3/00,G11B5/00,H01Q3/00,F27B9/00,E05D15/00,B62D9/00,H01H17/00,A63F13/00,G11B3/00,G05G9/00,F23H7/00,B43K24/00,B23Q5/00,A63B60/00,G03B7/00,B01J8/00,E06B9/00,H01C10/00; 遊技盤ユニット構成: A63F7/00,H04N19/00,A63F13/00,F04B1/00,H01L21/00,B29B7/00,C03B9/00,B23B39/00,H01L31/00,B41F3/00,G08B5/00,G05B19/00,B23D37/00,B60K35/00,G11B7/00,B01F27/00,B23Q41/00,H02B1/00,F04D25/00,H01H13/00</t>
+  </si>
+  <si>
+    <t>A63F7/00,A63F7/00,G01C19/00,F16D3/00,A63G1/00,H01H19/00,A63F7/00,E05F15/00,F16D3/00,A63F13/00,B62D9/00,A63F7/00,A63F13/00,B23B39/00,B29B7/00,C03B9/00</t>
+  </si>
+  <si>
+    <t>情報処理装置及びプログラム</t>
+  </si>
+  <si>
+    <t>A63F13/63</t>
+  </si>
+  <si>
+    <t>A63F13/80;A63F13/822;A63F13/35</t>
+  </si>
+  <si>
+    <t>【課題】戦略性を向上させたゲーム制御を行う情報処理装置を提供すること。 【解決手段】表示順が設定された複数の図柄による図柄変動を表示する複数の図柄表示手段と、複数の図柄表示手段のそれぞれに対応付けて、表示順が設定された複数の図柄を記憶する図柄記憶手段と、複数の図柄表示手段に表示される図柄変動の開始及び停止を制御する図柄制御手段と、図柄変動の停止により複数の図柄表示手段に表示された図柄の組み合わせに応じてゲーム制御を行うゲーム制御手段と、図柄記憶手段が記憶する表示順が設定された複数の図柄に対する編集操作をプレイヤから受け付け、編集操作に従って図柄記憶手段が記憶する表示順が設定された複数の図柄を編集する図柄編集手段と、を有することにより上記課題を解決する。</t>
+  </si>
+  <si>
+    <t>G05B19/00,G09G5/00,H03K17/00,B60K35/00,G06F3/00,B60T8/00,B41F33/00,G09G1/00,G05B11/00,G08B5/00,B41K3/00,B65B57/00,G03F7/00,B41L39/00,B23B39/00,F42B19/00,B61L25/00,G02F1/00,B60W30/00,B41J21/00,G09G5/00,G06F7/00,C09B35/00,A63F13/00,G06V10/00,G09B1/00,H04M1/00,G01D9/00,G06F3/00,G11B13/00,H04N21/00,G11B7/00,G09B3/00,G06V30/00,G11B23/00,B41J5/00,D05B19/00,G09C1/00,G01S5/00,G05B19/00,A63F13/00,G01F23/00,G09G5/00,G05B19/00,G06F3/00,B60K35/00,B43K24/00,G05D1/00,H03K17/00,G05G1/00,G09B1/00,H04M1/00,F04B27/00,B61G1/00,G06M1/00,B23B31/00,G07C5/00,G07C3/00,G01F1/00,G09G3/00,A63F13/00,G06F3/00,H04N21/00,G05B19/00,G05D1/00,G09G5/00,F16H59/00,B43K24/00,H03K17/00,G06V10/00,B41B27/00,H03J5/00,G06K11/00,G07D11/00,B63H25/00,B23B39/00,B25J13/00,B60W50/00,B60K35/00,G11B27/00,A63F13/00,G06F3/00,H04N21/00,H04L41/00,H04N19/00,B60W20/00,H04W36/00,H03M11/00,H04M1/00,H04W40/00,H03K17/00,F16H61/00,H04L45/00,B62M9/00,B60G17/00,H01H41/00,A47C7/00,H03K19/00,G06F119/00,B60K26/00</t>
+  </si>
+  <si>
+    <t>図柄表示制御: G05B19/00,G09G5/00,H03K17/00,B60K35/00,G06F3/00,B60T8/00,B41F33/00,G09G1/00,G05B11/00,G08B5/00,B41K3/00,B65B57/00,G03F7/00,B41L39/00,B23B39/00,F42B19/00,B61L25/00,G02F1/00,B60W30/00,B41J21/00; 図柄記憶・編集: G09G5/00,G06F7/00,C09B35/00,A63F13/00,G06V10/00,G09B1/00,H04M1/00,G01D9/00,G06F3/00,G11B13/00,H04N21/00,G11B7/00,G09B3/00,G06V30/00,G11B23/00,B41J5/00,D05B19/00,G09C1/00,G01S5/00,G05B19/00; ゲーム制御手段: A63F13/00,G01F23/00,G09G5/00,G05B19/00,G06F3/00,B60K35/00,B43K24/00,G05D1/00,H03K17/00,G05G1/00,G09B1/00,H04M1/00,F04B27/00,B61G1/00,G06M1/00,B23B31/00,G07C5/00,G07C3/00,G01F1/00,G09G3/00; プレイヤ操作受付: A63F13/00,G06F3/00,H04N21/00,G05B19/00,G05D1/00,G09G5/00,F16H59/00,B43K24/00,H03K17/00,G06V10/00,B41B27/00,H03J5/00,G06K11/00,G07D11/00,B63H25/00,B23B39/00,B25J13/00,B60W50/00,B60K35/00,G11B27/00; 戦略性向上機能: A63F13/00,G06F3/00,H04N21/00,H04L41/00,H04N19/00,B60W20/00,H04W36/00,H03M11/00,H04M1/00,H04W40/00,H03K17/00,F16H61/00,H04L45/00,B62M9/00,B60G17/00,H01H41/00,A47C7/00,H03K19/00,G06F119/00,B60K26/00</t>
+  </si>
+  <si>
+    <t>G05B19/00,G09G5/00,G09G1/00,G06F3/00,G05B11/00,G06F7/00,A63F13/00,G06F3/00,G09G5/00,G09B1/00,A63F13/00,G05B19/00,G09G5/00,G06F3/00,G05G1/00,A63F13/00,G06F3/00,H04N21/00,G05B19/00,G09G5/00,A63F13/00,G06F3/00,H04N21/00,H03M11/00,H04N19/00</t>
+  </si>
+  <si>
+    <t>医用画像診断装置及び画像処理装置</t>
+  </si>
+  <si>
+    <t>G06T7/32</t>
+  </si>
+  <si>
+    <t>【課題】異なるモダリティで撮像された複数の画像データや異なる時間に撮像された複数の画像データに基づき、効率的にこれらの画像データの位置合わせを行うことができる医用画像診断装置及び画像処理装置を提供する。 【解決手段】医用画像診断装置のデータ取得部は、被検体内の３次元領域を対象とする第１のボリュームデータと第２のボリュームデータとを取得する。設定部は、少なくとも前記第１のボリュームデータに基づく画像に対する操作入力に従って位置合わせ対象とする対象部位を設定する。位置調整部は、対象部位に基づき位置合わせ用のテンプレートを作成する。また位置調整部は、当該テンプレートに基づき第２のボリュームデータにおけるテンプレートに対応する照合領域を求める。また位置調整部は、テンプレートと前記照合領域とに基づいて、第１のボリュームデータと第２のボリュームデータとの位置合わせを行う。</t>
+  </si>
+  <si>
+    <t>H04N13/00,H04N25/00,H04N1/00,G06V10/00,H04N19/00,G01R33/00,H04N5/00,G02B30/00,H04N23/00,A61B5/00,H04N9/00,G06T7/00,G03H1/00,H01J31/00,G03F7/00,H04N21/00,G01S13/00,G01C11/00,H05G1/00,G01N23/00,H04N23/00,G06V10/00,G06F3/00,G05B19/00,G06T7/00,A61B6/00,H01J37/00,H04N25/00,H04N13/00,H03J5/00,H04N21/00,H04N19/00,G03B7/00,G06V30/00,G01C11/00,G06T3/00,G01R33/00,G16H30/00,G03F1/00,G09G5/00,G06V10/00,G06V30/00,G06T7/00,H04N1/00,H04N19/00,G06T3/00,G06F18/00,B23Q35/00,G07D7/00,G06T5/00,G03F1/00,H04N25/00,G01S13/00,G10L17/00,G01C11/00,E04B2/00,H04N5/00,H04N21/00,A61B34/00,G01V8/00,H04N13/00,G06V10/00,G06V30/00,G06T3/00,H04N25/00,H04N19/00,G06T7/00,H04N1/00,G01R33/00,H03J5/00,G01C11/00,H04N23/00,G07D7/00,G03F7/00,B23K26/00,G01S13/00,G03F1/00,G16H30/00,G06T5/00,H01H1/00,H04N13/00,H04N23/00,H04N25/00,H04N1/00,G06V10/00,H04N5/00,A61B6/00,H04N19/00,H04N9/00,G03G15/00,G01R33/00,A61B5/00,H04N3/00,H01J31/00,G01N23/00,G16H40/00,A61B3/00,G03C8/00,H05G1/00,G16H30/00</t>
+  </si>
+  <si>
+    <t>異種医用画像データ取得: H04N13/00,H04N25/00,H04N1/00,G06V10/00,H04N19/00,G01R33/00,H04N5/00,G02B30/00,H04N23/00,A61B5/00,H04N9/00,G06T7/00,G03H1/00,H01J31/00,G03F7/00,H04N21/00,G01S13/00,G01C11/00,H05G1/00,G01N23/00; 対象部位設定・操作入力: H04N23/00,G06V10/00,G06F3/00,G05B19/00,G06T7/00,A61B6/00,H01J37/00,H04N25/00,H04N13/00,H03J5/00,H04N21/00,H04N19/00,G03B7/00,G06V30/00,G01C11/00,G06T3/00,G01R33/00,G16H30/00,G03F1/00,G09G5/00; テンプレート作成・照合領域抽出: G06V10/00,G06V30/00,G06T7/00,H04N1/00,H04N19/00,G06T3/00,G06F18/00,B23Q35/00,G07D7/00,G06T5/00,G03F1/00,H04N25/00,G01S13/00,G10L17/00,G01C11/00,E04B2/00,H04N5/00,H04N21/00,A61B34/00,G01V8/00; 画像位置合わせアルゴリズム: H04N13/00,G06V10/00,G06V30/00,G06T3/00,H04N25/00,H04N19/00,G06T7/00,H04N1/00,G01R33/00,H03J5/00,G01C11/00,H04N23/00,G07D7/00,G03F7/00,B23K26/00,G01S13/00,G03F1/00,G16H30/00,G06T5/00,H01H1/00; 医用画像診断装置・画像処理装置の構成: H04N13/00,H04N23/00,H04N25/00,H04N1/00,G06V10/00,H04N5/00,A61B6/00,H04N19/00,H04N9/00,G03G15/00,G01R33/00,A61B5/00,H04N3/00,H01J31/00,G01N23/00,G16H40/00,A61B3/00,G03C8/00,H05G1/00,G16H30/00</t>
+  </si>
+  <si>
+    <t>A61B5/00,H04N13/00,G06V10/00,G01R33/00,H04N25/00,G06F3/00,G06V10/00,G06T7/00,A61B6/00,H04N23/00,G06V10/00,G06T7/00,G06T3/00,G06F18/00,G06T5/00,G06T3/00,G06T7/00,G06V10/00,H04N13/00,H04N25/00,A61B6/00,G06V10/00,H04N13/00,H04N23/00,H04N25/00</t>
+  </si>
+  <si>
+    <t>actual_all_subclass_count</t>
+  </si>
+  <si>
+    <t>middle_predicted_subclass_count</t>
+  </si>
+  <si>
+    <t>middle_main_subclass_hit_count</t>
+  </si>
+  <si>
+    <t>middle_main_subclass_miss_count</t>
+  </si>
+  <si>
+    <t>middle_all_subclass_hit_count</t>
+  </si>
+  <si>
+    <t>middle_all_subclass_miss_count</t>
+  </si>
+  <si>
+    <t>final_predicted_subclass_count</t>
+  </si>
+  <si>
+    <t>final_main_subclass_hit_count</t>
+  </si>
+  <si>
+    <t>final_main_subclass_miss_count</t>
+  </si>
+  <si>
+    <t>final_all_subclass_hit_count</t>
+  </si>
+  <si>
+    <t>final_all_subclass_miss_count</t>
   </si>
 </sst>
 </file>
@@ -712,20 +841,31 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2082C9BA-CBF1-4F86-AD06-97A3396FFC3F}" name="表2" displayName="表2" ref="I1:S26" totalsRowShown="0">
-  <autoFilter ref="I1:S26" xr:uid="{2082C9BA-CBF1-4F86-AD06-97A3396FFC3F}"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2082C9BA-CBF1-4F86-AD06-97A3396FFC3F}" name="表2" displayName="表2" ref="J1:AE26" totalsRowShown="0">
+  <autoFilter ref="J1:AE26" xr:uid="{2082C9BA-CBF1-4F86-AD06-97A3396FFC3F}"/>
+  <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{D0A4EA6B-EBB3-4AEF-97AA-D9F4EEFE61A8}" name="actual_all_ipc_count"/>
-    <tableColumn id="2" xr3:uid="{56EF71F3-3D01-4C5C-A94D-A7F2E43828CE}" name="middle_predicted_ipc_count"/>
-    <tableColumn id="3" xr3:uid="{54C8BBCA-28D2-4EE9-91DC-57A22859F15E}" name="middle_main_hit_count"/>
-    <tableColumn id="4" xr3:uid="{20A7E4E7-06BA-42CA-B498-96DFD833EFD9}" name="middle_main_miss_count"/>
-    <tableColumn id="5" xr3:uid="{AB95CAD9-E0C4-4E60-BC42-9D4823211F45}" name="middle_all_hit_count"/>
-    <tableColumn id="6" xr3:uid="{E747A284-031F-4278-934B-81318A5D0CE1}" name="middle_all_miss_count"/>
-    <tableColumn id="7" xr3:uid="{7CCB3695-2C3A-453E-A9F5-28AE4AA85186}" name="final_predicted_ipc_count"/>
-    <tableColumn id="8" xr3:uid="{12D608B1-FBDD-4C3E-8658-831EE5BB9DF4}" name="final_main_hit_count"/>
-    <tableColumn id="9" xr3:uid="{C0A99FDD-0D0B-4C51-A208-B1E1F955F177}" name="final_main_miss_count"/>
-    <tableColumn id="10" xr3:uid="{68A54F4C-9488-4E36-9D2C-29867F8FCF5B}" name="final_all_hit_count"/>
-    <tableColumn id="11" xr3:uid="{B4EB9896-267F-40CC-8DDD-92253A87B0D5}" name="final_all_miss_count"/>
+    <tableColumn id="2" xr3:uid="{56EF71F3-3D01-4C5C-A94D-A7F2E43828CE}" name="actual_all_subclass_count"/>
+    <tableColumn id="3" xr3:uid="{54C8BBCA-28D2-4EE9-91DC-57A22859F15E}" name="middle_predicted_ipc_count"/>
+    <tableColumn id="4" xr3:uid="{20A7E4E7-06BA-42CA-B498-96DFD833EFD9}" name="middle_predicted_subclass_count"/>
+    <tableColumn id="5" xr3:uid="{AB95CAD9-E0C4-4E60-BC42-9D4823211F45}" name="middle_main_hit_count"/>
+    <tableColumn id="6" xr3:uid="{E747A284-031F-4278-934B-81318A5D0CE1}" name="middle_main_miss_count"/>
+    <tableColumn id="7" xr3:uid="{7CCB3695-2C3A-453E-A9F5-28AE4AA85186}" name="middle_main_subclass_hit_count"/>
+    <tableColumn id="8" xr3:uid="{12D608B1-FBDD-4C3E-8658-831EE5BB9DF4}" name="middle_main_subclass_miss_count"/>
+    <tableColumn id="9" xr3:uid="{C0A99FDD-0D0B-4C51-A208-B1E1F955F177}" name="middle_all_hit_count"/>
+    <tableColumn id="10" xr3:uid="{68A54F4C-9488-4E36-9D2C-29867F8FCF5B}" name="middle_all_miss_count"/>
+    <tableColumn id="11" xr3:uid="{B4EB9896-267F-40CC-8DDD-92253A87B0D5}" name="middle_all_subclass_hit_count"/>
+    <tableColumn id="12" xr3:uid="{52951874-A4F7-452C-A020-F01FD1BF007F}" name="middle_all_subclass_miss_count"/>
+    <tableColumn id="13" xr3:uid="{0EE38102-0288-4094-AB74-3F9C0C1D8D58}" name="final_predicted_ipc_count"/>
+    <tableColumn id="14" xr3:uid="{E10870EF-61DC-4A83-B5C9-527F1EA25869}" name="final_predicted_subclass_count"/>
+    <tableColumn id="15" xr3:uid="{C24C080B-4196-40A5-93E1-AD810F95D6CC}" name="final_main_hit_count"/>
+    <tableColumn id="16" xr3:uid="{B1EC831D-AAA6-4546-AD4D-A7898AEF1410}" name="final_main_miss_count"/>
+    <tableColumn id="17" xr3:uid="{9C1D0E3E-6C2B-4E38-B9C9-CEE32C34BD50}" name="final_main_subclass_hit_count"/>
+    <tableColumn id="18" xr3:uid="{0E40E9DA-3E84-468A-8B0E-CC298C060D64}" name="final_main_subclass_miss_count"/>
+    <tableColumn id="19" xr3:uid="{E82AD334-BA43-43E9-A147-524A08BE3A83}" name="final_all_hit_count"/>
+    <tableColumn id="20" xr3:uid="{974CD933-6C21-4D4D-A464-1781EC413FDF}" name="final_all_miss_count"/>
+    <tableColumn id="21" xr3:uid="{A49960E1-2072-42F3-8DEB-35A226FCD882}" name="final_all_subclass_hit_count"/>
+    <tableColumn id="22" xr3:uid="{01120507-8C31-43EF-8336-480C94C840EE}" name="final_all_subclass_miss_count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1036,16 +1176,16 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.45" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" ht="18.45" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
@@ -1102,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742BDA38-63BE-424F-A9B2-256A772D5CD7}">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -1111,12 +1251,13 @@
     <col min="4" max="4" width="24.140625" customWidth="1"/>
     <col min="5" max="5" width="22.2109375" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.92578125" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" customWidth="1"/>
-    <col min="9" max="19" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="14.640625" customWidth="1"/>
+    <col min="8" max="8" width="19.92578125" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="20" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,44 +1279,80 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>93</v>
-      </c>
       <c r="J1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="L1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M1" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="N1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="O1" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="S1" t="s">
-        <v>92</v>
+        <v>72</v>
+      </c>
+      <c r="T1" t="s">
+        <v>185</v>
+      </c>
+      <c r="U1" t="s">
+        <v>186</v>
+      </c>
+      <c r="V1" t="s">
+        <v>79</v>
+      </c>
+      <c r="W1" t="s">
+        <v>187</v>
+      </c>
+      <c r="X1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>189</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>190</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>2019000004</v>
       </c>
@@ -1195,31 +1372,31 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2">
+        <v>84</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="J2">
-        <v>75</v>
-      </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -1233,8 +1410,44 @@
       <c r="S2">
         <v>2</v>
       </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>16</v>
+      </c>
+      <c r="W2">
+        <v>11</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>2</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2019000021</v>
       </c>
@@ -1254,31 +1467,31 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I3">
+        <v>87</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
-      <c r="J3">
-        <v>81</v>
-      </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -1292,8 +1505,44 @@
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>19</v>
+      </c>
+      <c r="W3">
+        <v>14</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>2</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2019000028</v>
       </c>
@@ -1303,7 +1552,9 @@
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
@@ -1311,46 +1562,82 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="J4">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>17</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
+      <c r="W4">
+        <v>11</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2019000046</v>
       </c>
@@ -1360,7 +1647,9 @@
       <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1368,46 +1657,82 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="J5">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
         <v>15</v>
       </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="W5">
+        <v>10</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2019000051</v>
       </c>
@@ -1417,7 +1742,9 @@
       <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1425,37 +1752,37 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="J6">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1463,8 +1790,44 @@
       <c r="S6">
         <v>1</v>
       </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>17</v>
+      </c>
+      <c r="W6">
+        <v>13</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2019000055</v>
       </c>
@@ -1484,46 +1847,82 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="J7">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
         <v>17</v>
       </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
+      <c r="W7">
+        <v>15</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2019000059</v>
       </c>
@@ -1543,37 +1942,37 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="I8">
+        <v>103</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8">
         <v>2</v>
       </c>
-      <c r="J8">
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
         <v>77</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
       <c r="M8">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1581,8 +1980,44 @@
       <c r="S8">
         <v>1</v>
       </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>18</v>
+      </c>
+      <c r="W8">
+        <v>11</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>2019000061</v>
       </c>
@@ -1592,7 +2027,9 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>34</v>
       </c>
@@ -1600,46 +2037,82 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
+        <v>106</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="J9">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
         <v>16</v>
       </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
+      <c r="W9">
+        <v>10</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2019000064</v>
       </c>
@@ -1659,37 +2132,37 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10">
+        <v>109</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10">
         <v>2</v>
       </c>
-      <c r="J10">
-        <v>69</v>
-      </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -1697,8 +2170,44 @@
       <c r="S10">
         <v>1</v>
       </c>
+      <c r="T10">
+        <v>2</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>20</v>
+      </c>
+      <c r="W10">
+        <v>16</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>2</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>2019000102</v>
       </c>
@@ -1718,31 +2227,31 @@
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I11">
+        <v>112</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11">
         <v>3</v>
       </c>
-      <c r="J11">
-        <v>57</v>
-      </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1756,8 +2265,44 @@
       <c r="S11">
         <v>3</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>17</v>
+      </c>
+      <c r="W11">
+        <v>9</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>3</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2019000125</v>
       </c>
@@ -1767,7 +2312,9 @@
       <c r="C12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>45</v>
       </c>
@@ -1775,46 +2322,82 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
+        <v>115</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="J12">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>16</v>
       </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
+      <c r="W12">
+        <v>10</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>2019000169</v>
       </c>
@@ -1824,7 +2407,9 @@
       <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E13" s="3" t="s">
         <v>48</v>
       </c>
@@ -1832,174 +2417,286 @@
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>69</v>
+      </c>
+      <c r="M13">
+        <v>44</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>17</v>
+      </c>
+      <c r="W13">
+        <v>9</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>2019000277</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H14" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>75</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
+      <c r="I14" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>64</v>
+      </c>
+      <c r="M14">
+        <v>48</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>17</v>
+      </c>
+      <c r="W14">
+        <v>16</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>1</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>2019000190</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="5" t="s">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>2019000293</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14">
-        <v>63</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>17</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14">
-        <v>1</v>
+      <c r="H15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>36</v>
+      </c>
+      <c r="M15">
+        <v>20</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>10</v>
+      </c>
+      <c r="W15">
+        <v>4</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>2019000203</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>56</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>16</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>2019000223</v>
+        <v>2019000297</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -2007,88 +2704,124 @@
       <c r="G16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="I16">
-        <v>1</v>
+      <c r="I16" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="J16">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N16">
         <v>1</v>
       </c>
       <c r="O16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>12</v>
+      </c>
+      <c r="W16">
+        <v>7</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
-        <v>2019000227</v>
+        <v>2019000302</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="I17">
-        <v>1</v>
+      <c r="H17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="J17">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -2102,514 +2835,848 @@
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>23</v>
+      </c>
+      <c r="W17">
+        <v>17</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>2019000246</v>
+        <v>2019000311</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="E18" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
+        <v>133</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="J18">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>17</v>
+      </c>
+      <c r="W18">
         <v>13</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>1</v>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
-        <v>2019000249</v>
+        <v>2019000319</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>63</v>
+      </c>
+      <c r="M19">
+        <v>44</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>13</v>
+      </c>
+      <c r="W19">
+        <v>10</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>2019000342</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>75</v>
+      </c>
+      <c r="M20">
+        <v>52</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>17</v>
+      </c>
+      <c r="W20">
+        <v>13</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>2019000344</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>65</v>
+      </c>
+      <c r="M21">
+        <v>45</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>15</v>
+      </c>
+      <c r="W21">
+        <v>8</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>1</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>2019000350</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
+      <c r="D22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>63</v>
+      </c>
+      <c r="M22">
+        <v>48</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>16</v>
+      </c>
+      <c r="W22">
+        <v>12</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>2019000351</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <v>66</v>
+      </c>
+      <c r="M23">
+        <v>50</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>2</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>16</v>
+      </c>
+      <c r="W23">
+        <v>10</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>2019000384</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
+      <c r="D24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>72</v>
+      </c>
+      <c r="M24">
+        <v>55</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>11</v>
+      </c>
+      <c r="W24">
+        <v>10</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
+        <v>2019000385</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>73</v>
+      </c>
+      <c r="M25">
+        <v>51</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
         <v>12</v>
       </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>1</v>
+      <c r="W25">
+        <v>8</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>1</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <v>2019000250</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>2019000403</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20">
+      <c r="D26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="J26">
         <v>2</v>
       </c>
-      <c r="J20">
-        <v>80</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>19</v>
-      </c>
-      <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
-      </c>
-      <c r="S20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
-        <v>2019000266</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>66</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>15</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
-        <v>2019000277</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>65</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>16</v>
-      </c>
-      <c r="P22">
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
-        <v>2019000293</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>43</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>11</v>
-      </c>
-      <c r="P23">
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
-        <v>2019000297</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="2">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>61</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>14</v>
-      </c>
-      <c r="P24">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>2019000302</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>86</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>22</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <v>2019000311</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>73</v>
-      </c>
       <c r="K26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -2618,18 +3685,55 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>2</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>12</v>
+      </c>
+      <c r="W26">
+        <v>6</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>2</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>2</v>
+      </c>
+      <c r="AE26">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H26" xr:uid="{742BDA38-63BE-424F-A9B2-256A772D5CD7}"/>
+  <autoFilter ref="A1:I26" xr:uid="{742BDA38-63BE-424F-A9B2-256A772D5CD7}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
